--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -567,7 +567,7 @@
         <v>45174</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         <v>44112</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44175</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44266</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45313</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45475</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>45195</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45604.4624537037</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>45840.46792824074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45158</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>44315</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>44455</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>44859</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45103</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45604.48800925926</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44833</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>45450.57783564815</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>45747</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45517.34768518519</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45404.55137731481</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45604.53089120371</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45826.4996875</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44937</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44295</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>44375</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>44827</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44207</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>44132</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45747</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>44054</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>45335</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>44950</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>44384</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>44091</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44550</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44676</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>45623</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>44160</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>45688.59202546296</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>45789.61961805556</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>45791.44271990741</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>44998</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>44663</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>45820.48319444444</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>45825</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>44858</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>45688.41431712963</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44207</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>44179.52865740741</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44243</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>44270.56321759259</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>44228</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>44069</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>44155</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>44069</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>44069</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>44089</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>44267.64171296296</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>44320.42899305555</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>44386</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>44386</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>44865.57608796296</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>44069</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>44887.42784722222</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>44887.42950231482</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44307.45770833334</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>44508</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>44175</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>44225</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>44201</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>44201</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>44201</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44285</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>44201</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>44613.65383101852</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44524.32766203704</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44483.4240625</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44193</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44225</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44202</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>44447</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44085</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44242</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>44487</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>44552.45428240741</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>44536</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>44574.4577662037</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>44461.68690972222</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>44510</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>44456</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>44127</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>44734.36189814815</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>44273</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>44321</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>44812.51043981482</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>44319.33803240741</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>44859</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44176.66133101852</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>44225</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>44229</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>44574.45553240741</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44165</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>44859</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44278</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>44265.69087962963</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>44676.551875</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44859</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>44859</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44749</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44574.43967592593</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>44602</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44580</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>44602.57726851852</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>44217</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44088.78303240741</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44201</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>44201</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>44859</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>44308</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>44430.93283564815</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>44795.48144675926</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44259</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44757.40570601852</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>44124</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>44228</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>44225</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44228</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>44225</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>44887.43138888889</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>44588.6396875</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44088</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>44505</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>44456</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>44069</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>44207</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>44434</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>44845</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>44375</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>44375</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44270.5584375</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>44364</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>44497</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>44552.45563657407</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>44201</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>44483.66988425926</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>44483.67144675926</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44375</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>44503</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>44475</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>44510</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>44376</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>44119</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>44601.75174768519</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>44524.46141203704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>44214</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>44858.49122685185</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44690</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>44602.51873842593</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44721.32116898148</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>44424.57810185185</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>44069</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>44683.46200231482</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>44686</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>44607</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>44607</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>44803.35861111111</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>44887.42521990741</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>44887.42283564815</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44887.42663194444</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>44490.74336805556</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44343.88627314815</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>44459</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>44711.38366898148</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>44074</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>44676.56075231481</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44610</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44609</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44089.35622685185</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>44531</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>44522.60883101852</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>44375</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>44371</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>44250</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44127</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>44253</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>44795.60174768518</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>44795.60293981482</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>44336.39239583333</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>44424.57476851852</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44242</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>44102</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>44328.41473379629</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>44470</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>44837.43361111111</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>44582</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>44475.66188657407</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44729.65407407407</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44859</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>44158</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>44068</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>44788.47552083333</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>44574</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>44175</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44207</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>44705</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>44284</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>44056</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>44175</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>44120</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>44602</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>44344.48678240741</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>44420.28219907408</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>44393</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>44757</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>44466</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>44603</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>44602</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>44120</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>44592.48909722222</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>44073</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45737</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>44285.87041666666</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>45273.60899305555</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>45273</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>45622</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>45233</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45755</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>44998.55319444444</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>45761.93627314815</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>45730</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>45761</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>44073</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45428.55946759259</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>45428.5703587963</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>45428.57371527778</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>45709.38748842593</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>45709.39251157407</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>45091</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>45709.38243055555</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>45745.75537037037</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45749</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45698</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45028</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>45244.86136574074</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>44276</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>45190.39688657408</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>44097</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>45338</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45338</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>44160</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>45691.56284722222</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>45454.73359953704</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>45335.63689814815</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>45341.58440972222</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>45118.36900462963</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45364.57331018519</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45697.97704861111</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>45385.49137731481</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45041.59671296296</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45041</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>44308</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>44375</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>44593.63554398148</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>45338</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45338</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45338</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>44881.54231481482</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45401.44325231481</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>45105.48627314815</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>44924.79619212963</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>45012</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>45208.64244212963</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>45391.58608796296</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45114.65185185185</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>45164</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>44354</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>44833</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45770.62311342593</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>45525.6055787037</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45643.43193287037</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45615</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44165</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45716.33921296296</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>45112.3402199074</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>45105.47802083333</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>45244.67376157407</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>45755.42104166667</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>44285.33586805555</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>45749</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>45670.3792824074</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44844.67142361111</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45764</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45775.49840277778</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45764</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>44392.68070601852</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>45459.71949074074</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45706.36192129629</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45085</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45583.40994212963</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>45005</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>44098</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>45098</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>45755</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>44882</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>44971.76994212963</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>45400</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45705.35732638889</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>45590</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>44757.39927083333</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>44757.40454861111</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>44153</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45082</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>44468.68219907407</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20210,7 +20210,7 @@
         <v>44446</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>45604.56427083333</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>45604.56517361111</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>45761.93880787037</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>45604.56623842593</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>45190.47119212963</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45708.35037037037</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>45471</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45692.42515046296</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>45400</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>44162</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45181</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>45229.49331018519</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45407.5766087963</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>45385</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44937</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44937.46436342593</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>45204</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44327</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45389</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>45389</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>45229.53780092593</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45091</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>45085</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44917.58131944444</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>45140</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>45749.74931712963</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>45716.34958333334</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>45547.62819444444</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44074</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>45547.62703703704</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44838</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>45440.6484375</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44994.45271990741</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>45660</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>44610</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>45149</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45093.34891203704</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45596.54981481482</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>45386.35322916666</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45295</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>45679.50844907408</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>44942.49850694444</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45698</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44789.46129629629</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45140</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>45219.79758101852</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>45737.65526620371</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>45085.53467592593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>45279.61047453704</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>44790</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>45401.690625</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>44154</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45427.9417824074</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45729.35393518519</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45716.35056712963</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>45428.57160879629</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45428.57215277778</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>45590.38761574074</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>45338</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>45338</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45716.3528125</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45019</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45369.42203703704</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>44524.66444444445</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>44503.58450231481</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>45349</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>45348</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>45348</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>45154.57079861111</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>45642</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>45714.37306712963</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>45001</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>45575.84530092592</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>45057</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>45154.65458333334</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>45728</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>45722.96171296296</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>45434.44790509259</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         <v>45506.60435185185</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>45288.46611111111</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>45709.42873842592</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>44073</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>45229.58863425926</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>45737</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44069</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>44734.3744212963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>44734.37710648148</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         <v>45165.77501157407</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>45082.56950231481</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>45245.37445601852</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>44438</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>44396</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44496</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>45489.50666666667</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>45544.33987268519</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44400</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>45749.46740740741</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>45428.54791666667</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>45709.42712962963</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45506.59847222222</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>45537.45255787037</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>45685.55012731482</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>45561.37106481481</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45428.53717592593</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>45428.54854166666</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26357,7 +26357,7 @@
         <v>45428.54914351852</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26414,7 +26414,7 @@
         <v>45428.55339120371</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>45428.56928240741</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>45428.58675925926</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>45568</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45568</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>45544.36982638889</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>45639.59918981481</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44105</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45335.63466435186</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26942,7 +26942,7 @@
         <v>45642.46802083333</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>45428.55409722222</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         <v>45428.55619212963</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>45320</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>44167</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>45384.42409722223</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>45336.92125</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>45642.47061342592</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>45428.54546296296</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45391.59185185185</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>45600.47440972222</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>45428.56197916667</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>45273</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>45279.37215277777</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27750,7 +27750,7 @@
         <v>45454.73629629629</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>45601</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45516.37174768518</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>45517.38890046296</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>45348.33475694444</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>44526</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>44140</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>44140</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>45089</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45709.33226851852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>45716.34298611111</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>45716.34217592593</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>45716.34775462963</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28516,7 +28516,7 @@
         <v>44998</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>45540.56981481481</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>45103</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28692,7 +28692,7 @@
         <v>44592.50912037037</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28749,7 +28749,7 @@
         <v>45181</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28806,7 +28806,7 @@
         <v>45428.56533564815</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>45428.57266203704</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>45607.37846064815</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>45783.38083333334</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>45469.34783564815</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>45674.38413194445</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45783.47896990741</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>45428.5499537037</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>45428.55199074074</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>44140</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>45049</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>44599</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29495,7 +29495,7 @@
         <v>45476</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>44152</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>45366</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>44154</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45153</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>45692</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>45488.46717592593</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>45677.70096064815</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>45530.36846064815</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>44154</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>45098.44975694444</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>45502.49574074074</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>45720.41747685185</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>45749.46461805556</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>45435.77655092593</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>44430.29293981481</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>45604.56101851852</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>45604.56190972222</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>45604.56958333333</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44984</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>45229</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45742</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45552.6449537037</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>45552</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>45476.50758101852</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44154</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>45389.74396990741</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>45747</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45747.61878472222</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>45747</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31245,7 +31245,7 @@
         <v>45786</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>45552.65006944445</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31359,7 +31359,7 @@
         <v>45113.36457175926</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>45013</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>45755.41075231481</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>45728.59358796296</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45604.44618055555</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45162</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>44942</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45692</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45154.56967592592</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31872,7 +31872,7 @@
         <v>44524</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>44524</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45233</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>45146</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>45211.81873842593</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32162,7 +32162,7 @@
         <v>45590.39090277778</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45146</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>45649.6427662037</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>44942.60704861111</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45428.53776620371</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45118</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>45320.58873842593</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>45355.56142361111</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>45791</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>45370.64554398148</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>44592.72989583333</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>45688.58755787037</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>45688.63835648148</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>44153.45842592593</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>45408.61435185185</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45736.32833333333</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>45338.43358796297</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>45338</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>45338</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>45622</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44124</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>45604.5687962963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45783</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>45204.42494212963</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44985</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>45597.34225694444</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45610.35752314814</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>45579</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>45604.48289351852</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44250</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>45792.81104166667</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45404</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>44659.58702546296</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34093,7 +34093,7 @@
         <v>45579</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>45636.96761574074</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>45338.43309027778</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45749.75060185185</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>45708.27960648148</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>45702.36793981482</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>45722.40604166667</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>45838.37465277778</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34559,7 +34559,7 @@
         <v>45838.6196875</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>44610</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>45474.36921296296</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>45191</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>45835.48375</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>45389.73820601852</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>45835.37094907407</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34963,7 +34963,7 @@
         <v>45597.35365740741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
         <v>45737.65686342592</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>45763.68868055556</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35144,7 +35144,7 @@
         <v>45763.69137731481</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>45642.47158564815</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>45223.60331018519</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>45839.58087962963</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>44945.39559027777</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45597.38799768518</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45597.39101851852</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>45839</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>45839</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>44844</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45063.27048611111</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>45840.479375</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>44858</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45597.3521412037</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35967,7 +35967,7 @@
         <v>45770</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36024,7 +36024,7 @@
         <v>45770</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36081,7 +36081,7 @@
         <v>45770</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>45372.49736111111</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45737.65869212963</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45737</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45743.59358796296</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45567.53571759259</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45440.63173611111</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45840.49215277778</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45169.38462962963</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45218</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>45729.67947916667</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>45372.49458333333</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36765,7 +36765,7 @@
         <v>44593</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>45196.47457175926</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>45841.74796296296</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>45404.56375</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>44229</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45278.39707175926</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37107,7 +37107,7 @@
         <v>45842.55467592592</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         <v>45547.6262037037</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>45841.73791666667</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37278,7 +37278,7 @@
         <v>45009</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37335,7 +37335,7 @@
         <v>45223</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>44923</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>45629.38060185185</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>45842.48019675926</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>45842.47915509259</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>44566</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45720.40681712963</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>45664.57111111111</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>45057</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45534</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37910,7 +37910,7 @@
         <v>45117</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>45273.615</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45800.6135300926</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38081,7 +38081,7 @@
         <v>45801.7406712963</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>45804</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>45804.49788194444</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>45211</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45804.40983796296</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38366,7 +38366,7 @@
         <v>45093</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>45688.58667824074</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>45801.72324074074</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>45107.61413194444</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>45604.56769675926</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45195</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45604.48214120371</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>45801.7155324074</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38837,7 +38837,7 @@
         <v>45804</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38894,7 +38894,7 @@
         <v>45801.73608796296</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>45757</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45764</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>45317</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39137,7 +39137,7 @@
         <v>44984</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>44984</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39251,7 +39251,7 @@
         <v>45184.46447916667</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39308,7 +39308,7 @@
         <v>44971.75834490741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39365,7 +39365,7 @@
         <v>45757.34662037037</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45075.50622685185</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45211</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>45085</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>45840.66209490741</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39650,7 +39650,7 @@
         <v>45459.71376157407</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39707,7 +39707,7 @@
         <v>45805.59104166667</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39764,7 +39764,7 @@
         <v>44496.58679398148</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>45764</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>44971.76626157408</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39940,7 +39940,7 @@
         <v>45709.32859953704</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40002,7 +40002,7 @@
         <v>45709.40761574074</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40064,7 +40064,7 @@
         <v>45354.72975694444</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
         <v>45460.82011574074</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45041</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40235,7 +40235,7 @@
         <v>45153</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40292,7 +40292,7 @@
         <v>45174</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40349,7 +40349,7 @@
         <v>45230</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45807.45759259259</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40468,7 +40468,7 @@
         <v>44074</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40525,7 +40525,7 @@
         <v>45547.62553240741</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>44523.4103587963</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40639,7 +40639,7 @@
         <v>45475</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>45688.43215277778</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40753,7 +40753,7 @@
         <v>45807.45905092593</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>45807.46021990741</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>44757</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40929,7 +40929,7 @@
         <v>45163.72633101852</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40986,7 +40986,7 @@
         <v>45181</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45838.67675925926</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41105,7 +41105,7 @@
         <v>45357.39202546296</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41162,7 +41162,7 @@
         <v>45615</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45811.59519675926</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41276,7 +41276,7 @@
         <v>45204</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>45769.41568287037</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>45709.40560185185</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41452,7 +41452,7 @@
         <v>45604.26549768518</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>45597.38953703704</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>45854.62081018519</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45118</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>45693</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45693</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>45155</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41856,7 +41856,7 @@
         <v>45243</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41913,7 +41913,7 @@
         <v>45709.39714120371</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>44915.41944444444</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45709.39515046297</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42094,7 +42094,7 @@
         <v>45709.40043981482</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45777.45011574074</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>45336</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>45818</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>44858</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45727.61247685185</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45692</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>44757.40103009259</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44757.40538194445</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>45201.50586805555</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>44054</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>45819.32747685185</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>44406</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42865,7 +42865,7 @@
         <v>45028</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42927,7 +42927,7 @@
         <v>45230</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>45819.46775462963</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>45734</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43103,7 +43103,7 @@
         <v>45351</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>45754.55663194445</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43217,7 +43217,7 @@
         <v>45861.42532407407</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45861.43393518519</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45264.6516087963</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>44939</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>44939</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>45692</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>44064</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43616,7 +43616,7 @@
         <v>44924.77766203704</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43673,7 +43673,7 @@
         <v>45824.48737268519</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>45865.66577546296</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43787,7 +43787,7 @@
         <v>45865</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>44369.46261574074</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>45230</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43963,7 +43963,7 @@
         <v>45865.67818287037</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44020,7 +44020,7 @@
         <v>45644.36364583333</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44077,7 +44077,7 @@
         <v>45826.50130787037</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>45324.40112268519</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
         <v>45279</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>45826.37920138889</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>45826.50511574074</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
         <v>45637.63881944444</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>45825.40163194444</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44476,7 +44476,7 @@
         <v>45219.44987268518</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>45825.58365740741</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>45825.46516203704</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>45826.49353009259</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44704,7 +44704,7 @@
         <v>44410</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45224</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45869.39628472222</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45205.35776620371</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>44757.40493055555</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44999,7 +44999,7 @@
         <v>45688</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>45688.64506944444</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>45831.5818287037</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>45831</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45237,7 +45237,7 @@
         <v>44361.93059027778</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45294,7 +45294,7 @@
         <v>44603</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>45155</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>45839</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>45839</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45542,7 +45542,7 @@
         <v>45737</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>45737</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45656,7 +45656,7 @@
         <v>45832.47321759259</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>45831.37613425926</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45775,7 +45775,7 @@
         <v>45873</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>45831.36230324074</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45889,7 +45889,7 @@
         <v>44278</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>45146</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         <v>45146</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46060,7 +46060,7 @@
         <v>45831.37420138889</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>44208</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46179,7 +46179,7 @@
         <v>45320.88226851852</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46236,7 +46236,7 @@
         <v>45831.51181712963</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>45764.67251157408</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>45666</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46407,7 +46407,7 @@
         <v>45709.40309027778</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>45308</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>45538.80545138889</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>45875</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>45547.62391203704</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>45547.62475694445</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>45764</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46816,7 +46816,7 @@
         <v>45764.84103009259</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46878,7 +46878,7 @@
         <v>45736.32997685186</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45736.33076388889</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47002,7 +47002,7 @@
         <v>45770.625625</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>44922.50314814815</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>45385.44706018519</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>44124</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47235,7 +47235,7 @@
         <v>45338</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>45338.43268518519</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>44897.42872685185</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>44459.56224537037</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>44951</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47530,7 +47530,7 @@
         <v>44946</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47587,7 +47587,7 @@
         <v>45561.3744212963</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>44160</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>45261</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47763,7 +47763,7 @@
         <v>44552.46184027778</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47820,7 +47820,7 @@
         <v>44595.55912037037</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>44533.35804398148</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47934,7 +47934,7 @@
         <v>45164</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47991,7 +47991,7 @@
         <v>44638.34265046296</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>45230.37582175926</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48110,7 +48110,7 @@
         <v>44089.35689814815</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48172,7 +48172,7 @@
         <v>44887</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>44054</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48286,7 +48286,7 @@
         <v>44468.65578703704</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48343,7 +48343,7 @@
         <v>45428.57578703704</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48400,7 +48400,7 @@
         <v>45398.79873842592</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48457,7 +48457,7 @@
         <v>45204</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48514,7 +48514,7 @@
         <v>45607.60341435186</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48571,7 +48571,7 @@
         <v>45595.77847222222</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48628,7 +48628,7 @@
         <v>45546.60894675926</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>45604.47792824074</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48742,7 +48742,7 @@
         <v>45226.45565972223</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48799,7 +48799,7 @@
         <v>45455</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>45232.72258101852</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48918,7 +48918,7 @@
         <v>45568</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45275.35230324074</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45245.7939699074</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>44711.38688657407</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49151,7 +49151,7 @@
         <v>44994.45623842593</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49208,7 +49208,7 @@
         <v>44902.79445601852</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49265,7 +49265,7 @@
         <v>45428.55520833333</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>45674.38553240741</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45174.34193287037</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45597.34579861111</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>45597.34881944444</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49565,7 +49565,7 @@
         <v>45600.45402777778</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49622,7 +49622,7 @@
         <v>44908</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49684,7 +49684,7 @@
         <v>44697</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49746,7 +49746,7 @@
         <v>45069.69295138889</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49803,7 +49803,7 @@
         <v>45020</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>44260</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>45668.63396990741</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45260.46252314815</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50036,7 +50036,7 @@
         <v>44865.54231481482</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45156.54523148148</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50150,7 +50150,7 @@
         <v>45369.44256944444</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50207,7 +50207,7 @@
         <v>44375</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>45434.56020833334</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50321,7 +50321,7 @@
         <v>45375</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50378,7 +50378,7 @@
         <v>45427.93607638889</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>45225</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50492,7 +50492,7 @@
         <v>45350</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -567,7 +567,7 @@
         <v>45174</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         <v>44112</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44175</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44266</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45313</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45475</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>45195</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45604.4624537037</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>45840.46792824074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45158</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>44315</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>44455</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>44859</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45103</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45604.48800925926</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44833</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>45450.57783564815</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>45747</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45517.34768518519</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45404.55137731481</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45604.53089120371</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45826.4996875</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44937</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44295</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>44375</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>44827</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44207</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>44132</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45747</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>44054</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>45335</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>44950</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>44384</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>44091</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44550</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44676</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>45623</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>44160</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>45688.59202546296</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>45789.61961805556</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>45791.44271990741</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>44998</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>44663</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>45820.48319444444</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>45825</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>44858</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>45688.41431712963</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44207</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>44179.52865740741</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44243</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>44270.56321759259</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>44228</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>44069</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>44155</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>44069</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>44069</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>44089</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>44267.64171296296</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>44320.42899305555</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>44386</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>44386</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>44865.57608796296</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>44069</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>44887.42784722222</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>44887.42950231482</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44307.45770833334</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>44508</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>44175</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>44225</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>44201</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>44201</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>44201</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44285</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>44201</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>44613.65383101852</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44524.32766203704</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44483.4240625</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44193</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44225</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44202</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>44447</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44085</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44242</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>44487</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>44552.45428240741</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>44536</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>44574.4577662037</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>44461.68690972222</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>44510</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>44456</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>44127</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>44734.36189814815</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>44273</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>44321</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>44812.51043981482</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>44319.33803240741</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>44859</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44176.66133101852</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>44225</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>44229</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>44574.45553240741</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44165</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>44859</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44278</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>44265.69087962963</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>44676.551875</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44859</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>44859</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44749</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44574.43967592593</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>44602</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44580</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>44602.57726851852</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>44217</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44088.78303240741</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44201</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>44201</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>44859</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>44308</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>44430.93283564815</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>44795.48144675926</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44259</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44757.40570601852</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>44124</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>44228</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>44225</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44228</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>44225</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>44887.43138888889</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>44588.6396875</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44088</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>44505</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>44456</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>44069</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>44207</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>44434</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>44845</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>44375</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>44375</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44270.5584375</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>44364</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>44497</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>44552.45563657407</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>44201</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>44483.66988425926</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>44483.67144675926</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44375</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>44503</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>44475</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>44510</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>44376</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>44119</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>44601.75174768519</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>44524.46141203704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>44214</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>44858.49122685185</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44690</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>44602.51873842593</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44721.32116898148</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>44424.57810185185</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>44069</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>44683.46200231482</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>44686</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>44607</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>44607</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>44803.35861111111</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>44887.42521990741</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>44887.42283564815</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44887.42663194444</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>44490.74336805556</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44343.88627314815</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>44459</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>44711.38366898148</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>44074</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>44676.56075231481</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44610</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44609</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44089.35622685185</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>44531</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>44522.60883101852</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>44375</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>44371</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>44250</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44127</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>44253</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>44795.60174768518</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>44795.60293981482</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>44336.39239583333</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>44424.57476851852</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44242</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>44102</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>44328.41473379629</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>44470</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>44837.43361111111</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>44582</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>44475.66188657407</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44729.65407407407</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44859</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>44158</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>44068</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>44788.47552083333</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>44574</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>44175</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44207</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>44705</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>44284</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>44056</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>44175</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>44120</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>44602</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>44344.48678240741</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>44420.28219907408</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>44393</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>44757</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>44466</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>44603</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>44602</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>44120</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>44592.48909722222</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>44073</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45737</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>44285.87041666666</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>45273.60899305555</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>45273</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>45622</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>45233</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45755</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>44998.55319444444</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>45761.93627314815</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>45730</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>45761</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>44073</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45428.55946759259</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>45428.5703587963</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>45428.57371527778</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>45709.38748842593</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>45709.39251157407</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>45091</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>45709.38243055555</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>45745.75537037037</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45749</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45698</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45028</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>45244.86136574074</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>44276</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>45190.39688657408</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>44097</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>45338</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45338</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>44160</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>45691.56284722222</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>45454.73359953704</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>45335.63689814815</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>45341.58440972222</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>45118.36900462963</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45364.57331018519</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45697.97704861111</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>45385.49137731481</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45041.59671296296</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45041</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>44308</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>44375</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>44593.63554398148</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>45338</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45338</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45338</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>44881.54231481482</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45401.44325231481</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>45105.48627314815</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>44924.79619212963</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>45012</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>45208.64244212963</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>45391.58608796296</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45114.65185185185</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>45164</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>44354</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>44833</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45770.62311342593</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>45525.6055787037</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45643.43193287037</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45615</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44165</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45716.33921296296</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>45112.3402199074</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>45105.47802083333</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>45244.67376157407</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>45755.42104166667</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>44285.33586805555</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>45749</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>45670.3792824074</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44844.67142361111</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45764</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45775.49840277778</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45764</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>44392.68070601852</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>45459.71949074074</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45706.36192129629</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45085</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45583.40994212963</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>45005</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>44098</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>45098</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>45755</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>44882</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>44971.76994212963</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>45400</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45705.35732638889</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>45590</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>44757.39927083333</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>44757.40454861111</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>44153</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45082</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>44468.68219907407</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20210,7 +20210,7 @@
         <v>44446</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>45604.56427083333</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>45604.56517361111</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>45761.93880787037</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>45604.56623842593</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>45190.47119212963</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45708.35037037037</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>45471</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45692.42515046296</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>45400</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>44162</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45181</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>45229.49331018519</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45407.5766087963</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>45385</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44937</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44937.46436342593</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>45204</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44327</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45389</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>45389</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>45229.53780092593</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45091</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>45085</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44917.58131944444</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>45140</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>45749.74931712963</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>45716.34958333334</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>45547.62819444444</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44074</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>45547.62703703704</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44838</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>45440.6484375</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44994.45271990741</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>45660</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>44610</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>45149</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45093.34891203704</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45596.54981481482</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>45386.35322916666</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45295</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>45679.50844907408</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>44942.49850694444</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45698</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44789.46129629629</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45140</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>45219.79758101852</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>45737.65526620371</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>45085.53467592593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>45279.61047453704</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>44790</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>45401.690625</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>44154</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45427.9417824074</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45729.35393518519</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45716.35056712963</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>45428.57160879629</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45428.57215277778</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>45590.38761574074</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>45338</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>45338</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45716.3528125</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45019</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45369.42203703704</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>44524.66444444445</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>44503.58450231481</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>45349</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>45348</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>45348</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>45154.57079861111</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>45642</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>45714.37306712963</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>45001</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>45575.84530092592</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>45057</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>45154.65458333334</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>45728</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>45722.96171296296</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>45434.44790509259</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         <v>45506.60435185185</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>45288.46611111111</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>45709.42873842592</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>44073</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>45229.58863425926</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>45737</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44069</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>44734.3744212963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>44734.37710648148</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         <v>45165.77501157407</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>45082.56950231481</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>45245.37445601852</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>44438</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>44396</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44496</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>45489.50666666667</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>45544.33987268519</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44400</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>45749.46740740741</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>45428.54791666667</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>45709.42712962963</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45506.59847222222</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>45537.45255787037</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>45685.55012731482</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>45561.37106481481</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45428.53717592593</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>45428.54854166666</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26357,7 +26357,7 @@
         <v>45428.54914351852</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26414,7 +26414,7 @@
         <v>45428.55339120371</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>45428.56928240741</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>45428.58675925926</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>45568</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45568</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>45544.36982638889</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>45639.59918981481</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44105</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45335.63466435186</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26942,7 +26942,7 @@
         <v>45642.46802083333</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>45428.55409722222</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         <v>45428.55619212963</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>45320</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>44167</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>45384.42409722223</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>45336.92125</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>45642.47061342592</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>45428.54546296296</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45391.59185185185</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>45600.47440972222</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>45428.56197916667</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>45273</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>45279.37215277777</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27750,7 +27750,7 @@
         <v>45454.73629629629</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>45601</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45516.37174768518</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>45517.38890046296</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>45348.33475694444</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>44526</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>44140</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>44140</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>45089</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45709.33226851852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>45716.34298611111</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>45716.34217592593</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>45716.34775462963</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28516,7 +28516,7 @@
         <v>44998</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>45540.56981481481</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>45103</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28692,7 +28692,7 @@
         <v>44592.50912037037</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28749,7 +28749,7 @@
         <v>45181</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28806,7 +28806,7 @@
         <v>45428.56533564815</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>45428.57266203704</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>45607.37846064815</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>45783.38083333334</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>45469.34783564815</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>45674.38413194445</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45783.47896990741</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>45428.5499537037</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>45428.55199074074</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>44140</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>45049</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>44599</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29495,7 +29495,7 @@
         <v>45476</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>44152</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>45366</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>44154</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45153</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>45692</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>45488.46717592593</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>45677.70096064815</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>45530.36846064815</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>44154</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>45098.44975694444</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>45502.49574074074</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>45720.41747685185</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>45749.46461805556</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>45435.77655092593</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>44430.29293981481</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>45604.56101851852</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>45604.56190972222</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>45604.56958333333</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44984</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>45229</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45742</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45552.6449537037</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>45552</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>45476.50758101852</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44154</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>45389.74396990741</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>45747</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45747.61878472222</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>45747</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31245,7 +31245,7 @@
         <v>45786</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>45552.65006944445</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31359,7 +31359,7 @@
         <v>45113.36457175926</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>45013</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>45755.41075231481</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>45728.59358796296</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45604.44618055555</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45162</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>44942</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45692</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45154.56967592592</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31872,7 +31872,7 @@
         <v>44524</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>44524</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45233</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>45146</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>45211.81873842593</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32162,7 +32162,7 @@
         <v>45590.39090277778</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45146</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>45649.6427662037</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>44942.60704861111</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45428.53776620371</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45118</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>45320.58873842593</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>45355.56142361111</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>45791</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>45370.64554398148</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>44592.72989583333</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>45688.58755787037</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>45688.63835648148</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>44153.45842592593</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>45408.61435185185</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45736.32833333333</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>45338.43358796297</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>45338</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>45338</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>45622</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44124</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>45604.5687962963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45783</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>45204.42494212963</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44985</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>45597.34225694444</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45610.35752314814</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>45579</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>45604.48289351852</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44250</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>45792.81104166667</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45404</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>44659.58702546296</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34093,7 +34093,7 @@
         <v>45579</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>45636.96761574074</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>45338.43309027778</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45749.75060185185</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>45708.27960648148</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>45702.36793981482</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>45722.40604166667</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>45838.37465277778</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34559,7 +34559,7 @@
         <v>45838.6196875</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>44610</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>45474.36921296296</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>45191</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>45835.48375</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>45389.73820601852</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>45835.37094907407</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34963,7 +34963,7 @@
         <v>45597.35365740741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
         <v>45737.65686342592</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>45763.68868055556</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35144,7 +35144,7 @@
         <v>45763.69137731481</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>45642.47158564815</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>45223.60331018519</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>45839.58087962963</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>44945.39559027777</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45597.38799768518</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45597.39101851852</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>45839</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>45839</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>44844</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45063.27048611111</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>45840.479375</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>44858</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45597.3521412037</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35967,7 +35967,7 @@
         <v>45770</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36024,7 +36024,7 @@
         <v>45770</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36081,7 +36081,7 @@
         <v>45770</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>45372.49736111111</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45737.65869212963</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45737</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45743.59358796296</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45567.53571759259</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45440.63173611111</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45840.49215277778</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45169.38462962963</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45218</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>45729.67947916667</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>45372.49458333333</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36765,7 +36765,7 @@
         <v>44593</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>45196.47457175926</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>45841.74796296296</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>45404.56375</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>44229</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45278.39707175926</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37107,7 +37107,7 @@
         <v>45842.55467592592</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         <v>45547.6262037037</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>45841.73791666667</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37278,7 +37278,7 @@
         <v>45009</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37335,7 +37335,7 @@
         <v>45223</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>44923</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>45629.38060185185</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>45842.48019675926</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>45842.47915509259</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>44566</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45720.40681712963</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>45664.57111111111</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>45057</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45534</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37910,7 +37910,7 @@
         <v>45117</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>45273.615</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45800.6135300926</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38081,7 +38081,7 @@
         <v>45801.7406712963</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>45804</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>45804.49788194444</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>45211</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45804.40983796296</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38366,7 +38366,7 @@
         <v>45093</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>45688.58667824074</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>45801.72324074074</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>45107.61413194444</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>45604.56769675926</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45195</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45604.48214120371</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>45801.7155324074</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38837,7 +38837,7 @@
         <v>45804</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38894,7 +38894,7 @@
         <v>45801.73608796296</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>45757</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45764</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>45317</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39137,7 +39137,7 @@
         <v>44984</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>44984</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39251,7 +39251,7 @@
         <v>45184.46447916667</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39308,7 +39308,7 @@
         <v>44971.75834490741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39365,7 +39365,7 @@
         <v>45757.34662037037</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45075.50622685185</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45211</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>45085</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>45840.66209490741</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39650,7 +39650,7 @@
         <v>45459.71376157407</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39707,7 +39707,7 @@
         <v>45805.59104166667</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39764,7 +39764,7 @@
         <v>44496.58679398148</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>45764</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>44971.76626157408</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39940,7 +39940,7 @@
         <v>45709.32859953704</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40002,7 +40002,7 @@
         <v>45709.40761574074</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40064,7 +40064,7 @@
         <v>45354.72975694444</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
         <v>45460.82011574074</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45041</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40235,7 +40235,7 @@
         <v>45153</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40292,7 +40292,7 @@
         <v>45174</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40349,7 +40349,7 @@
         <v>45230</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45807.45759259259</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40468,7 +40468,7 @@
         <v>44074</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40525,7 +40525,7 @@
         <v>45547.62553240741</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>44523.4103587963</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40639,7 +40639,7 @@
         <v>45475</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>45688.43215277778</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40753,7 +40753,7 @@
         <v>45807.45905092593</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>45807.46021990741</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>44757</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40929,7 +40929,7 @@
         <v>45163.72633101852</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40986,7 +40986,7 @@
         <v>45181</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45838.67675925926</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41105,7 +41105,7 @@
         <v>45357.39202546296</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41162,7 +41162,7 @@
         <v>45615</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45811.59519675926</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41276,7 +41276,7 @@
         <v>45204</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>45769.41568287037</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>45709.40560185185</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41452,7 +41452,7 @@
         <v>45604.26549768518</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>45597.38953703704</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>45854.62081018519</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45118</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>45693</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45693</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>45155</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41856,7 +41856,7 @@
         <v>45243</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41913,7 +41913,7 @@
         <v>45709.39714120371</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>44915.41944444444</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45709.39515046297</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42094,7 +42094,7 @@
         <v>45709.40043981482</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45777.45011574074</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>45336</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>45818</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>44858</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45727.61247685185</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45692</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>44757.40103009259</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44757.40538194445</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>45201.50586805555</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>44054</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>45819.32747685185</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>44406</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42865,7 +42865,7 @@
         <v>45028</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42927,7 +42927,7 @@
         <v>45230</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>45819.46775462963</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>45734</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43103,7 +43103,7 @@
         <v>45351</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>45754.55663194445</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43217,7 +43217,7 @@
         <v>45861.42532407407</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45861.43393518519</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45264.6516087963</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>44939</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>44939</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>45692</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>44064</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43616,7 +43616,7 @@
         <v>44924.77766203704</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43673,7 +43673,7 @@
         <v>45824.48737268519</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>45865.66577546296</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43787,7 +43787,7 @@
         <v>45865</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>44369.46261574074</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>45230</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43963,7 +43963,7 @@
         <v>45865.67818287037</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44020,7 +44020,7 @@
         <v>45644.36364583333</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44077,7 +44077,7 @@
         <v>45826.50130787037</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>45324.40112268519</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
         <v>45279</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>45826.37920138889</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>45826.50511574074</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
         <v>45637.63881944444</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>45825.40163194444</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44476,7 +44476,7 @@
         <v>45219.44987268518</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>45825.58365740741</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>45825.46516203704</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>45826.49353009259</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44704,7 +44704,7 @@
         <v>44410</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45224</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45869.39628472222</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45205.35776620371</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>44757.40493055555</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44999,7 +44999,7 @@
         <v>45688</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>45688.64506944444</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>45831.5818287037</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>45831</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45237,7 +45237,7 @@
         <v>44361.93059027778</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45294,7 +45294,7 @@
         <v>44603</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>45155</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>45839</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>45839</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45542,7 +45542,7 @@
         <v>45737</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>45737</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45656,7 +45656,7 @@
         <v>45832.47321759259</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>45831.37613425926</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45775,7 +45775,7 @@
         <v>45873</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>45831.36230324074</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45889,7 +45889,7 @@
         <v>44278</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>45146</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         <v>45146</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46060,7 +46060,7 @@
         <v>45831.37420138889</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>44208</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46179,7 +46179,7 @@
         <v>45320.88226851852</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46236,7 +46236,7 @@
         <v>45831.51181712963</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>45764.67251157408</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>45666</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46407,7 +46407,7 @@
         <v>45709.40309027778</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>45308</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>45538.80545138889</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>45875</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>45547.62391203704</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>45547.62475694445</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>45764</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46816,7 +46816,7 @@
         <v>45764.84103009259</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46878,7 +46878,7 @@
         <v>45736.32997685186</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45736.33076388889</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47002,7 +47002,7 @@
         <v>45770.625625</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>44922.50314814815</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>45385.44706018519</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>44124</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47235,7 +47235,7 @@
         <v>45338</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>45338.43268518519</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>44897.42872685185</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>44459.56224537037</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>44951</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47530,7 +47530,7 @@
         <v>44946</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47587,7 +47587,7 @@
         <v>45561.3744212963</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>44160</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>45261</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47763,7 +47763,7 @@
         <v>44552.46184027778</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47820,7 +47820,7 @@
         <v>44595.55912037037</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>44533.35804398148</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47934,7 +47934,7 @@
         <v>45164</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47991,7 +47991,7 @@
         <v>44638.34265046296</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>45230.37582175926</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48110,7 +48110,7 @@
         <v>44089.35689814815</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48172,7 +48172,7 @@
         <v>44887</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>44054</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48286,7 +48286,7 @@
         <v>44468.65578703704</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48343,7 +48343,7 @@
         <v>45428.57578703704</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48400,7 +48400,7 @@
         <v>45398.79873842592</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48457,7 +48457,7 @@
         <v>45204</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48514,7 +48514,7 @@
         <v>45607.60341435186</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48571,7 +48571,7 @@
         <v>45595.77847222222</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48628,7 +48628,7 @@
         <v>45546.60894675926</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>45604.47792824074</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48742,7 +48742,7 @@
         <v>45226.45565972223</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48799,7 +48799,7 @@
         <v>45455</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>45232.72258101852</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48918,7 +48918,7 @@
         <v>45568</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45275.35230324074</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45245.7939699074</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>44711.38688657407</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49151,7 +49151,7 @@
         <v>44994.45623842593</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49208,7 +49208,7 @@
         <v>44902.79445601852</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49265,7 +49265,7 @@
         <v>45428.55520833333</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>45674.38553240741</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45174.34193287037</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45597.34579861111</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>45597.34881944444</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49565,7 +49565,7 @@
         <v>45600.45402777778</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49622,7 +49622,7 @@
         <v>44908</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49684,7 +49684,7 @@
         <v>44697</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49746,7 +49746,7 @@
         <v>45069.69295138889</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49803,7 +49803,7 @@
         <v>45020</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>44260</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>45668.63396990741</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45260.46252314815</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50036,7 +50036,7 @@
         <v>44865.54231481482</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45156.54523148148</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50150,7 +50150,7 @@
         <v>45369.44256944444</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50207,7 +50207,7 @@
         <v>44375</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>45434.56020833334</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50321,7 +50321,7 @@
         <v>45375</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50378,7 +50378,7 @@
         <v>45427.93607638889</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>45225</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50492,7 +50492,7 @@
         <v>45350</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -567,7 +567,7 @@
         <v>45174</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         <v>44112</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44175</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44266</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45313</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45475</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>45604.4624537037</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>45840.46792824074</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45158</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45195</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>44315</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>44455</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>44859</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45450.57783564815</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45517.34768518519</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45404.55137731481</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>45826.4996875</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45747</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>44937</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45604.53089120371</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>45103</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>45604.48800925926</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44833</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44295</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>44375</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>44827</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44207</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>45789.61961805556</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45791.44271990741</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>44998</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>44950</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>44663</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44384</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>44091</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>44550</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>45820.48319444444</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>45825</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>44676</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>45623</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>44160</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>45688.59202546296</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>44858</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>45688.41431712963</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44132</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>45747</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>45335</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>44207</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>44179.52865740741</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>44243</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>44270.56321759259</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44228</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>44155</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>44069</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>44069</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>44089</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>44069</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44267.64171296296</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>44320.42899305555</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>44386</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>44386</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>44865.57608796296</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>44069</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44887.42784722222</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>44887.42950231482</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44307.45770833334</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>44508</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>44175</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>44225</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>44201</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44201</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>44201</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>44285</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>44201</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>44524.32766203704</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>44613.65383101852</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>44483.4240625</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44193</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>44225</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>44202</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>44447</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>44085</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>44487</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44242</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44552.45428240741</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>44536</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>44461.68690972222</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>44510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44574.4577662037</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>44456</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44127</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44734.36189814815</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>44273</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44812.51043981482</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>44321</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44319.33803240741</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44859</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>44176.66133101852</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>44225</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>44229</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>44574.45553240741</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>44165</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44859</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>44265.69087962963</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>44278</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>44676.551875</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>44859</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>44859</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>44749</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>44574.43967592593</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>44602</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>44580</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>44602.57726851852</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>44217</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>44088.78303240741</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>44201</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>44201</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>44859</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>44308</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>44430.93283564815</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>44259</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>44795.48144675926</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>44757.40570601852</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44124</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>44228</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>44225</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>44228</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>44225</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>44887.43138888889</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>44588.6396875</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>44088</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>44505</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>44456</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>44069</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44207</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>44434</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>44375</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>44845</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>44375</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>44270.5584375</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>44364</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>44497</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>44201</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>44552.45563657407</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>44483.66988425926</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>44483.67144675926</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>44375</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>44475</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>44503</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>44510</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44119</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>44376</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>44214</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44069</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10867,7 +10867,7 @@
         <v>44683.46200231482</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>44686</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>44803.35861111111</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>44887.42521990741</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>44607</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>44607</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>44343.88627314815</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>44887.42283564815</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>44887.42663194444</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44711.38366898148</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>44490.74336805556</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44459</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>44074</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>44610</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>44676.56075231481</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>44609</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>44089.35622685185</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>44522.60883101852</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>44531</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>44375</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>44253</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>44371</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>44250</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>44127</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>44795.60174768518</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>44795.60293981482</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44336.39239583333</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>44242</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>44102</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>44328.41473379629</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>44424.57476851852</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>44470</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>44837.43361111111</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>44582</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>44475.66188657407</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>44859</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>44729.65407407407</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>44158</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>44068</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>44788.47552083333</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>44574</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>44175</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>44207</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>44284</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>44705</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>44175</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>44757</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         <v>44344.48678240741</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>44120</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>44420.28219907408</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44120</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44602</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>44466</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>44603</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>44602</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>44073</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>44393</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44285.87041666666</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44524.46141203704</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44592.48909722222</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>44690</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>44721.32116898148</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>44073</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>44601.75174768519</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>44424.57810185185</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>45709.38748842593</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>45709.39251157407</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>44858.49122685185</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>45091</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>45770.62311342593</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>45709.38243055555</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>44276</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>45190.39688657408</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>45338</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>45338</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>44602.51873842593</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>45335.63689814815</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>45341.58440972222</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44285.33586805555</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>44524.66444444445</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>44503.58450231481</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>45349</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>45348</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>45348</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>45165.77501157407</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>45001</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45245.37445601852</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>45775.49840277778</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>45697.97704861111</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>45385.49137731481</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>45041.59671296296</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>45041</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>44400</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45288.46611111111</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>45749.46740740741</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>44308</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>45709.42712962963</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>45506.59847222222</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45082.56950231481</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>44396</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>44496</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45685.55012731482</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>45489.50666666667</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45400</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>45338</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>45338</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45338</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>45639.59918981481</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45537.45255787037</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45335.63466435186</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>45561.37106481481</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45642.46802083333</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>45401.44325231481</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>44757.39927083333</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>44757.40454861111</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>45428.55409722222</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>45428.55619212963</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>45384.42409722223</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>44153</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>45568</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>45568</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>45642.47061342592</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45208.64244212963</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45391.58608796296</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>45391.59185185185</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45600.47440972222</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>45273</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45601</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>45471</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>45516.37174768518</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>45517.38890046296</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>45320</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>44354</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>44833</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>44526</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>44140</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>44140</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45709.33226851852</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>45716.34298611111</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>45279.37215277777</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>45454.73629629629</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45716.34217592593</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>45716.34775462963</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45348.33475694444</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>45400</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>44998</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>45103</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>45181</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>45783.38083333334</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>45428.56533564815</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45428.57266203704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>45607.37846064815</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>45229.49331018519</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>45783.47896990741</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45469.34783564815</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45428.5499537037</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>45428.55199074074</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>45488.46717592593</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45153</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>45692</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>45502.49574074074</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45530.36846064815</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45720.41747685185</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45742</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44430.29293981481</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45476.50758101852</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>44984</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>45786</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45552.65006944445</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45229</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45728.59358796296</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>45604.44618055555</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45389.74396990741</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45791</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>45162</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>45736.32833333333</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45783</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45154.56967592592</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44524</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>44524</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45146</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>45389</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45389</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45590.39090277778</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>45792.81104166667</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45428.53776620371</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45118</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>45355.56142361111</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>45370.64554398148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44153.45842592593</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>45622</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44124</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>45204.42494212963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>45597.34225694444</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>45610.35752314814</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>45604.48289351852</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>44659.58702546296</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>45579</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22393,7 +22393,7 @@
         <v>45338.43309027778</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45749.75060185185</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>44610</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>45474.36921296296</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>45191</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>45720.40681712963</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>45534</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>45800.6135300926</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>45737.65686342592</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>45801.7406712963</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>45804</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>45804.49788194444</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>45140</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>44074</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>45804.40983796296</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>45801.72324074074</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>45642.47158564815</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>45597.38799768518</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>45597.39101851852</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>45801.7155324074</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>44844</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>45804</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>44858</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>45801.73608796296</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45764</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>45372.49736111111</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>45737</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>45743.59358796296</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45440.6484375</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>45567.53571759259</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>45440.63173611111</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>45805.59104166667</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24247,7 +24247,7 @@
         <v>45764</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45169.38462962963</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45218</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>45729.67947916667</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45386.35322916666</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45372.49458333333</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>44593</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>45196.47457175926</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>45404.56375</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45140</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45547.6262037037</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45807.45759259259</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45279.61047453704</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>44790</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>45223</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>44566</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45664.57111111111</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>45057</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>45117</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>45211</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45154.57079861111</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>45688.58667824074</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>45107.61413194444</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25578,7 +25578,7 @@
         <v>45195</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>45807.45905092593</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>45807.46021990741</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>45506.60435185185</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>44073</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25863,7 +25863,7 @@
         <v>44069</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>44438</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45757</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>45544.33987268519</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26101,7 +26101,7 @@
         <v>45184.46447916667</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45428.54791666667</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>45757.34662037037</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>45428.53717592593</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>45428.54854166666</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>45428.54914351852</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45211</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>45811.59519675926</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>45428.55339120371</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>45428.56928240741</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>45428.58675925926</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>45085</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>45544.36982638889</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>45709.40560185185</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>45459.71376157407</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>44105</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>45709.32859953704</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>45709.40761574074</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>44167</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>45336.92125</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>45153</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45854.62081018519</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45174</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         <v>45428.54546296296</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45230</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>45709.39714120371</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>45428.56197916667</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45709.39515046297</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45709.40043981482</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45089</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45777.45011574074</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>45540.56981481481</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>44592.50912037037</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>45688.43215277778</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45818</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45674.38413194445</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>44757</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>44140</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28317,7 +28317,7 @@
         <v>45049</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>44599</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>45476</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>45204</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45769.41568287037</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>44152</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>45366</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>44154</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>45819.32747685185</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>45819.46775462963</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45861.42532407407</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>45861.43393518519</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>45824.48737268519</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>45865.66577546296</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45865</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>45155</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>45865.67818287037</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45644.36364583333</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45243</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>45677.70096064815</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>45826.50130787037</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>45826.37920138889</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>45826.50511574074</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45825.40163194444</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>44154</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>45098.44975694444</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>45749.46461805556</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>45435.77655092593</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>45825.58365740741</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>45825.46516203704</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>45826.49353009259</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>45604.56101851852</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30156,7 +30156,7 @@
         <v>45604.56190972222</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>45604.56958333333</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>44915.41944444444</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30337,7 +30337,7 @@
         <v>45869.39628472222</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>45552.6449537037</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>45552</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>44154</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30565,7 +30565,7 @@
         <v>45336</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>45831.5818287037</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>45747</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>45747.61878472222</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30803,7 +30803,7 @@
         <v>45747</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>45831</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>44858</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30974,7 +30974,7 @@
         <v>45113.36457175926</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>45013</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>45755.41075231481</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         <v>45727.61247685185</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>45832.47321759259</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31264,7 +31264,7 @@
         <v>45831.37613425926</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>44757.40103009259</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>44757.40538194445</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>45873</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>45831.36230324074</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>45831.37420138889</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>45230</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>44942</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45734</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31792,7 +31792,7 @@
         <v>45692</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31849,7 +31849,7 @@
         <v>45351</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>45754.55663194445</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31963,7 +31963,7 @@
         <v>45233</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>45264.6516087963</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>45211.81873842593</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>44939</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>44939</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>45831.51181712963</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>45146</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>45649.6427662037</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44942.60704861111</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         <v>45875</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32533,7 +32533,7 @@
         <v>45324.40112268519</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>45320.58873842593</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32647,7 +32647,7 @@
         <v>45279</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>45835.37094907407</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32761,7 +32761,7 @@
         <v>44603</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32818,7 +32818,7 @@
         <v>45838.67675925926</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>45838.6196875</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>44592.72989583333</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32994,7 +32994,7 @@
         <v>45688.58755787037</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>45688.63835648148</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33118,7 +33118,7 @@
         <v>45408.61435185185</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>44278</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>45835.48375</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33289,7 +33289,7 @@
         <v>45146</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>45146</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>44208</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>45320.88226851852</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45839</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>45839</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>45881.4566087963</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45338.43358796297</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33775,7 +33775,7 @@
         <v>45338</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>45338</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>45295</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33961,7 +33961,7 @@
         <v>45604.5687962963</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>45839</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>44985</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45840.479375</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34194,7 +34194,7 @@
         <v>45877</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>45881</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45838.37465277778</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>45579</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>45839</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>44250</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>45840.66209490741</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>45404</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>45764.67251157408</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>45840.49215277778</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>45709.40309027778</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34831,7 +34831,7 @@
         <v>45308</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34888,7 +34888,7 @@
         <v>45881.55119212963</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>45538.80545138889</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45839.58087962963</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>45547.62391203704</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>45547.62475694445</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45636.96761574074</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>45708.27960648148</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35287,7 +35287,7 @@
         <v>45702.36793981482</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35344,7 +35344,7 @@
         <v>45722.40604166667</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35401,7 +35401,7 @@
         <v>45230</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>45764</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>45764.84103009259</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         <v>45666</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>45736.32997685186</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35706,7 +35706,7 @@
         <v>45736.33076388889</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>45841.73791666667</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>45770.625625</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>45389.73820601852</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35939,7 +35939,7 @@
         <v>44922.50314814815</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>45597.35365740741</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36058,7 +36058,7 @@
         <v>45842.48019675926</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>45841.74796296296</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36172,7 +36172,7 @@
         <v>45763.68868055556</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36234,7 +36234,7 @@
         <v>45842.47915509259</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36291,7 +36291,7 @@
         <v>45763.69137731481</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>45842.55467592592</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>45223.60331018519</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>45385.44706018519</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36529,7 +36529,7 @@
         <v>44945.39559027777</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>44124</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>45063.27048611111</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>45338</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>45338.43268518519</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>45597.3521412037</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36886,7 +36886,7 @@
         <v>45770</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36943,7 +36943,7 @@
         <v>45770</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37000,7 +37000,7 @@
         <v>45770</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>45737.65869212963</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>44897.42872685185</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37171,7 +37171,7 @@
         <v>44459.56224537037</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37228,7 +37228,7 @@
         <v>44951</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37285,7 +37285,7 @@
         <v>44946</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37342,7 +37342,7 @@
         <v>45561.3744212963</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>44160</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>44229</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>45261</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37575,7 +37575,7 @@
         <v>45278.39707175926</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>44552.46184027778</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>45009</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>44923</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37803,7 +37803,7 @@
         <v>45629.38060185185</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>44595.55912037037</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>44533.35804398148</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>45164</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38036,7 +38036,7 @@
         <v>45273.615</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38093,7 +38093,7 @@
         <v>44638.34265046296</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38150,7 +38150,7 @@
         <v>45093</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38207,7 +38207,7 @@
         <v>45230.37582175926</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>45604.56769675926</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>45604.48214120371</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>45317</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>44984</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38512,7 +38512,7 @@
         <v>44984</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38569,7 +38569,7 @@
         <v>44971.75834490741</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38626,7 +38626,7 @@
         <v>45075.50622685185</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38683,7 +38683,7 @@
         <v>44089.35689814815</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38745,7 +38745,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38802,7 +38802,7 @@
         <v>44468.65578703704</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>45428.57578703704</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>44496.58679398148</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45398.79873842592</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39030,7 +39030,7 @@
         <v>44971.76626157408</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39087,7 +39087,7 @@
         <v>45204</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>45354.72975694444</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>45460.82011574074</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>45041</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>45607.60341435186</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>45595.77847222222</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>45546.60894675926</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>45604.47792824074</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44074</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>45226.45565972223</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>45547.62553240741</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>44523.4103587963</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>45455</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39833,7 +39833,7 @@
         <v>45475</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39890,7 +39890,7 @@
         <v>45232.72258101852</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39947,7 +39947,7 @@
         <v>45568</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>45275.35230324074</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>45245.7939699074</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>44711.38688657407</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>45163.72633101852</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>45181</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44994.45623842593</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>45357.39202546296</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44902.79445601852</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>45428.55520833333</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45674.38553240741</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>45615</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40641,7 +40641,7 @@
         <v>45174.34193287037</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
         <v>45597.34579861111</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>45597.34881944444</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>45600.45402777778</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>44908</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40941,7 +40941,7 @@
         <v>44697</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>45069.69295138889</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>45604.26549768518</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>45597.38953703704</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>45020</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>44260</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>45668.63396990741</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>45118</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>45693</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41469,7 +41469,7 @@
         <v>45693</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>45260.46252314815</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41583,7 +41583,7 @@
         <v>44865.54231481482</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>45156.54523148148</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41697,7 +41697,7 @@
         <v>45369.44256944444</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>45692</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41816,7 +41816,7 @@
         <v>44375</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41873,7 +41873,7 @@
         <v>45201.50586805555</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41930,7 +41930,7 @@
         <v>44406</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>45028</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45434.56020833334</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42106,7 +42106,7 @@
         <v>45375</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>45427.93607638889</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42220,7 +42220,7 @@
         <v>45225</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42277,7 +42277,7 @@
         <v>45692</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>44064</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42391,7 +42391,7 @@
         <v>44924.77766203704</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42448,7 +42448,7 @@
         <v>45350</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42505,7 +42505,7 @@
         <v>44369.46261574074</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42562,7 +42562,7 @@
         <v>44998.55319444444</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>45637.63881944444</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>45428.55946759259</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42753,7 +42753,7 @@
         <v>45428.5703587963</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42810,7 +42810,7 @@
         <v>45428.57371527778</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42867,7 +42867,7 @@
         <v>45219.44987268518</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>44410</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42981,7 +42981,7 @@
         <v>45224</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43043,7 +43043,7 @@
         <v>45691.56284722222</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43100,7 +43100,7 @@
         <v>45454.73359953704</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43157,7 +43157,7 @@
         <v>45118.36900462963</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>45205.35776620371</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43271,7 +43271,7 @@
         <v>44757.40493055555</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>45688</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>45688.64506944444</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>45364.57331018519</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>44361.93059027778</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>44593.63554398148</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>45155</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>45737</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45737</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45105.48627314815</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45273.60899305555</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43913,7 +43913,7 @@
         <v>45273</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>45622</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44027,7 +44027,7 @@
         <v>45233</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44084,7 +44084,7 @@
         <v>45755</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>45114.65185185185</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44198,7 +44198,7 @@
         <v>45761.93627314815</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44260,7 +44260,7 @@
         <v>45730</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45761</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>45164</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>45745.75537037037</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44493,7 +44493,7 @@
         <v>45749</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44555,7 +44555,7 @@
         <v>45698</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45028</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>45244.86136574074</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>44097</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>44160</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44845,7 +44845,7 @@
         <v>45643.43193287037</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44902,7 +44902,7 @@
         <v>45615</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44959,7 +44959,7 @@
         <v>44165</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45016,7 +45016,7 @@
         <v>45105.47802083333</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>45244.67376157407</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>45755.42104166667</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>45749</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>45764</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45311,7 +45311,7 @@
         <v>45459.71949074074</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>44375</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>44881.54231481482</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45482,7 +45482,7 @@
         <v>45005</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>44924.79619212963</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45596,7 +45596,7 @@
         <v>45012</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45653,7 +45653,7 @@
         <v>44098</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45710,7 +45710,7 @@
         <v>45098</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
         <v>45525.6055787037</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45824,7 +45824,7 @@
         <v>45590</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45881,7 +45881,7 @@
         <v>45716.33921296296</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45943,7 +45943,7 @@
         <v>45112.3402199074</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46000,7 +46000,7 @@
         <v>45604.56427083333</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>45604.56517361111</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45761.93880787037</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>45604.56623842593</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45190.47119212963</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>45670.3792824074</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45708.35037037037</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>44844.67142361111</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>45764</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>45692.42515046296</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>44392.68070601852</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>45204</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46709,7 +46709,7 @@
         <v>45706.36192129629</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>45085</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>45583.40994212963</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>44327</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45229.53780092593</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45091</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45755</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
         <v>44882</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>45085</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>44971.76994212963</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>45705.35732638889</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47341,7 +47341,7 @@
         <v>45749.74931712963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47398,7 +47398,7 @@
         <v>45716.34958333334</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47460,7 +47460,7 @@
         <v>45082</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47517,7 +47517,7 @@
         <v>44468.68219907407</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47574,7 +47574,7 @@
         <v>44446</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47631,7 +47631,7 @@
         <v>44994.45271990741</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>45660</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47745,7 +47745,7 @@
         <v>44610</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47802,7 +47802,7 @@
         <v>45149</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47859,7 +47859,7 @@
         <v>44942.49850694444</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47916,7 +47916,7 @@
         <v>44162</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>45181</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45407.5766087963</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45385</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48154,7 +48154,7 @@
         <v>44937</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>44937.46436342593</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48268,7 +48268,7 @@
         <v>45698</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>44789.46129629629</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>45219.79758101852</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>45737.65526620371</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45085.53467592593</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45401.690625</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48615,7 +48615,7 @@
         <v>44154</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>44917.58131944444</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48729,7 +48729,7 @@
         <v>45427.9417824074</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48786,7 +48786,7 @@
         <v>45729.35393518519</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48843,7 +48843,7 @@
         <v>45428.57160879629</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48900,7 +48900,7 @@
         <v>45428.57215277778</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48957,7 +48957,7 @@
         <v>45547.62819444444</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49014,7 +49014,7 @@
         <v>45338</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49076,7 +49076,7 @@
         <v>45338</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49138,7 +49138,7 @@
         <v>45547.62703703704</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49195,7 +49195,7 @@
         <v>45716.3528125</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49257,7 +49257,7 @@
         <v>45019</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49314,7 +49314,7 @@
         <v>44838</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49371,7 +49371,7 @@
         <v>45093.34891203704</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49428,7 +49428,7 @@
         <v>45596.54981481482</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>45679.50844907408</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49542,7 +49542,7 @@
         <v>45642</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49599,7 +49599,7 @@
         <v>45714.37306712963</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49656,7 +49656,7 @@
         <v>45575.84530092592</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49713,7 +49713,7 @@
         <v>45716.35056712963</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49775,7 +49775,7 @@
         <v>45057</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49832,7 +49832,7 @@
         <v>45590.38761574074</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>45154.65458333334</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49946,7 +49946,7 @@
         <v>45728</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50003,7 +50003,7 @@
         <v>45722.96171296296</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50060,7 +50060,7 @@
         <v>45369.42203703704</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50117,7 +50117,7 @@
         <v>45434.44790509259</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50174,7 +50174,7 @@
         <v>45709.42873842592</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50236,7 +50236,7 @@
         <v>45229.58863425926</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50293,7 +50293,7 @@
         <v>45737</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50350,7 +50350,7 @@
         <v>44734.3744212963</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50407,7 +50407,7 @@
         <v>44734.37710648148</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -567,7 +567,7 @@
         <v>45174</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         <v>44112</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44175</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44266</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45313</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45475</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>45604.4624537037</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>45840.46792824074</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45158</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45195</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>44315</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>44455</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>44859</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45450.57783564815</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45517.34768518519</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45404.55137731481</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>45826.4996875</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45747</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>44937</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45604.53089120371</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>45103</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>45604.48800925926</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44833</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44295</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>44375</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>44827</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44207</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>45789.61961805556</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45791.44271990741</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>44998</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>44950</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>44663</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44384</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>44091</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>44550</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>45820.48319444444</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>45825</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>44676</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>45623</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>44160</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>45688.59202546296</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>44858</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>45688.41431712963</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44132</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>45747</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>45335</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>44207</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>44179.52865740741</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>44243</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>44270.56321759259</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44228</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>44155</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>44069</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>44069</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>44089</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>44069</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44267.64171296296</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>44320.42899305555</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>44386</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>44386</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>44865.57608796296</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>44069</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44887.42784722222</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>44887.42950231482</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44307.45770833334</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>44508</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>44175</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>44225</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>44201</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44201</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>44201</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>44285</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>44201</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>44524.32766203704</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>44613.65383101852</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>44483.4240625</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44193</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>44225</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>44202</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>44447</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>44085</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>44487</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44242</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44552.45428240741</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>44536</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>44461.68690972222</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>44510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44574.4577662037</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>44456</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44127</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44734.36189814815</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>44273</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44812.51043981482</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>44321</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44319.33803240741</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44859</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>44176.66133101852</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>44225</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>44229</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>44574.45553240741</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>44165</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44859</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>44265.69087962963</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>44278</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>44676.551875</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>44859</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>44859</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>44749</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>44574.43967592593</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>44602</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>44580</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>44602.57726851852</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>44217</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>44088.78303240741</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>44201</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>44201</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>44859</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>44308</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>44430.93283564815</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>44259</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>44795.48144675926</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>44757.40570601852</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44124</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>44228</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>44225</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>44228</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>44225</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>44887.43138888889</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>44588.6396875</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>44088</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>44505</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>44456</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>44069</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44207</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>44434</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>44375</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>44845</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>44375</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>44270.5584375</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>44364</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>44497</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>44201</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>44552.45563657407</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>44483.66988425926</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>44483.67144675926</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>44375</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>44475</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>44503</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>44510</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44119</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>44376</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>44214</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44069</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10867,7 +10867,7 @@
         <v>44683.46200231482</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>44686</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>44803.35861111111</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>44887.42521990741</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>44607</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>44607</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>44343.88627314815</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>44887.42283564815</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>44887.42663194444</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44711.38366898148</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>44490.74336805556</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44459</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>44074</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>44610</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>44676.56075231481</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>44609</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>44089.35622685185</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>44522.60883101852</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>44531</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>44375</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>44253</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>44371</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>44250</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>44127</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>44795.60174768518</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>44795.60293981482</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44336.39239583333</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>44242</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>44102</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>44328.41473379629</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>44424.57476851852</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>44470</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>44837.43361111111</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>44582</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>44475.66188657407</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>44859</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>44729.65407407407</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>44158</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>44068</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>44788.47552083333</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>44574</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>44175</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>44207</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>44284</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>44705</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>44175</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>44757</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         <v>44344.48678240741</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>44120</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>44420.28219907408</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44120</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44602</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>44466</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>44603</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>44602</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>44073</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>44393</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44285.87041666666</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44524.46141203704</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44592.48909722222</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>44690</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>44721.32116898148</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>44073</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>44601.75174768519</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>44424.57810185185</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>45709.38748842593</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>45709.39251157407</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>44858.49122685185</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>45091</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>45770.62311342593</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>45709.38243055555</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>44276</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>45190.39688657408</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>45338</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>45338</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>44602.51873842593</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>45335.63689814815</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>45341.58440972222</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44285.33586805555</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>44524.66444444445</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>44503.58450231481</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>45349</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>45348</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>45348</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>45165.77501157407</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>45001</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45245.37445601852</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>45775.49840277778</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>45697.97704861111</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>45385.49137731481</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>45041.59671296296</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>45041</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>44400</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45288.46611111111</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>45749.46740740741</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>44308</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>45709.42712962963</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>45506.59847222222</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45082.56950231481</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>44396</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>44496</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45685.55012731482</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>45489.50666666667</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45400</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>45338</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>45338</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45338</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>45639.59918981481</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45537.45255787037</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45335.63466435186</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>45561.37106481481</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45642.46802083333</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>45401.44325231481</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>44757.39927083333</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>44757.40454861111</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>45428.55409722222</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>45428.55619212963</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>45384.42409722223</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>44153</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>45568</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>45568</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>45642.47061342592</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45208.64244212963</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45391.58608796296</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>45391.59185185185</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45600.47440972222</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>45273</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45601</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>45471</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>45516.37174768518</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>45517.38890046296</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>45320</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>44354</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>44833</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>44526</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>44140</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>44140</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45709.33226851852</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>45716.34298611111</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>45279.37215277777</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>45454.73629629629</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45716.34217592593</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>45716.34775462963</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45348.33475694444</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>45400</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>44998</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>45103</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>45181</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>45783.38083333334</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>45428.56533564815</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45428.57266203704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>45607.37846064815</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>45229.49331018519</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>45783.47896990741</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45469.34783564815</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45428.5499537037</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>45428.55199074074</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>45488.46717592593</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45153</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>45692</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>45502.49574074074</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45530.36846064815</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45720.41747685185</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45742</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44430.29293981481</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45476.50758101852</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>44984</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>45786</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45552.65006944445</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45229</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45728.59358796296</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>45604.44618055555</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45389.74396990741</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45791</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>45162</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>45736.32833333333</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45783</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45154.56967592592</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44524</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>44524</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45146</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>45389</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45389</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45590.39090277778</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>45792.81104166667</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45428.53776620371</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45118</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>45355.56142361111</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>45370.64554398148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44153.45842592593</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>45622</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44124</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>45204.42494212963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>45597.34225694444</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>45610.35752314814</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>45604.48289351852</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>44659.58702546296</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>45579</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22393,7 +22393,7 @@
         <v>45338.43309027778</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45749.75060185185</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>44610</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>45474.36921296296</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>45191</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>45720.40681712963</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>45534</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>45800.6135300926</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>45737.65686342592</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>45801.7406712963</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>45804</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>45804.49788194444</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>45140</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>44074</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>45804.40983796296</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>45801.72324074074</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>45642.47158564815</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>45597.38799768518</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>45597.39101851852</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>45801.7155324074</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>44844</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>45804</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>44858</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>45801.73608796296</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45764</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>45372.49736111111</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>45737</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>45743.59358796296</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45440.6484375</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>45567.53571759259</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>45440.63173611111</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>45805.59104166667</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24247,7 +24247,7 @@
         <v>45764</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45169.38462962963</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45218</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>45729.67947916667</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45386.35322916666</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45372.49458333333</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>44593</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>45196.47457175926</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>45404.56375</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45140</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45547.6262037037</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45807.45759259259</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45279.61047453704</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>44790</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>45223</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>44566</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45664.57111111111</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>45057</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>45117</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>45211</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45154.57079861111</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>45688.58667824074</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>45107.61413194444</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25578,7 +25578,7 @@
         <v>45195</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>45807.45905092593</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>45807.46021990741</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>45506.60435185185</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>44073</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25863,7 +25863,7 @@
         <v>44069</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>44438</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45757</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>45544.33987268519</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26101,7 +26101,7 @@
         <v>45184.46447916667</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45428.54791666667</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>45757.34662037037</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>45428.53717592593</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>45428.54854166666</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>45428.54914351852</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45211</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>45811.59519675926</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>45428.55339120371</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>45428.56928240741</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>45428.58675925926</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>45085</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>45544.36982638889</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>45709.40560185185</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>45459.71376157407</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>44105</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>45709.32859953704</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>45709.40761574074</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>44167</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>45336.92125</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>45153</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45854.62081018519</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45174</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         <v>45428.54546296296</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45230</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>45709.39714120371</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>45428.56197916667</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45709.39515046297</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45709.40043981482</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45089</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45777.45011574074</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>45540.56981481481</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>44592.50912037037</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>45688.43215277778</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45818</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45674.38413194445</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>44757</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>44140</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28317,7 +28317,7 @@
         <v>45049</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>44599</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>45476</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>45204</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45769.41568287037</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>44152</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>45366</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>44154</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>45819.32747685185</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>45819.46775462963</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45861.42532407407</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>45861.43393518519</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>45824.48737268519</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>45865.66577546296</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45865</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>45155</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>45865.67818287037</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45644.36364583333</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45243</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>45677.70096064815</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>45826.50130787037</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>45826.37920138889</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>45826.50511574074</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45825.40163194444</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>44154</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>45098.44975694444</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>45749.46461805556</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>45435.77655092593</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>45825.58365740741</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>45825.46516203704</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>45826.49353009259</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>45604.56101851852</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30156,7 +30156,7 @@
         <v>45604.56190972222</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>45604.56958333333</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>44915.41944444444</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30337,7 +30337,7 @@
         <v>45869.39628472222</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>45552.6449537037</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>45552</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>44154</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30565,7 +30565,7 @@
         <v>45336</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>45831.5818287037</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>45747</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>45747.61878472222</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30803,7 +30803,7 @@
         <v>45747</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>45831</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>44858</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30974,7 +30974,7 @@
         <v>45113.36457175926</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>45013</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>45755.41075231481</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         <v>45727.61247685185</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>45832.47321759259</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31264,7 +31264,7 @@
         <v>45831.37613425926</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>44757.40103009259</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>44757.40538194445</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>45873</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>45831.36230324074</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>45831.37420138889</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>45230</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>44942</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45734</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31792,7 +31792,7 @@
         <v>45692</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31849,7 +31849,7 @@
         <v>45351</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>45754.55663194445</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31963,7 +31963,7 @@
         <v>45233</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>45264.6516087963</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>45211.81873842593</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>44939</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>44939</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>45831.51181712963</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>45146</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>45649.6427662037</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44942.60704861111</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         <v>45875</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32533,7 +32533,7 @@
         <v>45324.40112268519</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>45320.58873842593</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32647,7 +32647,7 @@
         <v>45279</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>45835.37094907407</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32761,7 +32761,7 @@
         <v>44603</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32818,7 +32818,7 @@
         <v>45838.67675925926</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>45838.6196875</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>44592.72989583333</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32994,7 +32994,7 @@
         <v>45688.58755787037</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>45688.63835648148</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33118,7 +33118,7 @@
         <v>45408.61435185185</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>44278</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>45835.48375</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33289,7 +33289,7 @@
         <v>45146</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>45146</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>44208</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>45320.88226851852</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45839</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>45839</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>45881.4566087963</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45338.43358796297</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33775,7 +33775,7 @@
         <v>45338</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>45338</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>45295</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33961,7 +33961,7 @@
         <v>45604.5687962963</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>45839</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>44985</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45840.479375</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34194,7 +34194,7 @@
         <v>45877</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>45881</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45838.37465277778</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>45579</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>45839</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>44250</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>45840.66209490741</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>45404</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>45764.67251157408</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>45840.49215277778</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>45709.40309027778</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34831,7 +34831,7 @@
         <v>45308</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34888,7 +34888,7 @@
         <v>45881.55119212963</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>45538.80545138889</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45839.58087962963</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>45547.62391203704</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>45547.62475694445</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45636.96761574074</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>45708.27960648148</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35287,7 +35287,7 @@
         <v>45702.36793981482</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35344,7 +35344,7 @@
         <v>45722.40604166667</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35401,7 +35401,7 @@
         <v>45230</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>45764</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>45764.84103009259</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         <v>45666</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>45736.32997685186</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35706,7 +35706,7 @@
         <v>45736.33076388889</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>45841.73791666667</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>45770.625625</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>45389.73820601852</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35939,7 +35939,7 @@
         <v>44922.50314814815</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>45597.35365740741</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36058,7 +36058,7 @@
         <v>45842.48019675926</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>45841.74796296296</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36172,7 +36172,7 @@
         <v>45763.68868055556</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36234,7 +36234,7 @@
         <v>45842.47915509259</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36291,7 +36291,7 @@
         <v>45763.69137731481</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>45842.55467592592</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>45223.60331018519</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>45385.44706018519</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36529,7 +36529,7 @@
         <v>44945.39559027777</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>44124</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>45063.27048611111</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>45338</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>45338.43268518519</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>45597.3521412037</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36886,7 +36886,7 @@
         <v>45770</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36943,7 +36943,7 @@
         <v>45770</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37000,7 +37000,7 @@
         <v>45770</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>45737.65869212963</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>44897.42872685185</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37171,7 +37171,7 @@
         <v>44459.56224537037</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37228,7 +37228,7 @@
         <v>44951</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37285,7 +37285,7 @@
         <v>44946</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37342,7 +37342,7 @@
         <v>45561.3744212963</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>44160</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>44229</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>45261</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37575,7 +37575,7 @@
         <v>45278.39707175926</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>44552.46184027778</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>45009</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>44923</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37803,7 +37803,7 @@
         <v>45629.38060185185</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>44595.55912037037</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>44533.35804398148</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>45164</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38036,7 +38036,7 @@
         <v>45273.615</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38093,7 +38093,7 @@
         <v>44638.34265046296</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38150,7 +38150,7 @@
         <v>45093</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38207,7 +38207,7 @@
         <v>45230.37582175926</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>45604.56769675926</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>45604.48214120371</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>45317</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>44984</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38512,7 +38512,7 @@
         <v>44984</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38569,7 +38569,7 @@
         <v>44971.75834490741</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38626,7 +38626,7 @@
         <v>45075.50622685185</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38683,7 +38683,7 @@
         <v>44089.35689814815</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38745,7 +38745,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38802,7 +38802,7 @@
         <v>44468.65578703704</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>45428.57578703704</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>44496.58679398148</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45398.79873842592</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39030,7 +39030,7 @@
         <v>44971.76626157408</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39087,7 +39087,7 @@
         <v>45204</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>45354.72975694444</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>45460.82011574074</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>45041</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>45607.60341435186</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>45595.77847222222</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>45546.60894675926</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>45604.47792824074</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44074</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>45226.45565972223</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>45547.62553240741</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>44523.4103587963</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>45455</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39833,7 +39833,7 @@
         <v>45475</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39890,7 +39890,7 @@
         <v>45232.72258101852</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39947,7 +39947,7 @@
         <v>45568</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>45275.35230324074</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>45245.7939699074</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>44711.38688657407</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>45163.72633101852</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>45181</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44994.45623842593</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>45357.39202546296</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44902.79445601852</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>45428.55520833333</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45674.38553240741</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>45615</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40641,7 +40641,7 @@
         <v>45174.34193287037</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
         <v>45597.34579861111</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>45597.34881944444</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>45600.45402777778</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>44908</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40941,7 +40941,7 @@
         <v>44697</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>45069.69295138889</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>45604.26549768518</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>45597.38953703704</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>45020</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>44260</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>45668.63396990741</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>45118</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>45693</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41469,7 +41469,7 @@
         <v>45693</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>45260.46252314815</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41583,7 +41583,7 @@
         <v>44865.54231481482</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>45156.54523148148</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41697,7 +41697,7 @@
         <v>45369.44256944444</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>45692</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41816,7 +41816,7 @@
         <v>44375</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41873,7 +41873,7 @@
         <v>45201.50586805555</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41930,7 +41930,7 @@
         <v>44406</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>45028</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45434.56020833334</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42106,7 +42106,7 @@
         <v>45375</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>45427.93607638889</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42220,7 +42220,7 @@
         <v>45225</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42277,7 +42277,7 @@
         <v>45692</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>44064</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42391,7 +42391,7 @@
         <v>44924.77766203704</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42448,7 +42448,7 @@
         <v>45350</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42505,7 +42505,7 @@
         <v>44369.46261574074</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42562,7 +42562,7 @@
         <v>44998.55319444444</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>45637.63881944444</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>45428.55946759259</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42753,7 +42753,7 @@
         <v>45428.5703587963</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42810,7 +42810,7 @@
         <v>45428.57371527778</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42867,7 +42867,7 @@
         <v>45219.44987268518</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>44410</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42981,7 +42981,7 @@
         <v>45224</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43043,7 +43043,7 @@
         <v>45691.56284722222</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43100,7 +43100,7 @@
         <v>45454.73359953704</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43157,7 +43157,7 @@
         <v>45118.36900462963</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>45205.35776620371</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43271,7 +43271,7 @@
         <v>44757.40493055555</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>45688</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>45688.64506944444</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>45364.57331018519</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>44361.93059027778</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>44593.63554398148</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>45155</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>45737</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45737</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45105.48627314815</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45273.60899305555</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43913,7 +43913,7 @@
         <v>45273</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>45622</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44027,7 +44027,7 @@
         <v>45233</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44084,7 +44084,7 @@
         <v>45755</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>45114.65185185185</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44198,7 +44198,7 @@
         <v>45761.93627314815</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44260,7 +44260,7 @@
         <v>45730</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45761</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>45164</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>45745.75537037037</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44493,7 +44493,7 @@
         <v>45749</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44555,7 +44555,7 @@
         <v>45698</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45028</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>45244.86136574074</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>44097</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>44160</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44845,7 +44845,7 @@
         <v>45643.43193287037</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44902,7 +44902,7 @@
         <v>45615</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44959,7 +44959,7 @@
         <v>44165</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45016,7 +45016,7 @@
         <v>45105.47802083333</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>45244.67376157407</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>45755.42104166667</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>45749</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>45764</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45311,7 +45311,7 @@
         <v>45459.71949074074</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>44375</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>44881.54231481482</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45482,7 +45482,7 @@
         <v>45005</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>44924.79619212963</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45596,7 +45596,7 @@
         <v>45012</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45653,7 +45653,7 @@
         <v>44098</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45710,7 +45710,7 @@
         <v>45098</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
         <v>45525.6055787037</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45824,7 +45824,7 @@
         <v>45590</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45881,7 +45881,7 @@
         <v>45716.33921296296</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45943,7 +45943,7 @@
         <v>45112.3402199074</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46000,7 +46000,7 @@
         <v>45604.56427083333</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>45604.56517361111</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45761.93880787037</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>45604.56623842593</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45190.47119212963</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>45670.3792824074</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45708.35037037037</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>44844.67142361111</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>45764</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>45692.42515046296</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>44392.68070601852</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>45204</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46709,7 +46709,7 @@
         <v>45706.36192129629</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>45085</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>45583.40994212963</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>44327</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45229.53780092593</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45091</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45755</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
         <v>44882</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>45085</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>44971.76994212963</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>45705.35732638889</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47341,7 +47341,7 @@
         <v>45749.74931712963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47398,7 +47398,7 @@
         <v>45716.34958333334</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47460,7 +47460,7 @@
         <v>45082</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47517,7 +47517,7 @@
         <v>44468.68219907407</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47574,7 +47574,7 @@
         <v>44446</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47631,7 +47631,7 @@
         <v>44994.45271990741</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>45660</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47745,7 +47745,7 @@
         <v>44610</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47802,7 +47802,7 @@
         <v>45149</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47859,7 +47859,7 @@
         <v>44942.49850694444</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47916,7 +47916,7 @@
         <v>44162</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>45181</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45407.5766087963</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45385</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48154,7 +48154,7 @@
         <v>44937</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>44937.46436342593</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48268,7 +48268,7 @@
         <v>45698</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>44789.46129629629</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>45219.79758101852</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>45737.65526620371</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45085.53467592593</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45401.690625</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48615,7 +48615,7 @@
         <v>44154</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>44917.58131944444</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48729,7 +48729,7 @@
         <v>45427.9417824074</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48786,7 +48786,7 @@
         <v>45729.35393518519</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48843,7 +48843,7 @@
         <v>45428.57160879629</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48900,7 +48900,7 @@
         <v>45428.57215277778</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48957,7 +48957,7 @@
         <v>45547.62819444444</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49014,7 +49014,7 @@
         <v>45338</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49076,7 +49076,7 @@
         <v>45338</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49138,7 +49138,7 @@
         <v>45547.62703703704</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49195,7 +49195,7 @@
         <v>45716.3528125</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49257,7 +49257,7 @@
         <v>45019</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49314,7 +49314,7 @@
         <v>44838</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49371,7 +49371,7 @@
         <v>45093.34891203704</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49428,7 +49428,7 @@
         <v>45596.54981481482</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>45679.50844907408</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49542,7 +49542,7 @@
         <v>45642</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49599,7 +49599,7 @@
         <v>45714.37306712963</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49656,7 +49656,7 @@
         <v>45575.84530092592</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49713,7 +49713,7 @@
         <v>45716.35056712963</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49775,7 +49775,7 @@
         <v>45057</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49832,7 +49832,7 @@
         <v>45590.38761574074</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>45154.65458333334</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49946,7 +49946,7 @@
         <v>45728</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50003,7 +50003,7 @@
         <v>45722.96171296296</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50060,7 +50060,7 @@
         <v>45369.42203703704</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50117,7 +50117,7 @@
         <v>45434.44790509259</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50174,7 +50174,7 @@
         <v>45709.42873842592</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50236,7 +50236,7 @@
         <v>45229.58863425926</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50293,7 +50293,7 @@
         <v>45737</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50350,7 +50350,7 @@
         <v>44734.3744212963</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50407,7 +50407,7 @@
         <v>44734.37710648148</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -567,7 +567,7 @@
         <v>45174</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         <v>44112</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44175</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44266</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45475</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45313</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>45195</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45158</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>45840.46792824074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45604.4624537037</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>44315</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>44455</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>44859</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>44833</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>45604.53089120371</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45517.34768518519</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>45450.57783564815</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>45404.55137731481</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45604.48800925926</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>45826.4996875</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>44937</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45889</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>45103</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>44295</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44375</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>44827</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44207</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>44550</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45335</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>44998</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>44160</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>45789.61961805556</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45791.44271990741</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>44858</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>45688.59202546296</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>44676</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45623</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>44663</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>44132</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>44384</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>45820.48319444444</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>45825</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44091</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>44950</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>45688.41431712963</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>44207</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>44179.52865740741</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44243</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44270.56321759259</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>44228</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44069</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>44069</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>44069</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>44155</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>44089</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44267.64171296296</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>44320.42899305555</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>44386</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>44386</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>44865.57608796296</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>44069</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>44887.42784722222</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>44887.42950231482</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>44307.45770833334</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>44508</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>44175</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44225</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>44201</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>44201</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>44201</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>44285</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44201</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>44613.65383101852</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44483.4240625</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44524.32766203704</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44225</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44193</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44447</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44085</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44202</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>44242</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>44552.45428240741</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44487</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44536</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44574.4577662037</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44461.68690972222</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44456</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>44127</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>44812.51043981482</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>44273</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>44321</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>44319.33803240741</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>44734.36189814815</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>44859</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>44176.66133101852</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44225</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>44229</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44574.45553240741</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>44165</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44859</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>44265.69087962963</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44278</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>44676.551875</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44859</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>44859</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>44749</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44574.43967592593</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44602</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>44580</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>44602.57726851852</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>44217</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44088.78303240741</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44201</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>44201</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>44308</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>44430.93283564815</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>44859</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>44795.48144675926</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>44259</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>44757.40570601852</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>44124</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44228</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>44225</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>44228</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>44225</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>44887.43138888889</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>44588.6396875</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>44088</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>44505</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>44456</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44069</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>44207</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>44434</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>44375</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>44845</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>44375</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>44270.5584375</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>44364</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>44497</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44201</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>44552.45563657407</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>44483.66988425926</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>44483.67144675926</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>44375</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>44503</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>44475</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>44510</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>44376</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>44119</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>44601.75174768519</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>44524.46141203704</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>44214</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>44858.49122685185</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>44690</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>44602.51873842593</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>44721.32116898148</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44069</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>44424.57810185185</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44607</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>44607</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>44803.35861111111</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>44887.42521990741</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>44683.46200231482</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>44686</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>44887.42283564815</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>44887.42663194444</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>44490.74336805556</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>44343.88627314815</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44459</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44711.38366898148</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44676.56075231481</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>44074</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>44089.35622685185</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>44522.60883101852</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>44610</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44609</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44531</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>44250</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>44127</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>44253</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>44375</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44336.39239583333</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>44424.57476851852</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44470</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>44371</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44475.66188657407</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>44837.43361111111</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>44795.60174768518</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>44795.60293981482</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>44242</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44859</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>44158</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>44729.65407407407</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>44102</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>44328.41473379629</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>44068</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44582</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>44788.47552083333</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>44574</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44175</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>44207</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>44705</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>44284</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44120</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>44602</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>44175</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>44393</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>44344.48678240741</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>44592.48909722222</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>44073</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>44420.28219907408</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>44466</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>44073</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>45233</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>45736.32997685186</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>45736.33076388889</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>44603</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>44602</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>44757</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>45338</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>45338</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>45338.43358796297</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>45338</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>45338</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>45156.54523148148</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>45600.45402777778</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>44120</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
         <v>44285.87041666666</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15255,7 +15255,7 @@
         <v>45089</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45118</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>45674.38413194445</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45230</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>45169.38462962963</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>44105</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>45720.41747685185</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>45273.60899305555</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45273</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>44887</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>45204</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>44922.50314814815</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>45229.58863425926</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>45389</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>45389</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>44167</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>45085</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>44410</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>44882</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>45407.5766087963</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>45364.57331018519</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>45154.65458333334</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>45075.50622685185</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>45098.44975694444</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
         <v>45770.625625</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45660</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>44524</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45530.36846064815</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>45688</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>45688.64506944444</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>44939</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>44939</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45181</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>45607.37846064815</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>44610</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>44285.33586805555</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>45012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>44438</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>45692</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>45702.36793981482</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>44375</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>45385</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>45755</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>44789.46129629629</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>44124</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>45642</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45324.40112268519</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>45020</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>44250</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>44946</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>45204.42494212963</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>45338</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>44937</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>44937.46436342593</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>45195</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>45085</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>45428.57578703704</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>44361.93059027778</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>45697.97704861111</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45604.48289351852</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45369.44256944444</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>45146</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>45146</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>45398.79873842592</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45716.34958333334</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>44154</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44599</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44595.55912037037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45384.42409722223</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>44757.39927083333</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>44757.40454861111</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>45642.47061342592</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>45001</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45389.73820601852</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>45264.6516087963</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>45561.3744212963</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>45722.40604166667</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45604.56101851852</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>45604.56623842593</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>45604.56958333333</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>45288.46611111111</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>45764.67251157408</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45460.82011574074</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>45747</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>45747</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45561.37106481481</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45401.690625</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45761.93627314815</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45761</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45764</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>45764.84103009259</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45118.36900462963</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>44593.63554398148</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45181</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20728,7 +20728,7 @@
         <v>45770.62311342593</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>45190.39688657408</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>44153</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>45427.93607638889</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45428.55946759259</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>45674.38553240741</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>45279</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>45153</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45244.67376157407</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45749.74931712963</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45154.56967592592</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>45338</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>45338.43268518519</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45146</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45590.39090277778</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>44524.66444444445</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45664.57111111111</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>45622</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>45428.54546296296</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>45428.54791666667</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45428.55520833333</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45428.56197916667</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>45538.80545138889</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45335.63689814815</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>45428.5703587963</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45428.57371527778</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>44998.55319444444</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>44165</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45698</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45009</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>45057</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>45275.35230324074</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>45427.9417824074</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44375</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>45604.26549768518</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>44430.29293981481</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>45668.63396990741</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>45708.35037037037</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>45709.40309027778</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>45737</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44610</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44697</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>44897.42872685185</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45607.60341435186</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>45649.6427662037</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>44998</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>45320.58873842593</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>45489.50666666667</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>45348</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>45714.37306712963</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>45604.48214120371</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>45471</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>44915.41944444444</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>44790</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>45320</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>45454.73359953704</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>45590</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>45775.49840277778</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>45057</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>45229.49331018519</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>45544.36982638889</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>45610.35752314814</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>44496.58679398148</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>44942.49850694444</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>45408.61435185185</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>45404</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45600.47440972222</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>45693</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45693</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>45165.77501157407</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>45709.33226851852</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>45601</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>45517.38890046296</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>45273</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>45391.59185185185</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>45516.37174768518</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>44140</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>44526</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>45336</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>44140</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>45722.96171296296</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45716.34217592593</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>45755.41075231481</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45716.34775462963</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>45716.34298611111</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>45783.47896990741</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>45226.45565972223</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>45568</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>45391.58608796296</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44400</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>45229</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45783.38083333334</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44757</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>45475</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>45639.59918981481</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45428.57266203704</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>45642.46802083333</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>45745.75537037037</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>45525.6055787037</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>45688.63835648148</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>45709.38243055555</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>45223.60331018519</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>44308</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44098</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>44523.4103587963</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26828,7 +26828,7 @@
         <v>44069</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>44097</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>45279.61047453704</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>45476.50758101852</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         <v>45502.49574074074</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>44327</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>45754.55663194445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>45069.69295138889</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>45749.46461805556</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>45440.6484375</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>45749.46740740741</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45279.37215277777</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>45488.46717592593</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>45786</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>45604.44618055555</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>45552.65006944445</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27750,7 +27750,7 @@
         <v>45742</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>45233</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45181</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>45389.74396990741</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>45783</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>45736.32833333333</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>45335.63466435186</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>45190.47119212963</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>44524</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45764</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>45575.84530092592</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>45728.59358796296</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>45245.37445601852</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45153</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>44468.65578703704</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>44468.68219907407</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28682,7 +28682,7 @@
         <v>44985</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45273.615</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>45709.42712962963</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>45792.81104166667</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>45791</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>45098</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>45019</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29086,7 +29086,7 @@
         <v>44566</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>44278</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29200,7 +29200,7 @@
         <v>45140</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>45769.41568287037</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>44459.56224537037</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44369.46261574074</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>44496</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>45155</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>45278.39707175926</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>45348.33475694444</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>45567.53571759259</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>45692</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29775,7 +29775,7 @@
         <v>45506.59847222222</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>45041.59671296296</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29889,7 +29889,7 @@
         <v>45041</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>44924.79619212963</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>44392.68070601852</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45350</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>45348</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>45400</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>45469.34783564815</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>45720.40681712963</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>45434.44790509259</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44552.46184027778</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30464,7 +30464,7 @@
         <v>45629.38060185185</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>44971.76626157408</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45670.3792824074</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>45440.63173611111</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30697,7 +30697,7 @@
         <v>45338.43309027778</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>45622</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>45534</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>45801.73608796296</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45801.72324074074</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44757.40493055555</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31049,7 +31049,7 @@
         <v>44902.79445601852</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>44924.77766203704</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31163,7 +31163,7 @@
         <v>45801.7406712963</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>45801.7155324074</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>45800.6135300926</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>45597.38953703704</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>45174.34193287037</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45804</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>45757.34662037037</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>45191</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45805.59104166667</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45804.40983796296</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>45049</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>45140</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45308</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>44858</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>45691.56284722222</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32028,7 +32028,7 @@
         <v>45804.49788194444</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>45804</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32142,7 +32142,7 @@
         <v>45727.61247685185</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>45105.47802083333</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>45764</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>45807.45759259259</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>45474.36921296296</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>45764</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>45807.45905092593</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>45807.46021990741</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>45093.34891203704</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45595.77847222222</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45709.40560185185</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>45174</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>45749.75060185185</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>44153.45842592593</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44074</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33012,7 +33012,7 @@
         <v>44984</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33069,7 +33069,7 @@
         <v>45757</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>44152</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>44984</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>45459.71376157407</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>45428.5499537037</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>45428.55199074074</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>45369.42203703704</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>45082.56950231481</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45547.6262037037</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33587,7 +33587,7 @@
         <v>45547.62703703704</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>45085.53467592593</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45355.56142361111</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>44446</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>44945.39559027777</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>45604.56769675926</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33934,7 +33934,7 @@
         <v>45230</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>45400</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45149</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
         <v>45385.44706018519</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>45615</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>45085</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>45811.59519675926</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>45113.36457175926</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45117</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>45636.96761574074</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45579</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44734.3744212963</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>44734.37710648148</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>45583.40994212963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>45854.62081018519</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45336.92125</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44942</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>44942.60704861111</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>45351</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>45642.47158564815</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>45706.36192129629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>45734</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>45677.70096064815</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>45164</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44208</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>45709.39515046297</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>45709.40043981482</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>45230.37582175926</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>45709.39714120371</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>45435.77655092593</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>45224</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>45211.81873842593</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45154.57079861111</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>45162</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>45547.62819444444</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45164</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>45596.54981481482</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36103,7 +36103,7 @@
         <v>45818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>45107.61413194444</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>45615</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>45777.45011574074</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>45861.42532407407</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>45861.43393518519</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>45819.32747685185</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>45819.46775462963</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>45385.49137731481</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>45375</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>45597.3521412037</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>45597.35365740741</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36807,7 +36807,7 @@
         <v>44354</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36864,7 +36864,7 @@
         <v>45865.66577546296</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>45824.48737268519</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36978,7 +36978,7 @@
         <v>45825.40163194444</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>45163.72633101852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>45865.67818287037</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>45825.58365740741</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37206,7 +37206,7 @@
         <v>45454.73629629629</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37263,7 +37263,7 @@
         <v>44951</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37320,7 +37320,7 @@
         <v>44858</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37377,7 +37377,7 @@
         <v>45404.56375</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37434,7 +37434,7 @@
         <v>45644.36364583333</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>45709.38748842593</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>45709.42873842592</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>45770</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>45825.46516203704</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45865</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>45547.62391203704</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>45547.62475694445</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>45763.68868055556</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37962,7 +37962,7 @@
         <v>45763.69137731481</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45476</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38081,7 +38081,7 @@
         <v>45688.58755787037</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>45826.49353009259</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>45093</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38257,7 +38257,7 @@
         <v>45826.37920138889</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38314,7 +38314,7 @@
         <v>45826.50130787037</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38371,7 +38371,7 @@
         <v>45869.39628472222</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>44917.58131944444</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>45826.50511574074</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>45831.36230324074</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>45831.37613425926</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38656,7 +38656,7 @@
         <v>44592.72989583333</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45831.51181712963</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>45831.37420138889</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>45546.60894675926</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>45082</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45428.53717592593</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>45428.54854166666</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45428.54914351852</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>45428.55339120371</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>45428.58675925926</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39226,7 +39226,7 @@
         <v>45831</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39283,7 +39283,7 @@
         <v>45716.3528125</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>45831.5818287037</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45604.56190972222</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>45604.56427083333</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>45604.56517361111</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39588,7 +39588,7 @@
         <v>44838</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39645,7 +39645,7 @@
         <v>45604.47792824074</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39702,7 +39702,7 @@
         <v>45832.47321759259</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39764,7 +39764,7 @@
         <v>45204</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>44984</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39878,7 +39878,7 @@
         <v>45692.42515046296</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39935,7 +39935,7 @@
         <v>45568</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39997,7 +39997,7 @@
         <v>45568</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>45873</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40116,7 +40116,7 @@
         <v>45091</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45118</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40235,7 +40235,7 @@
         <v>44638.34265046296</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40292,7 +40292,7 @@
         <v>45005</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40349,7 +40349,7 @@
         <v>45692</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45705.35732638889</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40468,7 +40468,7 @@
         <v>44865.54231481482</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40525,7 +40525,7 @@
         <v>44994.45271990741</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>44396</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40639,7 +40639,7 @@
         <v>45219.44987268518</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>45506.60435185185</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40753,7 +40753,7 @@
         <v>44603</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>44074</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>45835.37094907407</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40924,7 +40924,7 @@
         <v>44503.58450231481</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>45370.64554398148</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41038,7 +41038,7 @@
         <v>45434.56020833334</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>45637.63881944444</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41152,7 +41152,7 @@
         <v>44757.40103009259</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41214,7 +41214,7 @@
         <v>44757.40538194445</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41276,7 +41276,7 @@
         <v>45028</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>44124</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>45709.40761574074</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41452,7 +41452,7 @@
         <v>45552.6449537037</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>45552</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>44994.45623842593</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>45208.64244212963</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45770</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>45223</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>45372.49736111111</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45835.48375</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>45401.44325231481</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41970,7 +41970,7 @@
         <v>45112.3402199074</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>45547.62553240741</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>45232.72258101852</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>45875</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42198,7 +42198,7 @@
         <v>44229</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42255,7 +42255,7 @@
         <v>44154</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>45201.50586805555</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>45881</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>45838.67675925926</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>45184.46447916667</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45877</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45839</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45459.71949074074</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42716,7 +42716,7 @@
         <v>45211</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>45881.4566087963</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>44923</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45338</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>45338</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43011,7 +43011,7 @@
         <v>45103</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43068,7 +43068,7 @@
         <v>44162</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43125,7 +43125,7 @@
         <v>45838.37465277778</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>45839.58087962963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43239,7 +43239,7 @@
         <v>45366</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43296,7 +43296,7 @@
         <v>45261</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43358,7 +43358,7 @@
         <v>45839</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43415,7 +43415,7 @@
         <v>45838.6196875</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43472,7 +43472,7 @@
         <v>44154</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43529,7 +43529,7 @@
         <v>45841.74796296296</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43586,7 +43586,7 @@
         <v>44073</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43643,7 +43643,7 @@
         <v>45230</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>45219.79758101852</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43762,7 +43762,7 @@
         <v>45840.479375</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43819,7 +43819,7 @@
         <v>45881.55119212963</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43876,7 +43876,7 @@
         <v>45428.55409722222</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43933,7 +43933,7 @@
         <v>45428.55619212963</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>45840.66209490741</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44047,7 +44047,7 @@
         <v>45761.93880787037</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45204</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45841.73791666667</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>45428.53776620371</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>44276</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>45338</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>44844.67142361111</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45597.34225694444</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45597.38799768518</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45295</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44642,7 +44642,7 @@
         <v>45597.39101851852</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44704,7 +44704,7 @@
         <v>45840.49215277778</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45540.56981481481</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44818,7 +44818,7 @@
         <v>44711.38688657407</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44875,7 +44875,7 @@
         <v>45590.38761574074</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44932,7 +44932,7 @@
         <v>45749</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45842.48019675926</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>45349</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45887.45643518519</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45887.46554398148</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>45338</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>45218</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>45028</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45666</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45842.47915509259</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45105.48627314815</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>45386.35322916666</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>45688.43215277778</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>45688.58667824074</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>45544.33987268519</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>45842.55467592592</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>45155</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>45114.65185185185</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>45729.67947916667</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>45887.5765625</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>45889.37565972222</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>45749</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46216,7 +46216,7 @@
         <v>44659.58702546296</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>45709.32859953704</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>45013</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>45889.36107638889</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46449,7 +46449,7 @@
         <v>45354.72975694444</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>45243</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>44844</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46620,7 +46620,7 @@
         <v>45889.36693287037</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>44971.76994212963</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>44406</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46791,7 +46791,7 @@
         <v>44971.75834490741</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>45579</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>44154</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>45211</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47024,7 +47024,7 @@
         <v>45205.35776620371</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47081,7 +47081,7 @@
         <v>44533.35804398148</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47138,7 +47138,7 @@
         <v>45891.49868055555</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>45455</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47257,7 +47257,7 @@
         <v>45091</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>44908</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47381,7 +47381,7 @@
         <v>44160</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47443,7 +47443,7 @@
         <v>45839</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>45839</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47577,7 +47577,7 @@
         <v>45372.49458333333</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>45891.49476851852</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47691,7 +47691,7 @@
         <v>45196.47457175926</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47748,7 +47748,7 @@
         <v>44140</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47805,7 +47805,7 @@
         <v>45755.42104166667</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47862,7 +47862,7 @@
         <v>45755</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>45604.5687962963</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47981,7 +47981,7 @@
         <v>44833</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48043,7 +48043,7 @@
         <v>44881.54231481482</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48100,7 +48100,7 @@
         <v>45709.39251157407</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>45244.86136574074</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>45728</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48276,7 +48276,7 @@
         <v>45229.53780092593</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48333,7 +48333,7 @@
         <v>45685.55012731482</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48390,7 +48390,7 @@
         <v>45063.27048611111</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48447,7 +48447,7 @@
         <v>44089.35689814815</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48509,7 +48509,7 @@
         <v>45245.7939699074</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48566,7 +48566,7 @@
         <v>45764</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48628,7 +48628,7 @@
         <v>45225</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>45692</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48742,7 +48742,7 @@
         <v>45679.50844907408</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48799,7 +48799,7 @@
         <v>44260</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>45428.57160879629</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48913,7 +48913,7 @@
         <v>45428.57215277778</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>45597.34579861111</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
         <v>45597.34881944444</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>44160</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49151,7 +49151,7 @@
         <v>45317</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>45041</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45320.88226851852</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45260.46252314815</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>44592.50912037037</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>44593</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>45146</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>45357.39202546296</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45716.33921296296</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>45716.35056712963</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45341.58440972222</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -567,7 +567,7 @@
         <v>45174</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         <v>44112</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44175</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44266</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45475</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45313</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>45195</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45158</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>45840.46792824074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45604.4624537037</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>44315</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>44455</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>44859</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>44833</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>45604.53089120371</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45517.34768518519</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>45450.57783564815</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>45404.55137731481</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45604.48800925926</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>45826.4996875</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>44937</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45889</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>45103</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>44295</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44375</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>44827</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44207</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>44550</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45335</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>44998</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>44160</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>45789.61961805556</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45791.44271990741</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>44858</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>45688.59202546296</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>44676</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45623</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>44663</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>44132</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>44384</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>45820.48319444444</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>45825</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44091</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>44950</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>45688.41431712963</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>44207</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>44179.52865740741</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44243</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44270.56321759259</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>44228</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44069</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>44069</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>44069</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>44155</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>44089</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44267.64171296296</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>44320.42899305555</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>44386</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>44386</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>44865.57608796296</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>44069</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>44887.42784722222</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>44887.42950231482</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>44307.45770833334</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>44508</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>44175</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44225</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>44201</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>44201</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>44201</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>44285</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44201</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>44613.65383101852</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44483.4240625</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44524.32766203704</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44225</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44193</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44447</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44085</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44202</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>44242</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>44552.45428240741</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44487</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44536</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44574.4577662037</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44461.68690972222</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44456</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>44127</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>44812.51043981482</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>44273</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>44321</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>44319.33803240741</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>44734.36189814815</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>44859</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>44176.66133101852</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44225</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>44229</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44574.45553240741</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>44165</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44859</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>44265.69087962963</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44278</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>44676.551875</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44859</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>44859</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>44749</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44574.43967592593</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44602</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>44580</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>44602.57726851852</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>44217</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44088.78303240741</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44201</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>44201</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>44308</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>44430.93283564815</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>44859</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>44795.48144675926</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>44259</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>44757.40570601852</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>44124</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44228</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>44225</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>44228</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>44225</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>44887.43138888889</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>44588.6396875</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>44088</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>44505</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>44456</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44069</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>44207</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>44434</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>44375</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>44845</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>44375</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>44270.5584375</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>44364</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>44497</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44201</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>44552.45563657407</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>44483.66988425926</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>44483.67144675926</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>44375</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>44503</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>44475</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>44510</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>44376</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>44119</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>44601.75174768519</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>44524.46141203704</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>44214</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>44858.49122685185</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>44690</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>44602.51873842593</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>44721.32116898148</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44069</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>44424.57810185185</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44607</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>44607</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>44803.35861111111</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>44887.42521990741</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>44683.46200231482</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>44686</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>44887.42283564815</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>44887.42663194444</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>44490.74336805556</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>44343.88627314815</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44459</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44711.38366898148</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44676.56075231481</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>44074</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>44089.35622685185</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>44522.60883101852</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>44610</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44609</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44531</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>44250</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>44127</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>44253</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>44375</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44336.39239583333</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>44424.57476851852</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44470</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>44371</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44475.66188657407</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>44837.43361111111</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>44795.60174768518</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>44795.60293981482</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>44242</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44859</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>44158</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>44729.65407407407</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>44102</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>44328.41473379629</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>44068</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44582</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>44788.47552083333</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>44574</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44175</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>44207</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>44705</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>44284</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44120</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>44602</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>44175</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>44393</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>44344.48678240741</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>44592.48909722222</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>44073</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>44420.28219907408</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>44466</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>44073</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>45233</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>45736.32997685186</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>45736.33076388889</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>44603</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>44602</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>44757</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>45338</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>45338</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>45338.43358796297</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>45338</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>45338</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>45156.54523148148</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>45600.45402777778</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>44120</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
         <v>44285.87041666666</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15255,7 +15255,7 @@
         <v>45089</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45118</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>45674.38413194445</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45230</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>45169.38462962963</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>44105</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>45720.41747685185</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>45273.60899305555</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45273</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>44887</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>45204</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>44922.50314814815</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>45229.58863425926</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>45389</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>45389</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>44167</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>45085</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>44410</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>44882</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>45407.5766087963</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>45364.57331018519</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>45154.65458333334</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>45075.50622685185</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>45098.44975694444</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
         <v>45770.625625</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45660</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>44524</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45530.36846064815</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>45688</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>45688.64506944444</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>44939</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>44939</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45181</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>45607.37846064815</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>44610</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>44285.33586805555</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>45012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>44438</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>45692</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>45702.36793981482</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>44375</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>45385</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>45755</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>44789.46129629629</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>44124</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>45642</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45324.40112268519</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>45020</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>44250</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>44946</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>45204.42494212963</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>45338</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>44937</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>44937.46436342593</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>45195</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>45085</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>45428.57578703704</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>44361.93059027778</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>45697.97704861111</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45604.48289351852</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45369.44256944444</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>45146</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>45146</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>45398.79873842592</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45716.34958333334</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>44154</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44599</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44595.55912037037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45384.42409722223</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>44757.39927083333</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>44757.40454861111</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>45642.47061342592</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>45001</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45389.73820601852</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>45264.6516087963</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>45561.3744212963</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>45722.40604166667</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45604.56101851852</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>45604.56623842593</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>45604.56958333333</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>45288.46611111111</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>45764.67251157408</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45460.82011574074</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>45747</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>45747</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45561.37106481481</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45401.690625</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45761.93627314815</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45761</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45764</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>45764.84103009259</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45118.36900462963</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>44593.63554398148</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45181</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20728,7 +20728,7 @@
         <v>45770.62311342593</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>45190.39688657408</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>44153</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>45427.93607638889</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45428.55946759259</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>45674.38553240741</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>45279</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>45153</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45244.67376157407</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45749.74931712963</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45154.56967592592</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>45338</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>45338.43268518519</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45146</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45590.39090277778</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>44524.66444444445</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45664.57111111111</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>45622</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>45428.54546296296</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>45428.54791666667</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45428.55520833333</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45428.56197916667</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>45538.80545138889</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45335.63689814815</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>45428.5703587963</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45428.57371527778</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>44998.55319444444</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>44165</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45698</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45009</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>45057</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>45275.35230324074</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>45427.9417824074</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44375</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>45604.26549768518</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>44430.29293981481</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>45668.63396990741</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>45708.35037037037</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>45709.40309027778</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>45737</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44610</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44697</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>44897.42872685185</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45607.60341435186</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>45649.6427662037</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>44998</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>45320.58873842593</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>45489.50666666667</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>45348</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>45714.37306712963</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>45604.48214120371</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>45471</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>44915.41944444444</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>44790</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>45320</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>45454.73359953704</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>45590</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>45775.49840277778</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>45057</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>45229.49331018519</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>45544.36982638889</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>45610.35752314814</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>44496.58679398148</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>44942.49850694444</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>45408.61435185185</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>45404</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45600.47440972222</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>45693</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45693</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>45165.77501157407</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>45709.33226851852</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>45601</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>45517.38890046296</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>45273</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>45391.59185185185</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>45516.37174768518</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>44140</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>44526</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>45336</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>44140</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>45722.96171296296</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45716.34217592593</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>45755.41075231481</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45716.34775462963</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>45716.34298611111</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>45783.47896990741</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>45226.45565972223</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>45568</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>45391.58608796296</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44400</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>45229</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45783.38083333334</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44757</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>45475</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>45639.59918981481</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45428.57266203704</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>45642.46802083333</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>45745.75537037037</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>45525.6055787037</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>45688.63835648148</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>45709.38243055555</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>45223.60331018519</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>44308</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44098</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>44523.4103587963</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26828,7 +26828,7 @@
         <v>44069</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>44097</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>45279.61047453704</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>45476.50758101852</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         <v>45502.49574074074</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>44327</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>45754.55663194445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>45069.69295138889</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>45749.46461805556</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>45440.6484375</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>45749.46740740741</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45279.37215277777</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>45488.46717592593</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>45786</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>45604.44618055555</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>45552.65006944445</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27750,7 +27750,7 @@
         <v>45742</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>45233</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45181</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>45389.74396990741</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>45783</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>45736.32833333333</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>45335.63466435186</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>45190.47119212963</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>44524</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45764</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>45575.84530092592</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>45728.59358796296</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>45245.37445601852</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45153</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>44468.65578703704</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>44468.68219907407</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28682,7 +28682,7 @@
         <v>44985</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45273.615</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>45709.42712962963</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>45792.81104166667</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>45791</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>45098</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>45019</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29086,7 +29086,7 @@
         <v>44566</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>44278</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29200,7 +29200,7 @@
         <v>45140</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>45769.41568287037</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>44459.56224537037</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44369.46261574074</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>44496</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>45155</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>45278.39707175926</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>45348.33475694444</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>45567.53571759259</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>45692</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29775,7 +29775,7 @@
         <v>45506.59847222222</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>45041.59671296296</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29889,7 +29889,7 @@
         <v>45041</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>44924.79619212963</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>44392.68070601852</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45350</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>45348</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>45400</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>45469.34783564815</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>45720.40681712963</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>45434.44790509259</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44552.46184027778</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30464,7 +30464,7 @@
         <v>45629.38060185185</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>44971.76626157408</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45670.3792824074</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>45440.63173611111</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30697,7 +30697,7 @@
         <v>45338.43309027778</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>45622</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>45534</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>45801.73608796296</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45801.72324074074</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44757.40493055555</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31049,7 +31049,7 @@
         <v>44902.79445601852</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>44924.77766203704</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31163,7 +31163,7 @@
         <v>45801.7406712963</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>45801.7155324074</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>45800.6135300926</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>45597.38953703704</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>45174.34193287037</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45804</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>45757.34662037037</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>45191</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45805.59104166667</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45804.40983796296</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>45049</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>45140</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45308</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>44858</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>45691.56284722222</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32028,7 +32028,7 @@
         <v>45804.49788194444</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>45804</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32142,7 +32142,7 @@
         <v>45727.61247685185</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>45105.47802083333</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>45764</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>45807.45759259259</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>45474.36921296296</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>45764</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>45807.45905092593</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>45807.46021990741</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>45093.34891203704</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45595.77847222222</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45709.40560185185</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>45174</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>45749.75060185185</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>44153.45842592593</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44074</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33012,7 +33012,7 @@
         <v>44984</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33069,7 +33069,7 @@
         <v>45757</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>44152</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>44984</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>45459.71376157407</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>45428.5499537037</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>45428.55199074074</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>45369.42203703704</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>45082.56950231481</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45547.6262037037</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33587,7 +33587,7 @@
         <v>45547.62703703704</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>45085.53467592593</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45355.56142361111</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>44446</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>44945.39559027777</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>45604.56769675926</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33934,7 +33934,7 @@
         <v>45230</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>45400</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45149</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
         <v>45385.44706018519</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>45615</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>45085</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>45811.59519675926</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>45113.36457175926</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45117</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>45636.96761574074</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45579</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44734.3744212963</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>44734.37710648148</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>45583.40994212963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>45854.62081018519</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45336.92125</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44942</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>44942.60704861111</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>45351</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>45642.47158564815</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>45706.36192129629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>45734</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>45677.70096064815</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>45164</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44208</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>45709.39515046297</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>45709.40043981482</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>45230.37582175926</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>45709.39714120371</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>45435.77655092593</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>45224</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>45211.81873842593</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45154.57079861111</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>45162</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>45547.62819444444</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45164</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>45596.54981481482</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36103,7 +36103,7 @@
         <v>45818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>45107.61413194444</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>45615</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>45777.45011574074</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>45861.42532407407</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>45861.43393518519</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>45819.32747685185</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>45819.46775462963</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>45385.49137731481</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>45375</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>45597.3521412037</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>45597.35365740741</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36807,7 +36807,7 @@
         <v>44354</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36864,7 +36864,7 @@
         <v>45865.66577546296</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>45824.48737268519</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36978,7 +36978,7 @@
         <v>45825.40163194444</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>45163.72633101852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>45865.67818287037</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>45825.58365740741</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37206,7 +37206,7 @@
         <v>45454.73629629629</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37263,7 +37263,7 @@
         <v>44951</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37320,7 +37320,7 @@
         <v>44858</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37377,7 +37377,7 @@
         <v>45404.56375</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37434,7 +37434,7 @@
         <v>45644.36364583333</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>45709.38748842593</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>45709.42873842592</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>45770</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>45825.46516203704</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45865</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>45547.62391203704</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>45547.62475694445</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>45763.68868055556</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37962,7 +37962,7 @@
         <v>45763.69137731481</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45476</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38081,7 +38081,7 @@
         <v>45688.58755787037</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>45826.49353009259</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>45093</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38257,7 +38257,7 @@
         <v>45826.37920138889</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38314,7 +38314,7 @@
         <v>45826.50130787037</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38371,7 +38371,7 @@
         <v>45869.39628472222</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>44917.58131944444</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>45826.50511574074</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>45831.36230324074</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>45831.37613425926</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38656,7 +38656,7 @@
         <v>44592.72989583333</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45831.51181712963</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>45831.37420138889</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>45546.60894675926</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>45082</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45428.53717592593</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>45428.54854166666</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45428.54914351852</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>45428.55339120371</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>45428.58675925926</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39226,7 +39226,7 @@
         <v>45831</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39283,7 +39283,7 @@
         <v>45716.3528125</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>45831.5818287037</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45604.56190972222</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>45604.56427083333</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>45604.56517361111</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39588,7 +39588,7 @@
         <v>44838</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39645,7 +39645,7 @@
         <v>45604.47792824074</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39702,7 +39702,7 @@
         <v>45832.47321759259</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39764,7 +39764,7 @@
         <v>45204</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>44984</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39878,7 +39878,7 @@
         <v>45692.42515046296</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39935,7 +39935,7 @@
         <v>45568</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39997,7 +39997,7 @@
         <v>45568</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>45873</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40116,7 +40116,7 @@
         <v>45091</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45118</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40235,7 +40235,7 @@
         <v>44638.34265046296</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40292,7 +40292,7 @@
         <v>45005</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40349,7 +40349,7 @@
         <v>45692</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45705.35732638889</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40468,7 +40468,7 @@
         <v>44865.54231481482</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40525,7 +40525,7 @@
         <v>44994.45271990741</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>44396</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40639,7 +40639,7 @@
         <v>45219.44987268518</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>45506.60435185185</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40753,7 +40753,7 @@
         <v>44603</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>44074</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>45835.37094907407</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40924,7 +40924,7 @@
         <v>44503.58450231481</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>45370.64554398148</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41038,7 +41038,7 @@
         <v>45434.56020833334</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>45637.63881944444</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41152,7 +41152,7 @@
         <v>44757.40103009259</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41214,7 +41214,7 @@
         <v>44757.40538194445</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41276,7 +41276,7 @@
         <v>45028</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>44124</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>45709.40761574074</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41452,7 +41452,7 @@
         <v>45552.6449537037</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>45552</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>44994.45623842593</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>45208.64244212963</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45770</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>45223</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>45372.49736111111</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45835.48375</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>45401.44325231481</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41970,7 +41970,7 @@
         <v>45112.3402199074</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>45547.62553240741</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>45232.72258101852</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>45875</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42198,7 +42198,7 @@
         <v>44229</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42255,7 +42255,7 @@
         <v>44154</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>45201.50586805555</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>45881</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>45838.67675925926</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>45184.46447916667</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45877</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45839</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45459.71949074074</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42716,7 +42716,7 @@
         <v>45211</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>45881.4566087963</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>44923</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45338</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>45338</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43011,7 +43011,7 @@
         <v>45103</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43068,7 +43068,7 @@
         <v>44162</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43125,7 +43125,7 @@
         <v>45838.37465277778</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>45839.58087962963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43239,7 +43239,7 @@
         <v>45366</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43296,7 +43296,7 @@
         <v>45261</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43358,7 +43358,7 @@
         <v>45839</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43415,7 +43415,7 @@
         <v>45838.6196875</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43472,7 +43472,7 @@
         <v>44154</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43529,7 +43529,7 @@
         <v>45841.74796296296</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43586,7 +43586,7 @@
         <v>44073</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43643,7 +43643,7 @@
         <v>45230</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>45219.79758101852</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43762,7 +43762,7 @@
         <v>45840.479375</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43819,7 +43819,7 @@
         <v>45881.55119212963</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43876,7 +43876,7 @@
         <v>45428.55409722222</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43933,7 +43933,7 @@
         <v>45428.55619212963</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>45840.66209490741</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44047,7 +44047,7 @@
         <v>45761.93880787037</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45204</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45841.73791666667</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>45428.53776620371</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>44276</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>45338</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>44844.67142361111</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45597.34225694444</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45597.38799768518</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45295</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44642,7 +44642,7 @@
         <v>45597.39101851852</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44704,7 +44704,7 @@
         <v>45840.49215277778</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45540.56981481481</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44818,7 +44818,7 @@
         <v>44711.38688657407</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44875,7 +44875,7 @@
         <v>45590.38761574074</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44932,7 +44932,7 @@
         <v>45749</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45842.48019675926</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>45349</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45887.45643518519</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45887.46554398148</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>45338</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>45218</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>45028</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45666</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45842.47915509259</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45105.48627314815</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>45386.35322916666</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>45688.43215277778</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>45688.58667824074</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>45544.33987268519</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>45842.55467592592</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>45155</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>45114.65185185185</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>45729.67947916667</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>45887.5765625</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>45889.37565972222</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>45749</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46216,7 +46216,7 @@
         <v>44659.58702546296</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>45709.32859953704</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>45013</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>45889.36107638889</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46449,7 +46449,7 @@
         <v>45354.72975694444</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>45243</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>44844</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46620,7 +46620,7 @@
         <v>45889.36693287037</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>44971.76994212963</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>44406</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46791,7 +46791,7 @@
         <v>44971.75834490741</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>45579</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>44154</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>45211</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47024,7 +47024,7 @@
         <v>45205.35776620371</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47081,7 +47081,7 @@
         <v>44533.35804398148</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47138,7 +47138,7 @@
         <v>45891.49868055555</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>45455</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47257,7 +47257,7 @@
         <v>45091</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>44908</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47381,7 +47381,7 @@
         <v>44160</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47443,7 +47443,7 @@
         <v>45839</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>45839</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47577,7 +47577,7 @@
         <v>45372.49458333333</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>45891.49476851852</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47691,7 +47691,7 @@
         <v>45196.47457175926</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47748,7 +47748,7 @@
         <v>44140</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47805,7 +47805,7 @@
         <v>45755.42104166667</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47862,7 +47862,7 @@
         <v>45755</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>45604.5687962963</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47981,7 +47981,7 @@
         <v>44833</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48043,7 +48043,7 @@
         <v>44881.54231481482</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48100,7 +48100,7 @@
         <v>45709.39251157407</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>45244.86136574074</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>45728</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48276,7 +48276,7 @@
         <v>45229.53780092593</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48333,7 +48333,7 @@
         <v>45685.55012731482</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48390,7 +48390,7 @@
         <v>45063.27048611111</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48447,7 +48447,7 @@
         <v>44089.35689814815</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48509,7 +48509,7 @@
         <v>45245.7939699074</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48566,7 +48566,7 @@
         <v>45764</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48628,7 +48628,7 @@
         <v>45225</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>45692</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48742,7 +48742,7 @@
         <v>45679.50844907408</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48799,7 +48799,7 @@
         <v>44260</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>45428.57160879629</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48913,7 +48913,7 @@
         <v>45428.57215277778</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>45597.34579861111</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
         <v>45597.34881944444</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>44160</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49151,7 +49151,7 @@
         <v>45317</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>45041</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45320.88226851852</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45260.46252314815</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>44592.50912037037</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>44593</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>45146</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>45357.39202546296</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45716.33921296296</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>45716.35056712963</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45341.58440972222</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -567,7 +567,7 @@
         <v>45174</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         <v>44112</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44175</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44266</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45313</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45475</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>45604.4624537037</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>45840.46792824074</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45158</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45195</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>44315</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>44455</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>44859</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45450.57783564815</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45517.34768518519</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45404.55137731481</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>45826.4996875</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45604.53089120371</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>44937</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>45889</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45103</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>45604.48800925926</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44833</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>44295</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44375</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>44827</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44207</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>44950</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45789.61961805556</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45791.44271990741</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>44384</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>44091</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44550</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>44998</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44676</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45623</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>44160</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45688.59202546296</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>45820.48319444444</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>44663</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>45825</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45897.51854166666</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>44858</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>44132</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45688.41431712963</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45335</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>44207</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>44179.52865740741</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>44243</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>44270.56321759259</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>44228</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>44155</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>44089</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>44267.64171296296</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>44320.42899305555</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>44386</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44386</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44865.57608796296</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>44887.42784722222</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>44887.42950231482</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>44307.45770833334</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>44508</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>44175</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44225</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>44201</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>44201</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>44201</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>44285</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>44201</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44613.65383101852</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44524.32766203704</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44483.4240625</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44193</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44225</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44202</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44447</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44085</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>44242</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44552.45428240741</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>44487</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>44536</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>44461.68690972222</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>44510</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>44574.4577662037</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>44456</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>44127</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44273</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>44321</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>44734.36189814815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>44812.51043981482</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44319.33803240741</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>44859</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>44176.66133101852</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>44225</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>44229</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>44574.45553240741</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>44165</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>44859</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>44265.69087962963</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>44278</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44676.551875</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>44859</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44859</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>44749</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>44574.43967592593</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>44602</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>44580</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>44602.57726851852</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>44217</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>44201</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>44201</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44088.78303240741</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>44859</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>44308</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44430.93283564815</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>44259</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>44795.48144675926</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>44757.40570601852</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>44124</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>44228</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>44225</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44228</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>44225</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>44887.43138888889</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>44588.6396875</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44088</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44505</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>44456</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>44207</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>44434</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>44375</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>44845</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>44375</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>44270.5584375</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>44364</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44497</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>44201</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44552.45563657407</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>44483.66988425926</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>44483.67144675926</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>44375</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>44475</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44503</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>44510</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44119</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>44376</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>44214</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44602.51873842593</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>44721.32116898148</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>44424.57810185185</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>44803.35861111111</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>44887.42521990741</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>44683.46200231482</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>44686</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>44607</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44607</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>44343.88627314815</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44711.38366898148</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>44887.42283564815</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>44887.42663194444</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>44490.74336805556</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>44459</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>44074</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>44610</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>44609</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>44676.56075231481</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>44089.35622685185</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>44522.60883101852</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44375</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>44253</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>44371</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>44531</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>44336.39239583333</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>44795.60174768518</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>44795.60293981482</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>44250</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>44127</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>44242</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>44102</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>44328.41473379629</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>44837.43361111111</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>44582</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>44475.66188657407</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>44424.57476851852</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>44470</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>44859</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>44158</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>44729.65407407407</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>44175</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>44574</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>44207</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44788.47552083333</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>44284</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>44175</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>44705</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>44757</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>44344.48678240741</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>44420.28219907408</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>44073</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>44120</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>44120</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>44466</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>44602</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>44603</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>44602</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44285.87041666666</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>44393</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>44524.46141203704</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>44592.48909722222</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>44690</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>45338</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>45338</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45338</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45401.44325231481</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44073</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44601.75174768519</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>45208.64244212963</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>45709.38748842593</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>45709.39251157407</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>45391.58608796296</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>44858.49122685185</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
         <v>45091</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>45709.38243055555</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>44276</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>45190.39688657408</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>45338</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>45338</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>44354</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         <v>44833</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44524.66444444445</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>45770.62311342593</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>45335.63689814815</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>45341.58440972222</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>44503.58450231481</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>45165.77501157407</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>45348</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45348</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15739,7 +15739,7 @@
         <v>45245.37445601852</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>45001</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>44285.33586805555</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45697.97704861111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>45385.49137731481</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>44400</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>45041.59671296296</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>45041</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>45749.46740740741</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>44308</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>45709.42712962963</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>45506.59847222222</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>45775.49840277778</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45685.55012731482</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>45288.46611111111</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>45639.59918981481</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45335.63466435186</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45082.56950231481</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45642.46802083333</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>45428.55409722222</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>45428.55619212963</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45384.42409722223</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>44396</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>44496</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>45489.50666666667</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45642.47061342592</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>45391.59185185185</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>45600.47440972222</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>45273</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45400</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>45601</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>45561.37106481481</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>45516.37174768518</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>45517.38890046296</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45568</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>45568</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>44526</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>44140</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>44140</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45709.33226851852</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>44757.39927083333</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>44757.40454861111</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44153</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>45716.34298611111</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45716.34217592593</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>45716.34775462963</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>45320</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45471</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>45400</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>45229.49331018519</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45783.38083333334</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>45279.37215277777</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>45454.73629629629</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45783.47896990741</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>45348.33475694444</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>45389</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>45389</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>45140</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>44074</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>44998</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>45103</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>45440.6484375</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45488.46717592593</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45181</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>45502.49574074074</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45428.57266203704</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45386.35322916666</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>45607.37846064815</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45469.34783564815</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>45742</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45476.50758101852</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>45428.5499537037</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>45428.55199074074</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>45140</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>45786</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>45279.61047453704</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>45552.65006944445</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44790</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>45153</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>45692</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45728.59358796296</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>45604.44618055555</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>45530.36846064815</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>45720.41747685185</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>44430.29293981481</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>44984</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>45791</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>45154.57079861111</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>45229</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45389.74396990741</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45736.32833333333</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>45783</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>45162</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>45506.60435185185</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45792.81104166667</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>44073</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45154.56967592592</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>44524</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>44524</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>44438</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>45146</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45544.33987268519</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>45590.39090277778</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         <v>45428.54791666667</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45428.53776620371</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45118</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>45355.56142361111</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>45428.53717592593</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45428.54854166666</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         <v>45428.54914351852</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         <v>45428.55339120371</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>45428.58675925926</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22238,7 +22238,7 @@
         <v>45544.36982638889</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>45370.64554398148</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>44105</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>44153.45842592593</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>44167</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>45336.92125</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>45622</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>44124</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>45204.42494212963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>45428.54546296296</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45428.56197916667</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>45597.34225694444</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>45610.35752314814</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>45604.48289351852</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>45089</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44659.58702546296</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>45720.40681712963</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45534</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45800.6135300926</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>45540.56981481481</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>45579</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>45801.7406712963</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>45804</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>44592.50912037037</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45804.49788194444</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>45804.40983796296</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         <v>45801.72324074074</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>45338.43309027778</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>45749.75060185185</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>45801.7155324074</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23968,7 +23968,7 @@
         <v>45804</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         <v>45674.38413194445</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>45801.73608796296</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>44140</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>45764</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>44610</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>45474.36921296296</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45049</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>45191</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24496,7 +24496,7 @@
         <v>44599</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>45805.59104166667</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>45764</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>45476</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>44152</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45366</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>44154</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45677.70096064815</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>45807.45759259259</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>45642.47158564815</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>45597.38799768518</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25138,7 +25138,7 @@
         <v>45597.39101851852</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>44844</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>45807.45905092593</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>45807.46021990741</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44858</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>45372.49736111111</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>44154</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>45098.44975694444</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>45811.59519675926</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>45749.46461805556</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>45567.53571759259</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45440.63173611111</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45709.40560185185</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>45435.77655092593</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>45604.56101851852</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>45604.56190972222</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26075,7 +26075,7 @@
         <v>45604.56958333333</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>45169.38462962963</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>45218</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45729.67947916667</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45372.49458333333</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>44593</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45196.47457175926</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>45552.6449537037</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>45552</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>44154</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>45709.39714120371</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>45404.56375</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45709.39515046297</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>45709.40043981482</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45747</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>45747</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45113.36457175926</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45013</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>45777.45011574074</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45755.41075231481</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45547.6262037037</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>45223</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45818</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>44566</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>44942</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>45692</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45233</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45664.57111111111</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45211.81873842593</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>45057</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>45117</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>45146</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>45649.6427662037</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>45819.32747685185</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>44942.60704861111</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45320.58873842593</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>45819.46775462963</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>45861.42532407407</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>45861.43393518519</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28333,7 +28333,7 @@
         <v>44592.72989583333</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>45688.58755787037</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>45688.63835648148</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>45211</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45408.61435185185</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45824.48737268519</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>45338.43358796297</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>45338</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>45338</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>45865.66577546296</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>45865</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>45604.5687962963</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>45688.58667824074</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>45865.67818287037</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>45644.36364583333</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44985</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45107.61413194444</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>45195</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45826.50130787037</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45579</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>44250</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45826.37920138889</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45404</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45826.50511574074</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>45825.40163194444</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>45825.58365740741</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>45825.46516203704</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>45826.49353009259</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29969,7 +29969,7 @@
         <v>45757</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45636.96761574074</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>45702.36793981482</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>45722.40604166667</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>45869.39628472222</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
         <v>45184.46447916667</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30316,7 +30316,7 @@
         <v>45757.34662037037</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30373,7 +30373,7 @@
         <v>45389.73820601852</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45597.35365740741</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30492,7 +30492,7 @@
         <v>45831.5818287037</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>45211</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30606,7 +30606,7 @@
         <v>45831</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>45085</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>45459.71376157407</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30777,7 +30777,7 @@
         <v>45763.68868055556</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>45763.69137731481</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>45832.47321759259</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>45831.37613425926</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>45709.32859953704</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>45709.40761574074</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>45873</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45223.60331018519</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>45831.36230324074</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>44945.39559027777</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>45831.37420138889</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31429,7 +31429,7 @@
         <v>45063.27048611111</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>45831.51181712963</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>45153</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>45174</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>45597.3521412037</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>45770</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31776,7 +31776,7 @@
         <v>45770</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>45230</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31895,7 +31895,7 @@
         <v>45688.43215277778</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>44757</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32014,7 +32014,7 @@
         <v>45875</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32071,7 +32071,7 @@
         <v>44229</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>45278.39707175926</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32185,7 +32185,7 @@
         <v>45009</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32242,7 +32242,7 @@
         <v>45204</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>44923</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45835.37094907407</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>45629.38060185185</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>45769.41568287037</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>45838.67675925926</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45838.6196875</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>45273.615</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>45835.48375</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>45881.4566087963</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32822,7 +32822,7 @@
         <v>45295</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32884,7 +32884,7 @@
         <v>45839</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>45093</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>45840.479375</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33055,7 +33055,7 @@
         <v>45155</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>45243</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>45877</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>45881</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>45604.56769675926</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>45604.48214120371</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>45838.37465277778</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>45839</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>45840.66209490741</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>45317</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44915.41944444444</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>45840.49215277778</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>45881.55119212963</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>45839.58087962963</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45336</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>44858</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44984</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>44984</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44971.75834490741</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>45230</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45075.50622685185</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45666</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34329,7 +34329,7 @@
         <v>45727.61247685185</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>45841.73791666667</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>44496.58679398148</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34500,7 +34500,7 @@
         <v>44757.40103009259</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>44757.40538194445</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>45842.48019675926</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34681,7 +34681,7 @@
         <v>44971.76626157408</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34738,7 +34738,7 @@
         <v>45841.74796296296</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>45842.47915509259</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34852,7 +34852,7 @@
         <v>45842.55467592592</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>45354.72975694444</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>45230</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35028,7 +35028,7 @@
         <v>45734</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>45351</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>45460.82011574074</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>45887.45643518519</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>45887.46554398148</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>45349</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>45754.55663194445</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>45041</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35484,7 +35484,7 @@
         <v>45264.6516087963</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35541,7 +35541,7 @@
         <v>45114.65185185185</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>44939</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35655,7 +35655,7 @@
         <v>44939</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>44074</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>45547.62553240741</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>44523.4103587963</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35883,7 +35883,7 @@
         <v>45887.5765625</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35940,7 +35940,7 @@
         <v>45475</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>45889.36693287037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>45324.40112268519</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36111,7 +36111,7 @@
         <v>45163.72633101852</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36168,7 +36168,7 @@
         <v>45889.37565972222</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>45279</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36282,7 +36282,7 @@
         <v>45181</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>45889.36107638889</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36396,7 +36396,7 @@
         <v>45357.39202546296</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>44603</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>45615</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>45894.59266203704</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>45891.49868055555</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36681,7 +36681,7 @@
         <v>45891.49476851852</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>45604.26549768518</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>45597.38953703704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>44278</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>45146</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45146</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>44208</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>45320.88226851852</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>45118</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45693</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>45693</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45839</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37395,7 +37395,7 @@
         <v>45854.62081018519</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45764.67251157408</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>45839</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>45898.39543981481</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>45709.40309027778</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>45308</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>45538.80545138889</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>45897</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>45547.62391203704</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>45547.62475694445</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>45897.35350694445</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45897.34547453704</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>45692</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>45897</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>45897.44971064815</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>45201.50586805555</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>45764</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38379,7 +38379,7 @@
         <v>45764.84103009259</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>44406</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38498,7 +38498,7 @@
         <v>45028</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>45736.32997685186</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38622,7 +38622,7 @@
         <v>45736.33076388889</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>45770.625625</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>44922.50314814815</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>45692</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>44924.77766203704</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>44369.46261574074</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38969,7 +38969,7 @@
         <v>45637.63881944444</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39026,7 +39026,7 @@
         <v>45219.44987268518</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>44410</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>45224</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45385.44706018519</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39264,7 +39264,7 @@
         <v>44124</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>45205.35776620371</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>44757.40493055555</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39440,7 +39440,7 @@
         <v>45688</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>45688.64506944444</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>45338</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45338.43268518519</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>44361.93059027778</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>45155</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>45273.60899305555</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45273</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>45622</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>45233</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>45755</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>44897.42872685185</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45761.93627314815</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40206,7 +40206,7 @@
         <v>45761</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>45745.75537037037</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45749</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>44459.56224537037</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45028</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40501,7 +40501,7 @@
         <v>45244.86136574074</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40558,7 +40558,7 @@
         <v>44951</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>44097</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40672,7 +40672,7 @@
         <v>44160</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40734,7 +40734,7 @@
         <v>44946</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40791,7 +40791,7 @@
         <v>45561.3744212963</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40848,7 +40848,7 @@
         <v>44160</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40905,7 +40905,7 @@
         <v>45261</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40967,7 +40967,7 @@
         <v>44552.46184027778</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41024,7 +41024,7 @@
         <v>44595.55912037037</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>44533.35804398148</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>44375</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41195,7 +41195,7 @@
         <v>45164</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>44881.54231481482</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>44924.79619212963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45012</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>44638.34265046296</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>45230.37582175926</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45525.6055787037</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>45716.33921296296</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>45112.3402199074</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41718,7 +41718,7 @@
         <v>44089.35689814815</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41780,7 +41780,7 @@
         <v>44887</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41837,7 +41837,7 @@
         <v>44468.65578703704</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>45428.57578703704</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41951,7 +41951,7 @@
         <v>45670.3792824074</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42008,7 +42008,7 @@
         <v>44844.67142361111</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42065,7 +42065,7 @@
         <v>45764</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42127,7 +42127,7 @@
         <v>44392.68070601852</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42184,7 +42184,7 @@
         <v>45398.79873842592</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>45706.36192129629</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42298,7 +42298,7 @@
         <v>45085</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42355,7 +42355,7 @@
         <v>45583.40994212963</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>45204</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42469,7 +42469,7 @@
         <v>45755</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42526,7 +42526,7 @@
         <v>44882</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42583,7 +42583,7 @@
         <v>44971.76994212963</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42640,7 +42640,7 @@
         <v>45607.60341435186</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>45595.77847222222</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>45705.35732638889</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42811,7 +42811,7 @@
         <v>45546.60894675926</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>45082</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>45604.47792824074</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>44468.68219907407</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>44446</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>45226.45565972223</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43153,7 +43153,7 @@
         <v>45455</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45232.72258101852</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>44162</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43329,7 +43329,7 @@
         <v>45181</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43391,7 +43391,7 @@
         <v>45407.5766087963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43448,7 +43448,7 @@
         <v>45568</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>45385</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43572,7 +43572,7 @@
         <v>44937</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>44937.46436342593</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43686,7 +43686,7 @@
         <v>45275.35230324074</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43743,7 +43743,7 @@
         <v>45245.7939699074</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43800,7 +43800,7 @@
         <v>44711.38688657407</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43857,7 +43857,7 @@
         <v>44994.45623842593</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>44917.58131944444</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>44902.79445601852</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45547.62819444444</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44085,7 +44085,7 @@
         <v>45428.55520833333</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44142,7 +44142,7 @@
         <v>45547.62703703704</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>44838</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45674.38553240741</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45174.34193287037</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44375,7 +44375,7 @@
         <v>45597.34579861111</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>45597.34881944444</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>45600.45402777778</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>44908</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>45093.34891203704</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>45596.54981481482</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>44697</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45069.69295138889</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45679.50844907408</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>45716.35056712963</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44970,7 +44970,7 @@
         <v>45590.38761574074</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>45369.42203703704</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45084,7 +45084,7 @@
         <v>45020</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45146,7 +45146,7 @@
         <v>44260</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45203,7 +45203,7 @@
         <v>45668.63396990741</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45260,7 +45260,7 @@
         <v>45260.46252314815</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>44865.54231481482</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45374,7 +45374,7 @@
         <v>45156.54523148148</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>45369.44256944444</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>44375</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45545,7 +45545,7 @@
         <v>45434.56020833334</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45602,7 +45602,7 @@
         <v>45375</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45659,7 +45659,7 @@
         <v>45427.93607638889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45716,7 +45716,7 @@
         <v>45225</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45773,7 +45773,7 @@
         <v>45350</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45830,7 +45830,7 @@
         <v>44998.55319444444</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45907,7 +45907,7 @@
         <v>45428.55946759259</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45964,7 +45964,7 @@
         <v>45428.5703587963</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46021,7 +46021,7 @@
         <v>45428.57371527778</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46078,7 +46078,7 @@
         <v>45691.56284722222</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46135,7 +46135,7 @@
         <v>45454.73359953704</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46192,7 +46192,7 @@
         <v>45118.36900462963</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46249,7 +46249,7 @@
         <v>45364.57331018519</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>44593.63554398148</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>45105.48627314815</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>45164</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46477,7 +46477,7 @@
         <v>45615</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46534,7 +46534,7 @@
         <v>44165</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46591,7 +46591,7 @@
         <v>45105.47802083333</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46648,7 +46648,7 @@
         <v>45244.67376157407</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46705,7 +46705,7 @@
         <v>45755.42104166667</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46762,7 +46762,7 @@
         <v>45749</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46824,7 +46824,7 @@
         <v>45764</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46886,7 +46886,7 @@
         <v>45459.71949074074</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46943,7 +46943,7 @@
         <v>45005</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47000,7 +47000,7 @@
         <v>44098</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47057,7 +47057,7 @@
         <v>45098</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47114,7 +47114,7 @@
         <v>45590</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>45604.56427083333</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47233,7 +47233,7 @@
         <v>45604.56517361111</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47295,7 +47295,7 @@
         <v>45761.93880787037</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47357,7 +47357,7 @@
         <v>45604.56623842593</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47419,7 +47419,7 @@
         <v>45190.47119212963</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         <v>45708.35037037037</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47533,7 +47533,7 @@
         <v>45692.42515046296</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47590,7 +47590,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47647,7 +47647,7 @@
         <v>44327</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47704,7 +47704,7 @@
         <v>45229.53780092593</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>45091</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47823,7 +47823,7 @@
         <v>45085</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47880,7 +47880,7 @@
         <v>45749.74931712963</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>45716.34958333334</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47999,7 +47999,7 @@
         <v>44994.45271990741</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48056,7 +48056,7 @@
         <v>45660</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48113,7 +48113,7 @@
         <v>44610</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48170,7 +48170,7 @@
         <v>45149</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48227,7 +48227,7 @@
         <v>44942.49850694444</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>44789.46129629629</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48341,7 +48341,7 @@
         <v>45219.79758101852</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>45085.53467592593</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>45401.690625</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44154</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>45427.9417824074</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>45428.57160879629</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>45428.57215277778</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45338</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45338</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>45716.3528125</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45019</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45642</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45714.37306712963</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>45575.84530092592</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45057</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45154.65458333334</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>45728</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49330,7 +49330,7 @@
         <v>45722.96171296296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>45434.44790509259</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>45709.42873842592</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49506,7 +49506,7 @@
         <v>45229.58863425926</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>45737</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49620,7 +49620,7 @@
         <v>44734.3744212963</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49677,7 +49677,7 @@
         <v>44734.37710648148</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -567,7 +567,7 @@
         <v>45174</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         <v>44112</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44175</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44266</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45313</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45475</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>45604.4624537037</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>45840.46792824074</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45158</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45195</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>44315</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>44455</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>44859</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45450.57783564815</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45517.34768518519</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45404.55137731481</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>45826.4996875</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45604.53089120371</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>44937</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>45889</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45103</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>45604.48800925926</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44833</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>44295</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44375</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>44827</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44207</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>44950</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45789.61961805556</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45791.44271990741</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>44384</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>44091</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44550</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>44998</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44676</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45623</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>44160</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45688.59202546296</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>45820.48319444444</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>44663</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>45825</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45897.51854166666</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>44858</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>44132</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45688.41431712963</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45335</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>44207</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>44179.52865740741</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>44243</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>44270.56321759259</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>44228</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>44155</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>44089</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>44267.64171296296</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>44320.42899305555</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>44386</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44386</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44865.57608796296</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>44887.42784722222</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>44887.42950231482</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>44307.45770833334</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>44508</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>44175</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44225</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>44201</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>44201</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>44201</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>44285</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>44201</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44613.65383101852</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44524.32766203704</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44483.4240625</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44193</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44225</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44202</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44447</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44085</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>44242</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44552.45428240741</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>44487</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>44536</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>44461.68690972222</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>44510</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>44574.4577662037</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>44456</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>44127</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44273</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>44321</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>44734.36189814815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>44812.51043981482</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44319.33803240741</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>44859</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>44176.66133101852</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>44225</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>44229</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>44574.45553240741</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>44165</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>44859</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>44265.69087962963</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>44278</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44676.551875</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>44859</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44859</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>44749</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>44574.43967592593</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>44602</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>44580</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>44602.57726851852</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>44217</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>44201</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>44201</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44088.78303240741</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>44859</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>44308</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44430.93283564815</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>44259</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>44795.48144675926</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>44757.40570601852</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>44124</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>44228</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>44225</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44228</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>44225</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>44887.43138888889</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>44588.6396875</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44088</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44505</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>44456</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>44207</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>44434</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>44375</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>44845</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>44375</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>44270.5584375</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>44364</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44497</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>44201</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44552.45563657407</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>44483.66988425926</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>44483.67144675926</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>44375</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>44475</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44503</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>44510</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44119</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>44376</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>44214</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44602.51873842593</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>44721.32116898148</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>44424.57810185185</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>44803.35861111111</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>44887.42521990741</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>44683.46200231482</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>44686</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>44607</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44607</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>44343.88627314815</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44711.38366898148</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>44887.42283564815</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>44887.42663194444</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>44490.74336805556</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>44459</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>44074</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>44610</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>44609</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>44676.56075231481</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>44089.35622685185</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>44522.60883101852</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44375</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>44253</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>44371</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>44531</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>44336.39239583333</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>44795.60174768518</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>44795.60293981482</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>44250</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>44127</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>44242</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>44102</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>44328.41473379629</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>44837.43361111111</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>44582</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>44475.66188657407</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>44424.57476851852</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>44470</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>44859</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>44158</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>44729.65407407407</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>44175</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>44574</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>44207</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44788.47552083333</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>44284</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>44175</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>44705</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>44757</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>44344.48678240741</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>44420.28219907408</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>44073</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>44120</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>44120</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>44466</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>44602</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>44603</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>44602</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44285.87041666666</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>44393</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>44524.46141203704</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>44592.48909722222</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>44690</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>45338</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>45338</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45338</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45401.44325231481</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44073</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44601.75174768519</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>45208.64244212963</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>45709.38748842593</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>45709.39251157407</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>45391.58608796296</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>44858.49122685185</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
         <v>45091</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>45709.38243055555</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>44276</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>45190.39688657408</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>45338</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>45338</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>44354</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         <v>44833</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44524.66444444445</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>45770.62311342593</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>45335.63689814815</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>45341.58440972222</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>44503.58450231481</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>45165.77501157407</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>45348</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45348</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15739,7 +15739,7 @@
         <v>45245.37445601852</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>45001</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>44285.33586805555</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45697.97704861111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>45385.49137731481</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>44400</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>45041.59671296296</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>45041</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>45749.46740740741</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>44308</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>45709.42712962963</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>45506.59847222222</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>45775.49840277778</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45685.55012731482</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>45288.46611111111</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>45639.59918981481</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45335.63466435186</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45082.56950231481</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45642.46802083333</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>45428.55409722222</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>45428.55619212963</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45384.42409722223</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>44396</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>44496</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>45489.50666666667</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45642.47061342592</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>45391.59185185185</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>45600.47440972222</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>45273</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45400</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>45601</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>45561.37106481481</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>45516.37174768518</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>45517.38890046296</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45568</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>45568</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>44526</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>44140</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>44140</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45709.33226851852</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>44757.39927083333</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>44757.40454861111</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44153</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>45716.34298611111</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45716.34217592593</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>45716.34775462963</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>45320</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45471</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>45400</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>45229.49331018519</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45783.38083333334</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>45279.37215277777</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>45454.73629629629</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45783.47896990741</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>45348.33475694444</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>45389</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>45389</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>45140</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>44074</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>44998</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>45103</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>45440.6484375</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45488.46717592593</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45181</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>45502.49574074074</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45428.57266203704</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45386.35322916666</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>45607.37846064815</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45469.34783564815</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>45742</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45476.50758101852</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>45428.5499537037</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>45428.55199074074</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>45140</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>45786</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>45279.61047453704</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>45552.65006944445</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44790</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>45153</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>45692</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45728.59358796296</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>45604.44618055555</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>45530.36846064815</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>45720.41747685185</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>44430.29293981481</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>44984</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>45791</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>45154.57079861111</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>45229</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45389.74396990741</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45736.32833333333</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>45783</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>45162</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>45506.60435185185</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45792.81104166667</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>44073</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45154.56967592592</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>44524</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>44524</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>44438</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>45146</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45544.33987268519</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>45590.39090277778</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         <v>45428.54791666667</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45428.53776620371</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45118</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>45355.56142361111</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>45428.53717592593</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45428.54854166666</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         <v>45428.54914351852</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         <v>45428.55339120371</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>45428.58675925926</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22238,7 +22238,7 @@
         <v>45544.36982638889</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>45370.64554398148</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>44105</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>44153.45842592593</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>44167</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>45336.92125</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>45622</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>44124</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>45204.42494212963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>45428.54546296296</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45428.56197916667</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>45597.34225694444</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>45610.35752314814</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>45604.48289351852</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>45089</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44659.58702546296</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>45720.40681712963</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45534</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45800.6135300926</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>45540.56981481481</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>45579</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>45801.7406712963</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>45804</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>44592.50912037037</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45804.49788194444</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>45804.40983796296</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         <v>45801.72324074074</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>45338.43309027778</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>45749.75060185185</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>45801.7155324074</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23968,7 +23968,7 @@
         <v>45804</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         <v>45674.38413194445</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>45801.73608796296</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>44140</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>45764</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>44610</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>45474.36921296296</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45049</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>45191</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24496,7 +24496,7 @@
         <v>44599</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>45805.59104166667</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>45764</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>45476</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>44152</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45366</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>44154</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45677.70096064815</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>45807.45759259259</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>45642.47158564815</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>45597.38799768518</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25138,7 +25138,7 @@
         <v>45597.39101851852</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>44844</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>45807.45905092593</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>45807.46021990741</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44858</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>45372.49736111111</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>44154</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>45098.44975694444</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>45811.59519675926</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>45749.46461805556</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>45567.53571759259</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45440.63173611111</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45709.40560185185</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>45435.77655092593</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>45604.56101851852</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>45604.56190972222</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26075,7 +26075,7 @@
         <v>45604.56958333333</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>45169.38462962963</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>45218</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45729.67947916667</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45372.49458333333</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>44593</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45196.47457175926</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>45552.6449537037</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>45552</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>44154</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>45709.39714120371</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>45404.56375</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45709.39515046297</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>45709.40043981482</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45747</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>45747</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45113.36457175926</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45013</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>45777.45011574074</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45755.41075231481</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45547.6262037037</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>45223</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45818</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>44566</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>44942</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>45692</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45233</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45664.57111111111</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45211.81873842593</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>45057</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>45117</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>45146</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>45649.6427662037</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>45819.32747685185</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>44942.60704861111</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45320.58873842593</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>45819.46775462963</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>45861.42532407407</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>45861.43393518519</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28333,7 +28333,7 @@
         <v>44592.72989583333</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>45688.58755787037</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>45688.63835648148</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>45211</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45408.61435185185</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45824.48737268519</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>45338.43358796297</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>45338</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>45338</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>45865.66577546296</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>45865</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>45604.5687962963</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>45688.58667824074</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>45865.67818287037</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>45644.36364583333</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44985</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45107.61413194444</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>45195</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45826.50130787037</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45579</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>44250</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45826.37920138889</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45404</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45826.50511574074</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>45825.40163194444</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>45825.58365740741</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>45825.46516203704</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>45826.49353009259</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29969,7 +29969,7 @@
         <v>45757</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45636.96761574074</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>45702.36793981482</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>45722.40604166667</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>45869.39628472222</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
         <v>45184.46447916667</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30316,7 +30316,7 @@
         <v>45757.34662037037</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30373,7 +30373,7 @@
         <v>45389.73820601852</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45597.35365740741</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30492,7 +30492,7 @@
         <v>45831.5818287037</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>45211</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30606,7 +30606,7 @@
         <v>45831</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>45085</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>45459.71376157407</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30777,7 +30777,7 @@
         <v>45763.68868055556</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>45763.69137731481</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>45832.47321759259</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>45831.37613425926</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>45709.32859953704</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>45709.40761574074</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>45873</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45223.60331018519</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>45831.36230324074</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>44945.39559027777</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>45831.37420138889</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31429,7 +31429,7 @@
         <v>45063.27048611111</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>45831.51181712963</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>45153</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>45174</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>45597.3521412037</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>45770</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31776,7 +31776,7 @@
         <v>45770</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>45230</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31895,7 +31895,7 @@
         <v>45688.43215277778</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>44757</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32014,7 +32014,7 @@
         <v>45875</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32071,7 +32071,7 @@
         <v>44229</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>45278.39707175926</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32185,7 +32185,7 @@
         <v>45009</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32242,7 +32242,7 @@
         <v>45204</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>44923</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45835.37094907407</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>45629.38060185185</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>45769.41568287037</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>45838.67675925926</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45838.6196875</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>45273.615</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>45835.48375</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>45881.4566087963</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32822,7 +32822,7 @@
         <v>45295</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32884,7 +32884,7 @@
         <v>45839</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>45093</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>45840.479375</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33055,7 +33055,7 @@
         <v>45155</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>45243</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>45877</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>45881</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>45604.56769675926</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>45604.48214120371</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>45838.37465277778</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>45839</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>45840.66209490741</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>45317</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44915.41944444444</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>45840.49215277778</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>45881.55119212963</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>45839.58087962963</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45336</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>44858</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44984</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>44984</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44971.75834490741</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>45230</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45075.50622685185</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45666</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34329,7 +34329,7 @@
         <v>45727.61247685185</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>45841.73791666667</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>44496.58679398148</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34500,7 +34500,7 @@
         <v>44757.40103009259</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>44757.40538194445</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>45842.48019675926</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34681,7 +34681,7 @@
         <v>44971.76626157408</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34738,7 +34738,7 @@
         <v>45841.74796296296</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>45842.47915509259</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34852,7 +34852,7 @@
         <v>45842.55467592592</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>45354.72975694444</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>45230</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35028,7 +35028,7 @@
         <v>45734</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>45351</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>45460.82011574074</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>45887.45643518519</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>45887.46554398148</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>45349</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>45754.55663194445</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>45041</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35484,7 +35484,7 @@
         <v>45264.6516087963</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35541,7 +35541,7 @@
         <v>45114.65185185185</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>44939</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35655,7 +35655,7 @@
         <v>44939</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>44074</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>45547.62553240741</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>44523.4103587963</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35883,7 +35883,7 @@
         <v>45887.5765625</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35940,7 +35940,7 @@
         <v>45475</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>45889.36693287037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>45324.40112268519</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36111,7 +36111,7 @@
         <v>45163.72633101852</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36168,7 +36168,7 @@
         <v>45889.37565972222</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>45279</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36282,7 +36282,7 @@
         <v>45181</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>45889.36107638889</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36396,7 +36396,7 @@
         <v>45357.39202546296</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>44603</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>45615</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>45894.59266203704</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>45891.49868055555</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36681,7 +36681,7 @@
         <v>45891.49476851852</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>45604.26549768518</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>45597.38953703704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>44278</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>45146</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45146</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>44208</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>45320.88226851852</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>45118</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45693</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>45693</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45839</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37395,7 +37395,7 @@
         <v>45854.62081018519</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45764.67251157408</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>45839</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>45898.39543981481</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>45709.40309027778</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>45308</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>45538.80545138889</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>45897</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>45547.62391203704</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>45547.62475694445</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>45897.35350694445</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45897.34547453704</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>45692</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>45897</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>45897.44971064815</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>45201.50586805555</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>45764</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38379,7 +38379,7 @@
         <v>45764.84103009259</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>44406</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38498,7 +38498,7 @@
         <v>45028</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>45736.32997685186</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38622,7 +38622,7 @@
         <v>45736.33076388889</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>45770.625625</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>44922.50314814815</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>45692</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>44924.77766203704</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>44369.46261574074</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38969,7 +38969,7 @@
         <v>45637.63881944444</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39026,7 +39026,7 @@
         <v>45219.44987268518</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>44410</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>45224</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45385.44706018519</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39264,7 +39264,7 @@
         <v>44124</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>45205.35776620371</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>44757.40493055555</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39440,7 +39440,7 @@
         <v>45688</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>45688.64506944444</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>45338</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45338.43268518519</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>44361.93059027778</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>45155</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>45273.60899305555</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45273</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>45622</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>45233</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>45755</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>44897.42872685185</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45761.93627314815</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40206,7 +40206,7 @@
         <v>45761</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>45745.75537037037</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45749</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>44459.56224537037</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45028</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40501,7 +40501,7 @@
         <v>45244.86136574074</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40558,7 +40558,7 @@
         <v>44951</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>44097</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40672,7 +40672,7 @@
         <v>44160</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40734,7 +40734,7 @@
         <v>44946</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40791,7 +40791,7 @@
         <v>45561.3744212963</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40848,7 +40848,7 @@
         <v>44160</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40905,7 +40905,7 @@
         <v>45261</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40967,7 +40967,7 @@
         <v>44552.46184027778</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41024,7 +41024,7 @@
         <v>44595.55912037037</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>44533.35804398148</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>44375</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41195,7 +41195,7 @@
         <v>45164</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>44881.54231481482</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>44924.79619212963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45012</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>44638.34265046296</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>45230.37582175926</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45525.6055787037</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>45716.33921296296</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>45112.3402199074</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41718,7 +41718,7 @@
         <v>44089.35689814815</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41780,7 +41780,7 @@
         <v>44887</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41837,7 +41837,7 @@
         <v>44468.65578703704</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>45428.57578703704</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41951,7 +41951,7 @@
         <v>45670.3792824074</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42008,7 +42008,7 @@
         <v>44844.67142361111</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42065,7 +42065,7 @@
         <v>45764</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42127,7 +42127,7 @@
         <v>44392.68070601852</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42184,7 +42184,7 @@
         <v>45398.79873842592</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>45706.36192129629</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42298,7 +42298,7 @@
         <v>45085</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42355,7 +42355,7 @@
         <v>45583.40994212963</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>45204</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42469,7 +42469,7 @@
         <v>45755</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42526,7 +42526,7 @@
         <v>44882</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42583,7 +42583,7 @@
         <v>44971.76994212963</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42640,7 +42640,7 @@
         <v>45607.60341435186</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>45595.77847222222</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>45705.35732638889</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42811,7 +42811,7 @@
         <v>45546.60894675926</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>45082</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>45604.47792824074</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>44468.68219907407</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>44446</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>45226.45565972223</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43153,7 +43153,7 @@
         <v>45455</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45232.72258101852</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>44162</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43329,7 +43329,7 @@
         <v>45181</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43391,7 +43391,7 @@
         <v>45407.5766087963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43448,7 +43448,7 @@
         <v>45568</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>45385</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43572,7 +43572,7 @@
         <v>44937</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>44937.46436342593</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43686,7 +43686,7 @@
         <v>45275.35230324074</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43743,7 +43743,7 @@
         <v>45245.7939699074</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43800,7 +43800,7 @@
         <v>44711.38688657407</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43857,7 +43857,7 @@
         <v>44994.45623842593</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>44917.58131944444</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>44902.79445601852</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45547.62819444444</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44085,7 +44085,7 @@
         <v>45428.55520833333</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44142,7 +44142,7 @@
         <v>45547.62703703704</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>44838</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45674.38553240741</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45174.34193287037</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44375,7 +44375,7 @@
         <v>45597.34579861111</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>45597.34881944444</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>45600.45402777778</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>44908</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>45093.34891203704</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>45596.54981481482</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>44697</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45069.69295138889</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45679.50844907408</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>45716.35056712963</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44970,7 +44970,7 @@
         <v>45590.38761574074</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>45369.42203703704</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45084,7 +45084,7 @@
         <v>45020</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45146,7 +45146,7 @@
         <v>44260</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45203,7 +45203,7 @@
         <v>45668.63396990741</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45260,7 +45260,7 @@
         <v>45260.46252314815</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>44865.54231481482</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45374,7 +45374,7 @@
         <v>45156.54523148148</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>45369.44256944444</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>44375</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45545,7 +45545,7 @@
         <v>45434.56020833334</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45602,7 +45602,7 @@
         <v>45375</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45659,7 +45659,7 @@
         <v>45427.93607638889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45716,7 +45716,7 @@
         <v>45225</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45773,7 +45773,7 @@
         <v>45350</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45830,7 +45830,7 @@
         <v>44998.55319444444</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45907,7 +45907,7 @@
         <v>45428.55946759259</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45964,7 +45964,7 @@
         <v>45428.5703587963</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46021,7 +46021,7 @@
         <v>45428.57371527778</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46078,7 +46078,7 @@
         <v>45691.56284722222</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46135,7 +46135,7 @@
         <v>45454.73359953704</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46192,7 +46192,7 @@
         <v>45118.36900462963</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46249,7 +46249,7 @@
         <v>45364.57331018519</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>44593.63554398148</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>45105.48627314815</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>45164</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46477,7 +46477,7 @@
         <v>45615</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46534,7 +46534,7 @@
         <v>44165</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46591,7 +46591,7 @@
         <v>45105.47802083333</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46648,7 +46648,7 @@
         <v>45244.67376157407</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46705,7 +46705,7 @@
         <v>45755.42104166667</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46762,7 +46762,7 @@
         <v>45749</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46824,7 +46824,7 @@
         <v>45764</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46886,7 +46886,7 @@
         <v>45459.71949074074</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46943,7 +46943,7 @@
         <v>45005</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47000,7 +47000,7 @@
         <v>44098</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47057,7 +47057,7 @@
         <v>45098</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47114,7 +47114,7 @@
         <v>45590</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>45604.56427083333</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47233,7 +47233,7 @@
         <v>45604.56517361111</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47295,7 +47295,7 @@
         <v>45761.93880787037</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47357,7 +47357,7 @@
         <v>45604.56623842593</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47419,7 +47419,7 @@
         <v>45190.47119212963</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         <v>45708.35037037037</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47533,7 +47533,7 @@
         <v>45692.42515046296</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47590,7 +47590,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47647,7 +47647,7 @@
         <v>44327</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47704,7 +47704,7 @@
         <v>45229.53780092593</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>45091</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47823,7 +47823,7 @@
         <v>45085</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47880,7 +47880,7 @@
         <v>45749.74931712963</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>45716.34958333334</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47999,7 +47999,7 @@
         <v>44994.45271990741</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48056,7 +48056,7 @@
         <v>45660</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48113,7 +48113,7 @@
         <v>44610</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48170,7 +48170,7 @@
         <v>45149</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48227,7 +48227,7 @@
         <v>44942.49850694444</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>44789.46129629629</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48341,7 +48341,7 @@
         <v>45219.79758101852</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>45085.53467592593</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>45401.690625</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44154</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>45427.9417824074</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>45428.57160879629</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>45428.57215277778</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45338</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45338</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>45716.3528125</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45019</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45642</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45714.37306712963</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>45575.84530092592</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45057</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45154.65458333334</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>45728</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49330,7 +49330,7 @@
         <v>45722.96171296296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>45434.44790509259</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>45709.42873842592</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49506,7 +49506,7 @@
         <v>45229.58863425926</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>45737</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49620,7 +49620,7 @@
         <v>44734.3744212963</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49677,7 +49677,7 @@
         <v>44734.37710648148</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -567,7 +567,7 @@
         <v>45174</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         <v>44112</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44175</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44266</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45313</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45475</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>45158</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>45840.46792824074</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45604.4624537037</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45195</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>44315</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>44455</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>44859</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45450.57783564815</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45604.53089120371</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44833</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>45517.34768518519</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>45404.55137731481</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45604.48800925926</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>45826.4996875</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45889</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>44937</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>45103</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>44295</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44375</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>44827</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44207</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>44998</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45335</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>45789.61961805556</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>45791.44271990741</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>44160</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44858</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>45688.59202546296</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>44676</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>45623</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45820.48319444444</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>45825</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>44384</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>45897.51854166666</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44091</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>44663</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>44132</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>44950</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>45688.41431712963</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>44550</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>44207</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>44179.52865740741</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>44243</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>44270.56321759259</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>44228</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>44155</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>44089</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>44267.64171296296</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>44320.42899305555</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>44386</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44386</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44865.57608796296</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>44887.42784722222</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>44887.42950231482</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>44307.45770833334</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>44508</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>44175</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44225</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>44201</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>44201</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>44201</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>44285</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>44201</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44613.65383101852</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44524.32766203704</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44483.4240625</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44225</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>44193</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44202</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44447</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44085</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>44242</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44487</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>44552.45428240741</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>44536</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>44461.68690972222</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>44574.4577662037</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>44510</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>44456</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>44127</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44734.36189814815</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>44812.51043981482</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>44319.33803240741</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>44273</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44321</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>44859</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>44176.66133101852</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>44225</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>44229</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>44574.45553240741</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>44165</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>44859</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>44265.69087962963</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>44278</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44676.551875</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>44859</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44859</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>44749</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>44574.43967592593</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>44602</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>44580</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>44602.57726851852</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>44217</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>44201</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>44201</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44088.78303240741</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>44859</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>44308</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44430.93283564815</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>44259</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>44795.48144675926</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>44757.40570601852</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>44124</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>44228</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>44225</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44228</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>44225</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>44887.43138888889</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>44588.6396875</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44088</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44505</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>44456</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>44207</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>44434</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>44375</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>44845</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>44375</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>44270.5584375</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>44364</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44497</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>44552.45563657407</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44201</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>44483.66988425926</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>44483.67144675926</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>44375</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>44503</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44475</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>44510</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44119</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>44376</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>44214</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44683.46200231482</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>44686</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>44803.35861111111</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>44887.42521990741</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>44607</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>44607</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>44343.88627314815</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>44887.42283564815</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44887.42663194444</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>44490.74336805556</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>44711.38366898148</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>44459</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>44610</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>44676.56075231481</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>44609</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>44089.35622685185</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>44522.60883101852</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>44375</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>44371</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>44253</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>44795.60174768518</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44795.60293981482</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>44242</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>44102</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         <v>44336.39239583333</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>44328.41473379629</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>44531</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12048,7 +12048,7 @@
         <v>44582</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>44837.43361111111</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>44250</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>44127</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>44424.57476851852</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>44470</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>44859</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>44158</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>44729.65407407407</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>44475.66188657407</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>44175</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>44207</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44788.47552083333</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>44574</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>44705</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44284</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>44120</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44175</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>44344.48678240741</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>44420.28219907408</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>44602</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>44393</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>44466</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>44603</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>44602</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>44592.48909722222</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>44524.46141203704</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>44757</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>44250</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>44690</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>44120</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
         <v>44285.87041666666</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>45697.97704861111</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>45736.32997685186</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45736.33076388889</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>45398.79873842592</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>44721.32116898148</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>44424.57810185185</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>44601.75174768519</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44154</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>45338</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>45338</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>45338.43358796297</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>45338</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45338</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45275.35230324074</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>44858.49122685185</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>45156.54523148148</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>44602.51873842593</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>45384.42409722223</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45708.35037037037</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>45709.40309027778</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>45642.47061342592</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>44496.58679398148</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>44697</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>44897.42872685185</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>45607.60341435186</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>45600.47440972222</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>45709.33226851852</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>45601</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>45517.38890046296</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>45273</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>45391.59185185185</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>45516.37174768518</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>44140</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>44526</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>44140</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45389.73820601852</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>45716.34217592593</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>45716.34775462963</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>45716.34298611111</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>45783.47896990741</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>45604.48214120371</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>45401.690625</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45761.93627314815</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>45761</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>45118.36900462963</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45783.38083333334</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>44915.41944444444</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>44790</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>45320</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>45454.73359953704</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         <v>45089</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>45674.38413194445</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>45338</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45338.43268518519</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>45590.39090277778</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>45664.57111111111</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>45622</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>45428.54546296296</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>45428.54791666667</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>45428.55520833333</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>45428.56197916667</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>45590</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>45775.49840277778</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45057</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>44922.50314814815</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45229.58863425926</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45389</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>45389</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>44167</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>44375</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>45476.50758101852</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>45229.49331018519</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45604.26549768518</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45610.35752314814</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>44430.29293981481</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>45098.44975694444</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>45770.625625</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>44524</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>45181</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>45502.49574074074</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>44610</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>45404</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>45668.63396990741</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>45165.77501157407</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>44285.33586805555</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>45737</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>45336</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45722.96171296296</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45755.41075231481</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>45488.46717592593</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>45568</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>45391.58608796296</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>44400</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>45786</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>45604.44618055555</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>45552.65006944445</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>45742</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45475</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>45639.59918981481</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>45428.57266203704</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45320.58873842593</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>45348</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45714.37306712963</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>45783</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>45736.32833333333</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20022,7 +20022,7 @@
         <v>45642.46802083333</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45385</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>44789.46129629629</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>45020</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>45525.6055787037</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>45471</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         <v>45688.63835648148</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>45709.38243055555</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>44308</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45728.59358796296</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>44523.4103587963</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>44097</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>45279.61047453704</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45544.36982638889</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>44327</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>44942.49850694444</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45408.61435185185</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45069.69295138889</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>45693</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>45693</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45440.6484375</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>45279.37215277777</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45792.81104166667</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>45791</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>45181</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>45226.45565972223</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>45389.74396990741</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>45190.47119212963</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>45764</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>45575.84530092592</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>45229</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>44757</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>45745.75537037037</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>45223.60331018519</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>44098</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>44468.65578703704</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>44468.68219907407</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>45709.42712962963</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>45098</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22285,7 +22285,7 @@
         <v>45754.55663194445</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>45749.46461805556</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>45720.40681712963</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>45749.46740740741</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>45019</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>45534</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>45233</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45140</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>45801.73608796296</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>45769.41568287037</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>45801.72324074074</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>45335.63466435186</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44524</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>45801.7406712963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>44369.46261574074</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>45245.37445601852</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23207,7 +23207,7 @@
         <v>44496</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>45155</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>45153</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>45801.7155324074</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45800.6135300926</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>45804</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>45506.59847222222</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>44985</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45273.615</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45805.59104166667</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>45804.40983796296</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>45350</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>45348</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23948,7 +23948,7 @@
         <v>45434.44790509259</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>44552.46184027778</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24062,7 +24062,7 @@
         <v>45629.38060185185</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>44971.76626157408</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>45804.49788194444</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45804</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>44566</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>45764</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>45807.45759259259</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>45764</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>45807.45905092593</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45807.46021990741</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>44278</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>44757.40493055555</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>44459.56224537037</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>45278.39707175926</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>45049</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>45140</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         <v>45308</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>45691.56284722222</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25108,7 +25108,7 @@
         <v>45348.33475694444</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>45567.53571759259</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>45105.47802083333</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>45474.36921296296</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>45692</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45093.34891203704</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>45595.77847222222</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45811.59519675926</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>45174</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>45041.59671296296</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>45041</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>44924.79619212963</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>44392.68070601852</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>44152</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>45547.6262037037</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>45547.62703703704</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>45709.39515046297</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>45709.40043981482</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26149,7 +26149,7 @@
         <v>45355.56142361111</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26206,7 +26206,7 @@
         <v>45709.39714120371</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26268,7 +26268,7 @@
         <v>44446</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>45400</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>45469.34783564815</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>45670.3792824074</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>45400</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>45149</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>45818</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>45440.63173611111</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>45338.43309027778</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
         <v>45615</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>45777.45011574074</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>45622</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         <v>45085</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         <v>45819.32747685185</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27091,7 +27091,7 @@
         <v>45819.46775462963</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27148,7 +27148,7 @@
         <v>44902.79445601852</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         <v>44924.77766203704</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>45597.38953703704</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>45174.34193287037</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>45113.36457175926</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>45117</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>45757.34662037037</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27552,7 +27552,7 @@
         <v>45579</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>45865.66577546296</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
         <v>45824.48737268519</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27728,7 +27728,7 @@
         <v>45351</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>45825.40163194444</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>45191</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>45642.47158564815</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>45865.67818287037</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>45825.58365740741</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>45706.36192129629</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>45734</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>45644.36364583333</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>45825.46516203704</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>45865</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>45826.49353009259</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>45826.37920138889</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28479,7 +28479,7 @@
         <v>45826.50130787037</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>45869.39628472222</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>45826.50511574074</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>45831.36230324074</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>45831.37613425926</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>45831.51181712963</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>45831.37420138889</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>45831</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>45831.5818287037</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>44858</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45832.47321759259</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45727.61247685185</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>45873</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>45835.37094907407</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>45835.48375</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>45875</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>45881</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>45838.67675925926</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>45877</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>45839</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>45435.77655092593</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>45881.4566087963</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>45838.37465277778</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>45839.58087962963</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>45839</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>45838.6196875</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>45841.74796296296</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>45230</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>45840.479375</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>45881.55119212963</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>45840.66209490741</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>45841.73791666667</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45295</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45749.75060185185</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30442,7 +30442,7 @@
         <v>45840.49215277778</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>45224</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>45349</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>45887.45643518519</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>45887.46554398148</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>45666</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>45842.47915509259</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30846,7 +30846,7 @@
         <v>45211.81873842593</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>45842.55467592592</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>45154.57079861111</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31017,7 +31017,7 @@
         <v>45114.65185185185</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>44153.45842592593</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>45162</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>45547.62819444444</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31245,7 +31245,7 @@
         <v>45164</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>45887.5765625</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31359,7 +31359,7 @@
         <v>45889.37565972222</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>45596.54981481482</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>44984</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>45757</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>45889.36107638889</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>45889.36693287037</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>44984</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31763,7 +31763,7 @@
         <v>45615</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31820,7 +31820,7 @@
         <v>45891.49868055555</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31877,7 +31877,7 @@
         <v>45459.71376157407</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>45428.5499537037</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45428.55199074074</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>45369.42203703704</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>45839</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>45082.56950231481</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32239,7 +32239,7 @@
         <v>45385.49137731481</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32296,7 +32296,7 @@
         <v>45894.59266203704</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>45891.49476851852</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32410,7 +32410,7 @@
         <v>45854.62081018519</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>45897.34547453704</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>45897</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>45897.44971064815</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>45897.35350694445</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32695,7 +32695,7 @@
         <v>45839</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>45897</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45085.53467592593</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
         <v>44945.39559027777</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>45375</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>45901.57252314815</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33037,7 +33037,7 @@
         <v>45604.56769675926</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>45901.31172453704</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>45901.31505787037</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>45898.39543981481</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>45597.3521412037</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>45597.35365740741</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>45901.44929398148</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45901.55628472222</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>44354</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>45861.43393518519</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>45861.42532407407</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>45902.78745370371</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>45454.73629629629</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>45230</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>45709.40560185185</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33917,7 +33917,7 @@
         <v>45902.56516203703</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>44858</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>45404.56375</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>45709.38748842593</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34150,7 +34150,7 @@
         <v>45709.42873842592</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>45385.44706018519</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45636.96761574074</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>44734.3744212963</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>44734.37710648148</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>45583.40994212963</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>45336.92125</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34559,7 +34559,7 @@
         <v>44942</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>44942.60704861111</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>45476</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>45904.48038194444</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34787,7 +34787,7 @@
         <v>45905.62797453703</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>45677.70096064815</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34901,7 +34901,7 @@
         <v>45164</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34958,7 +34958,7 @@
         <v>44208</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>45842.48019675926</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>45230.37582175926</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35139,7 +35139,7 @@
         <v>44592.72989583333</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>45546.60894675926</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35253,7 +35253,7 @@
         <v>45082</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35310,7 +35310,7 @@
         <v>45604.56190972222</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35372,7 +35372,7 @@
         <v>45604.56427083333</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>45604.56517361111</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44838</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45204</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>45107.61413194444</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35667,7 +35667,7 @@
         <v>45692.42515046296</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35724,7 +35724,7 @@
         <v>45568</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>45568</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45091</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>45118</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35967,7 +35967,7 @@
         <v>45005</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36024,7 +36024,7 @@
         <v>45692</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36086,7 +36086,7 @@
         <v>45705.35732638889</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>44994.45271990741</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>44396</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45219.44987268518</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36314,7 +36314,7 @@
         <v>45163.72633101852</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>44951</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>45370.64554398148</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36485,7 +36485,7 @@
         <v>45770</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36542,7 +36542,7 @@
         <v>45434.56020833334</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>45547.62391203704</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45547.62475694445</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36713,7 +36713,7 @@
         <v>45763.68868055556</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>45763.69137731481</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>45709.40761574074</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>45208.64244212963</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36956,7 +36956,7 @@
         <v>45688.58755787037</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>45770</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>45223</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37132,7 +37132,7 @@
         <v>45372.49736111111</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>45093</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45547.62553240741</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>44917.58131944444</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>45428.53717592593</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>45428.54854166666</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>45428.54914351852</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>45428.55339120371</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>45428.58675925926</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>45716.3528125</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37707,7 +37707,7 @@
         <v>45604.47792824074</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37764,7 +37764,7 @@
         <v>44154</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37821,7 +37821,7 @@
         <v>44984</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>44638.34265046296</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37935,7 +37935,7 @@
         <v>44865.54231481482</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37992,7 +37992,7 @@
         <v>45201.50586805555</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38049,7 +38049,7 @@
         <v>45506.60435185185</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>45184.46447916667</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>44603</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>44503.58450231481</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38277,7 +38277,7 @@
         <v>45211</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38334,7 +38334,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38391,7 +38391,7 @@
         <v>45103</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>44162</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>45261</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>45637.63881944444</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>44757.40103009259</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>44757.40538194445</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38748,7 +38748,7 @@
         <v>45028</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38805,7 +38805,7 @@
         <v>44124</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>45552.6449537037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>45552</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>44994.45623842593</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39033,7 +39033,7 @@
         <v>45204</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39090,7 +39090,7 @@
         <v>45338</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>45401.44325231481</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44844.67142361111</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>45112.3402199074</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>45232.72258101852</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>44229</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>45590.38761574074</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>45459.71949074074</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>45218</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>45028</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45105.48627314815</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45386.35322916666</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39794,7 +39794,7 @@
         <v>45688.43215277778</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39851,7 +39851,7 @@
         <v>45688.58667824074</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>45544.33987268519</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>45338</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>45338</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>45155</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>45366</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
         <v>44154</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>45219.79758101852</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40322,7 +40322,7 @@
         <v>45749</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>45428.55409722222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>45428.55619212963</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40498,7 +40498,7 @@
         <v>45709.32859953704</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>45761.93880787037</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>45428.53776620371</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40679,7 +40679,7 @@
         <v>44276</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>45597.34225694444</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>45597.38799768518</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40860,7 +40860,7 @@
         <v>45597.39101851852</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40922,7 +40922,7 @@
         <v>45354.72975694444</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40979,7 +40979,7 @@
         <v>45243</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41036,7 +41036,7 @@
         <v>45540.56981481481</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41093,7 +41093,7 @@
         <v>44844</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41150,7 +41150,7 @@
         <v>44711.38688657407</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41207,7 +41207,7 @@
         <v>45749</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41269,7 +41269,7 @@
         <v>44406</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41326,7 +41326,7 @@
         <v>45338</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41388,7 +41388,7 @@
         <v>44908</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>44160</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45372.49458333333</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45196.47457175926</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
         <v>45729.67947916667</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41683,7 +41683,7 @@
         <v>44140</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>45755.42104166667</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45755</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>44659.58702546296</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>45013</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41968,7 +41968,7 @@
         <v>44833</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45244.86136574074</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>44971.76994212963</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>44971.75834490741</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45579</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>44154</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>45211</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>45205.35776620371</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>44533.35804398148</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>45685.55012731482</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45063.27048611111</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
         <v>45245.7939699074</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>45455</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>45091</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>45692</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>44260</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>45428.57160879629</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>45428.57215277778</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>45597.34579861111</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>45597.34881944444</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43138,7 +43138,7 @@
         <v>45604.5687962963</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43200,7 +43200,7 @@
         <v>44881.54231481482</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43257,7 +43257,7 @@
         <v>45260.46252314815</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>44592.50912037037</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>44593</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43428,7 +43428,7 @@
         <v>45709.39251157407</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>45600.45402777778</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>45728</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>45229.53780092593</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43661,7 +43661,7 @@
         <v>44089.35689814815</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>45230</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43785,7 +43785,7 @@
         <v>44105</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43842,7 +43842,7 @@
         <v>45764</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43904,7 +43904,7 @@
         <v>45225</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>45679.50844907408</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44018,7 +44018,7 @@
         <v>44160</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45317</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45041</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44194,7 +44194,7 @@
         <v>45320.88226851852</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44251,7 +44251,7 @@
         <v>45075.50622685185</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44308,7 +44308,7 @@
         <v>45146</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44365,7 +44365,7 @@
         <v>45660</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44422,7 +44422,7 @@
         <v>45688</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45688.64506944444</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>44939</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>44939</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45357.39202546296</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>45716.33921296296</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44779,7 +44779,7 @@
         <v>45716.35056712963</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>44438</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44898,7 +44898,7 @@
         <v>45341.58440972222</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44960,7 +44960,7 @@
         <v>45692</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45017,7 +45017,7 @@
         <v>45702.36793981482</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45074,7 +45074,7 @@
         <v>45755</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>44124</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45188,7 +45188,7 @@
         <v>45233</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45245,7 +45245,7 @@
         <v>45338</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>44937</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45364,7 +45364,7 @@
         <v>44937.46436342593</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45421,7 +45421,7 @@
         <v>45195</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45478,7 +45478,7 @@
         <v>44361.93059027778</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45535,7 +45535,7 @@
         <v>45118</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45592,7 +45592,7 @@
         <v>45169.38462962963</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45649,7 +45649,7 @@
         <v>45146</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45706,7 +45706,7 @@
         <v>45146</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45763,7 +45763,7 @@
         <v>45716.34958333334</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>45720.41747685185</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45882,7 +45882,7 @@
         <v>45273.60899305555</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45939,7 +45939,7 @@
         <v>45273</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45996,7 +45996,7 @@
         <v>44887</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46053,7 +46053,7 @@
         <v>45204</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46110,7 +46110,7 @@
         <v>45085</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46167,7 +46167,7 @@
         <v>44410</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46224,7 +46224,7 @@
         <v>44882</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45407.5766087963</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46338,7 +46338,7 @@
         <v>45364.57331018519</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>45154.65458333334</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45530.36846064815</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>45460.82011574074</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>45607.37846064815</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>45561.37106481481</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>45764</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46742,7 +46742,7 @@
         <v>45764.84103009259</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>44593.63554398148</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46861,7 +46861,7 @@
         <v>45012</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46918,7 +46918,7 @@
         <v>45181</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46980,7 +46980,7 @@
         <v>44375</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47037,7 +47037,7 @@
         <v>45770.62311342593</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47094,7 +47094,7 @@
         <v>44153</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47151,7 +47151,7 @@
         <v>45642</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47208,7 +47208,7 @@
         <v>45324.40112268519</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47265,7 +47265,7 @@
         <v>45674.38553240741</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>45279</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45153</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47441,7 +47441,7 @@
         <v>45244.67376157407</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47498,7 +47498,7 @@
         <v>44946</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47555,7 +47555,7 @@
         <v>45204.42494212963</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>45154.56967592592</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         <v>45085</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>45428.57578703704</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47783,7 +47783,7 @@
         <v>45335.63689814815</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>44998.55319444444</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47922,7 +47922,7 @@
         <v>45604.48289351852</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47984,7 +47984,7 @@
         <v>45369.44256944444</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>44165</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48098,7 +48098,7 @@
         <v>45057</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48155,7 +48155,7 @@
         <v>44599</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48212,7 +48212,7 @@
         <v>45427.9417824074</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>44595.55912037037</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48326,7 +48326,7 @@
         <v>44757.39927083333</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>44757.40454861111</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>45001</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>44610</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45649.6427662037</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45264.6516087963</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45561.3744212963</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>44998</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48797,7 +48797,7 @@
         <v>45722.40604166667</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45604.56101851852</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48916,7 +48916,7 @@
         <v>45604.56623842593</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45604.56958333333</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49040,7 +49040,7 @@
         <v>45489.50666666667</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49097,7 +49097,7 @@
         <v>45288.46611111111</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45764.67251157408</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45747</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49278,7 +49278,7 @@
         <v>45747</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49335,7 +49335,7 @@
         <v>45190.39688657408</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49392,7 +49392,7 @@
         <v>45427.93607638889</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49449,7 +49449,7 @@
         <v>45428.55946759259</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49506,7 +49506,7 @@
         <v>45749.74931712963</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>45146</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49620,7 +49620,7 @@
         <v>44524.66444444445</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49677,7 +49677,7 @@
         <v>45538.80545138889</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>45428.5703587963</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49791,7 +49791,7 @@
         <v>45428.57371527778</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49848,7 +49848,7 @@
         <v>45009</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -567,7 +567,7 @@
         <v>45174</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         <v>44112</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44175</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44266</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45313</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45475</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>45604.4624537037</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>45158</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45840.46792824074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45195</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>44315</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>44455</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>44859</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45450.57783564815</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45517.34768518519</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45404.55137731481</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>45826.4996875</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45604.53089120371</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>44937</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>45103</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45889</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>45604.48800925926</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44833</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>44295</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44375</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>44827</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44950</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>44207</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45789.61961805556</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45791.44271990741</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>44384</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>44091</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44550</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>44998</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44663</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>44676</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>45623</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>44160</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45688.59202546296</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>45820.48319444444</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>45825</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>44132</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45335</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>44858</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>45688.41431712963</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45897.51854166666</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>44207</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>44243</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>44179.52865740741</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>44270.56321759259</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>44228</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>44155</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>44089</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>44267.64171296296</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>44320.42899305555</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>44386</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44386</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44865.57608796296</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>44887.42784722222</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>44887.42950231482</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>44307.45770833334</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>44508</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>44175</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44225</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>44201</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>44201</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>44201</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>44285</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>44201</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44524.32766203704</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44613.65383101852</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44483.4240625</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44193</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44225</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44447</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44202</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44242</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>44487</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44552.45428240741</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>44536</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>44461.68690972222</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>44574.4577662037</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>44510</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>44127</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44734.36189814815</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>44456</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>44273</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>44321</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>44812.51043981482</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>44319.33803240741</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44859</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>44176.66133101852</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>44225</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44229</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>44574.45553240741</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>44165</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>44265.69087962963</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>44278</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>44859</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>44676.551875</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44859</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>44859</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44749</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>44574.43967592593</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>44602</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>44580</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>44602.57726851852</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>44217</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>44088.78303240741</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>44201</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>44201</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44859</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>44308</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>44259</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44795.48144675926</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>44757.40570601852</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44430.93283564815</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>44124</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>44228</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>44225</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>44228</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44225</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>44887.43138888889</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>44588.6396875</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>44088</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44505</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44456</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>44207</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>44434</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>44375</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>44845</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>44270.5584375</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44364</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>44375</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>44497</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44201</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>44552.45563657407</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44483.66988425926</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>44483.67144675926</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>44503</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>44375</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>44475</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44510</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>44119</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44376</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>44214</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>44602.51873842593</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44721.32116898148</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>44424.57810185185</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>44683.46200231482</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>44686</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>44803.35861111111</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>44887.42521990741</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>44711.38366898148</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>44343.88627314815</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44459</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>44610</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44089.35622685185</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>44522.60883101852</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>44531</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>44609</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>44607</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>44607</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>44253</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>44887.42283564815</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>44887.42663194444</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>44375</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>44490.74336805556</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>44424.57476851852</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>44470</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>44371</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         <v>44795.60174768518</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>44795.60293981482</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>44336.39239583333</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>44242</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>44102</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>44328.41473379629</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>44837.43361111111</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>44582</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>44676.56075231481</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>44729.65407407407</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>44859</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>44158</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>44788.47552083333</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>44705</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>44175</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>44207</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>44120</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>44602</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>44393</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>44592.48909722222</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>44757</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>44120</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>45385.49137731481</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>45041.59671296296</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>45041</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>44308</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>44285.87041666666</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>45338</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>45338</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>45338</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>44250</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>44127</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45709.38748842593</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>45709.39251157407</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>45091</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>45709.38243055555</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>45208.64244212963</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>45391.58608796296</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>44276</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>45190.39688657408</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>44354</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>44833</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>45338</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>45338</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>45770.62311342593</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>45335.63689814815</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14584,7 +14584,7 @@
         <v>45341.58440972222</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>44285.33586805555</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44601.75174768519</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44858.49122685185</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45775.49840277778</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>45697.97704861111</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>45165.77501157407</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>45245.37445601852</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>44524.66444444445</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>44503.58450231481</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45348</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>45348</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44475.66188657407</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>45001</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44400</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>45749.46740740741</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>45400</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>45709.42712962963</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>45506.59847222222</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45685.55012731482</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15739,7 +15739,7 @@
         <v>45288.46611111111</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45639.59918981481</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45335.63466435186</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>45642.46802083333</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         <v>45082.56950231481</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45428.55619212963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>45384.42409722223</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>44757.39927083333</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>44757.40454861111</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>44396</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>44496</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>45489.50666666667</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>44153</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45642.47061342592</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45391.59185185185</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>45600.47440972222</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>45273</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>45561.37106481481</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>45601</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>45516.37174768518</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>45568</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>45568</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45517.38890046296</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>45471</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44526</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44140</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44140</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45709.33226851852</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>45400</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45229.49331018519</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>45320</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>45716.34298611111</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45716.34217592593</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>45716.34775462963</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>45389</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45389</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>45279.37215277777</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>45454.73629629629</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45348.33475694444</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>45783.47896990741</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>44998</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45103</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>45140</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>45181</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>45440.6484375</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>45607.37846064815</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>45469.34783564815</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45428.5499537037</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>45428.55199074074</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45488.46717592593</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>44574</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>45502.49574074074</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>45386.35322916666</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>45153</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>45692</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>45530.36846064815</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45742</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>45476.50758101852</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45720.41747685185</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>44430.29293981481</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>45786</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>45140</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>45552.65006944445</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>44984</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>44284</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45229</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45279.61047453704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>44790</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45728.59358796296</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>45604.44618055555</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45389.74396990741</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>44175</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>44344.48678240741</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>44420.28219907408</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45154.57079861111</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>45162</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>45154.56967592592</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>44466</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>45736.32833333333</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44603</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>44602</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>44524</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>44524</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20580,7 +20580,7 @@
         <v>45146</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45783</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45506.60435185185</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45590.39090277778</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45428.53776620371</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>45118</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>45355.56142361111</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>44438</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>45370.64554398148</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>45544.33987268519</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>44153.45842592593</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45428.54791666667</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>45428.53717592593</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45428.54854166666</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>45428.54914351852</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>45428.55339120371</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>45428.58675925926</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>45622</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>44124</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>45544.36982638889</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>45204.42494212963</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44105</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>44524.46141203704</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>45597.34225694444</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>45610.35752314814</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45604.48289351852</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>44659.58702546296</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>45336.92125</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45579</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>45428.54546296296</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>45338.43309027778</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>45749.75060185185</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>44690</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>44610</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>45474.36921296296</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22652,7 +22652,7 @@
         <v>45089</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45191</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45720.40681712963</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>45534</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45642.47158564815</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>45800.6135300926</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>45540.56981481481</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23061,7 +23061,7 @@
         <v>45801.7406712963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>45597.38799768518</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23180,7 +23180,7 @@
         <v>45597.39101851852</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>45804</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>45804.49788194444</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44592.50912037037</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44844</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44858</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>45804.40983796296</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23584,7 +23584,7 @@
         <v>45801.72324074074</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>45801.7155324074</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45804</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>45801.73608796296</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>45372.49736111111</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>45764</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>45674.38413194445</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>45567.53571759259</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24050,7 +24050,7 @@
         <v>45440.63173611111</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>44140</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>45169.38462962963</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45049</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>45218</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>45729.67947916667</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24392,7 +24392,7 @@
         <v>45372.49458333333</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24449,7 +24449,7 @@
         <v>45805.59104166667</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>45764</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44599</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>44593</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>45196.47457175926</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>45404.56375</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>45476</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>44152</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>45366</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>44154</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25024,7 +25024,7 @@
         <v>45677.70096064815</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45547.6262037037</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25138,7 +25138,7 @@
         <v>45807.45759259259</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25195,7 +25195,7 @@
         <v>45223</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>44154</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>45098.44975694444</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>44566</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>45749.46461805556</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>45664.57111111111</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>45435.77655092593</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>45057</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>45117</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>45604.56101851852</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>45604.56190972222</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>45604.56958333333</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45807.45905092593</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>45807.46021990741</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>45552.6449537037</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45552</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>44154</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45211</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45811.59519675926</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>45688.58667824074</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>45747</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45107.61413194444</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>45747</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>45195</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>45113.36457175926</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>45013</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>45755.41075231481</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>45709.39714120371</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>45709.39515046297</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>45709.40043981482</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>45757</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>44942</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45692</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>45184.46447916667</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45777.45011574074</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45233</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>45211.81873842593</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45757.34662037037</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>45211</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45818</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>45085</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45146</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45649.6427662037</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45459.71376157407</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>44942.60704861111</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>45320.58873842593</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>45709.32859953704</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45709.40761574074</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>44592.72989583333</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>45819.32747685185</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>45688.58755787037</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>45688.63835648148</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>45819.46775462963</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>45153</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>45174</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         <v>45408.61435185185</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>45338.43358796297</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>45338</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28591,7 +28591,7 @@
         <v>45338</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>45230</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>45604.5687962963</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>44985</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28834,7 +28834,7 @@
         <v>45824.48737268519</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>45644.36364583333</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28948,7 +28948,7 @@
         <v>45688.43215277778</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29005,7 +29005,7 @@
         <v>45579</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>44250</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>45826.50130787037</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>44757</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45404</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>45826.37920138889</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>45826.50511574074</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>45825.40163194444</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>45825.58365740741</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>45825.46516203704</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>45826.49353009259</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45636.96761574074</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>45204</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>45702.36793981482</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>45769.41568287037</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>45722.40604166667</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>45831.5818287037</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>45831</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45389.73820601852</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45597.35365740741</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45832.47321759259</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>45831.37613425926</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45873</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>45831.36230324074</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>45155</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>45243</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>45831.37420138889</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>45763.68868055556</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>45763.69137731481</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>45831.51181712963</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30745,7 +30745,7 @@
         <v>44915.41944444444</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>45223.60331018519</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>44945.39559027777</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>45875</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>45063.27048611111</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>45597.3521412037</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45770</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>45336</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>45770</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45835.37094907407</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>44858</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31377,7 +31377,7 @@
         <v>44229</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>45278.39707175926</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>45009</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>44923</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>45629.38060185185</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>45838.67675925926</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>45838.6196875</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>45727.61247685185</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>44757.40103009259</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>44757.40538194445</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>45273.615</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>45835.48375</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>45230</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>45734</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>45351</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>45881.4566087963</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>45093</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45604.56769675926</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45604.48214120371</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>45264.6516087963</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>45295</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>44939</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>44939</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>45317</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32790,7 +32790,7 @@
         <v>44984</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32847,7 +32847,7 @@
         <v>44984</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32904,7 +32904,7 @@
         <v>44971.75834490741</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>45075.50622685185</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>44496.58679398148</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>44971.76626157408</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>45839</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>45840.479375</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45877</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45354.72975694444</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33360,7 +33360,7 @@
         <v>45881</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>45460.82011574074</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33474,7 +33474,7 @@
         <v>45324.40112268519</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45041</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>45838.37465277778</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>45279</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>45839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>45840.66209490741</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>45547.62553240741</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>44523.4103587963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33930,7 +33930,7 @@
         <v>45475</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33987,7 +33987,7 @@
         <v>45163.72633101852</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>45181</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>45357.39202546296</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>45615</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45840.49215277778</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>44603</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34329,7 +34329,7 @@
         <v>45604.26549768518</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>45597.38953703704</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>45118</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>45693</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>45693</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>45881.55119212963</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>45839.58087962963</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>44278</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>45146</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>45146</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>44208</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>45320.88226851852</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45692</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>45201.50586805555</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>44406</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>45028</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>45230</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>45692</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>45666</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>44924.77766203704</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>44369.46261574074</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>45637.63881944444</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45219.44987268518</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35665,7 +35665,7 @@
         <v>45764.67251157408</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>44410</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>45224</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>45841.73791666667</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>45205.35776620371</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>44757.40493055555</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36017,7 +36017,7 @@
         <v>45688</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>45688.64506944444</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44361.93059027778</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>45155</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45273.60899305555</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>45273</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>45622</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>45233</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>45755</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>45761.93627314815</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>45761</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>45745.75537037037</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>45749</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45028</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45244.86136574074</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>44097</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>44160</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>45709.40309027778</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>45308</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>45538.80545138889</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>45547.62391203704</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45547.62475694445</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>45841.74796296296</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>44375</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>44881.54231481482</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>44924.79619212963</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45012</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>45525.6055787037</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>45764</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45764.84103009259</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45716.33921296296</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45112.3402199074</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>45670.3792824074</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>44844.67142361111</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>45842.47915509259</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>45764</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>44392.68070601852</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>45706.36192129629</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38238,7 +38238,7 @@
         <v>45736.32997685186</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38300,7 +38300,7 @@
         <v>45736.33076388889</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>45085</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38419,7 +38419,7 @@
         <v>45583.40994212963</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>45770.625625</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         <v>45842.55467592592</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>44922.50314814815</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45755</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>44882</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>44971.76994212963</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38818,7 +38818,7 @@
         <v>45887.45643518519</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45887.46554398148</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45349</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45705.35732638889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45082</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39103,7 +39103,7 @@
         <v>44468.68219907407</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39160,7 +39160,7 @@
         <v>44446</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>45114.65185185185</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>44162</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39331,7 +39331,7 @@
         <v>45181</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>45407.5766087963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>45385</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44937</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>44937.46436342593</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45385.44706018519</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>44124</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>44917.58131944444</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>45547.62819444444</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45547.62703703704</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>45887.5765625</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>44838</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>45338</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>45338.43268518519</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>45889.36693287037</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>45093.34891203704</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>45596.54981481482</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45679.50844907408</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>44897.42872685185</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>45889.37565972222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>45716.35056712963</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40558,7 +40558,7 @@
         <v>45889.36107638889</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>44459.56224537037</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40672,7 +40672,7 @@
         <v>44951</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         <v>45590.38761574074</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>44946</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40843,7 +40843,7 @@
         <v>45369.42203703704</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>45561.3744212963</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40957,7 +40957,7 @@
         <v>44160</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41014,7 +41014,7 @@
         <v>45261</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>44552.46184027778</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41133,7 +41133,7 @@
         <v>45894.59266203704</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>44595.55912037037</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>44533.35804398148</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>45891.49868055555</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>45891.49476851852</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>45164</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>44638.34265046296</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>45854.62081018519</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>45230.37582175926</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>45898.39543981481</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>45897</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41765,7 +41765,7 @@
         <v>44089.35689814815</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>44887</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>44468.65578703704</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>45428.57578703704</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>45897.35350694445</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45897.34547453704</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>45398.79873842592</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45897</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45897.44971064815</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45204</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42340,7 +42340,7 @@
         <v>45901.57252314815</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>45709.40560185185</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45607.60341435186</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>45901.44929398148</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42573,7 +42573,7 @@
         <v>45595.77847222222</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>45901.55628472222</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>45901.31505787037</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>45546.60894675926</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42801,7 +42801,7 @@
         <v>45901.31172453704</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>45604.47792824074</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>45902.78745370371</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>45904.48038194444</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43029,7 +43029,7 @@
         <v>45226.45565972223</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43086,7 +43086,7 @@
         <v>45861.43393518519</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43143,7 +43143,7 @@
         <v>45455</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>45232.72258101852</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43262,7 +43262,7 @@
         <v>45861.42532407407</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>45842.48019675926</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>45568</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>45275.35230324074</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43495,7 +43495,7 @@
         <v>45902.56516203703</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>45792.81104166667</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>45245.7939699074</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>44711.38688657407</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>44994.45623842593</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43780,7 +43780,7 @@
         <v>45908.39239583333</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43837,7 +43837,7 @@
         <v>45865.67818287037</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>44902.79445601852</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>45428.55520833333</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44008,7 +44008,7 @@
         <v>45908.51197916667</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44065,7 +44065,7 @@
         <v>45674.38553240741</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>45865</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44184,7 +44184,7 @@
         <v>45174.34193287037</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>45597.34579861111</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44303,7 +44303,7 @@
         <v>45597.34881944444</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44365,7 +44365,7 @@
         <v>45600.45402777778</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44422,7 +44422,7 @@
         <v>44908</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45865.66577546296</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>44697</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45905.62797453703</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45737</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>45069.69295138889</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>45910.50434027778</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45020</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44893,7 +44893,7 @@
         <v>45910.6044212963</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44950,7 +44950,7 @@
         <v>44260</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>45668.63396990741</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45064,7 +45064,7 @@
         <v>45910.6277662037</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45121,7 +45121,7 @@
         <v>45910.63862268518</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45178,7 +45178,7 @@
         <v>45260.46252314815</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         <v>45909</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45292,7 +45292,7 @@
         <v>44865.54231481482</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         <v>45839</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45406,7 +45406,7 @@
         <v>45839</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45483,7 +45483,7 @@
         <v>45869.39628472222</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45540,7 +45540,7 @@
         <v>45156.54523148148</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45597,7 +45597,7 @@
         <v>45369.44256944444</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45654,7 +45654,7 @@
         <v>44375</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45711,7 +45711,7 @@
         <v>45434.56020833334</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45768,7 +45768,7 @@
         <v>45375</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>45427.93607638889</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45882,7 +45882,7 @@
         <v>45225</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45939,7 +45939,7 @@
         <v>45350</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45996,7 +45996,7 @@
         <v>44998.55319444444</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46073,7 +46073,7 @@
         <v>45428.55946759259</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>45428.5703587963</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46187,7 +46187,7 @@
         <v>45428.57371527778</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>45691.56284722222</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>45454.73359953704</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>45118.36900462963</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46415,7 +46415,7 @@
         <v>44593.63554398148</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46472,7 +46472,7 @@
         <v>45105.48627314815</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>45164</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46586,7 +46586,7 @@
         <v>45615</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>44165</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46700,7 +46700,7 @@
         <v>45105.47802083333</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46757,7 +46757,7 @@
         <v>45244.67376157407</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>45755.42104166667</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>45749</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46933,7 +46933,7 @@
         <v>45764</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46995,7 +46995,7 @@
         <v>45459.71949074074</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47052,7 +47052,7 @@
         <v>45005</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47109,7 +47109,7 @@
         <v>44098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47166,7 +47166,7 @@
         <v>45098</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47223,7 +47223,7 @@
         <v>45590</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47280,7 +47280,7 @@
         <v>45604.56427083333</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47342,7 +47342,7 @@
         <v>45604.56517361111</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47404,7 +47404,7 @@
         <v>45761.93880787037</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47466,7 +47466,7 @@
         <v>45604.56623842593</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47528,7 +47528,7 @@
         <v>45190.47119212963</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         <v>45708.35037037037</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47642,7 +47642,7 @@
         <v>45692.42515046296</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>44327</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>45229.53780092593</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>45091</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>45085</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>45749.74931712963</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>45716.34958333334</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48108,7 +48108,7 @@
         <v>44994.45271990741</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>45660</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>44610</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48279,7 +48279,7 @@
         <v>45149</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>44942.49850694444</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>44789.46129629629</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>45219.79758101852</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45085.53467592593</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>44154</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45427.9417824074</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45428.57160879629</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45338</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48797,7 +48797,7 @@
         <v>45338</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48859,7 +48859,7 @@
         <v>45716.3528125</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>45019</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45642</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>45714.37306712963</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45575.84530092592</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45057</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45154.65458333334</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45728</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45722.96171296296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45434.44790509259</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49434,7 +49434,7 @@
         <v>45709.42873842592</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>45229.58863425926</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>44734.3744212963</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>44734.37710648148</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -567,7 +567,7 @@
         <v>45174</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         <v>44112</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44175</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44266</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45313</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45475</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>45604.4624537037</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>45158</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45840.46792824074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45195</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>44315</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>44455</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>44859</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45450.57783564815</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45517.34768518519</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45404.55137731481</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>45826.4996875</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45604.53089120371</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>44937</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>45103</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45889</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>45604.48800925926</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44833</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>44295</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44375</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>44827</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44950</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>44207</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45789.61961805556</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45791.44271990741</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>44384</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>44091</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44550</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>44998</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44663</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>44676</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>45623</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>44160</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45688.59202546296</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>45820.48319444444</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>45825</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>44132</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45335</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>44858</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>45688.41431712963</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45897.51854166666</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>44207</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>44243</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>44179.52865740741</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>44270.56321759259</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>44228</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>44155</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>44089</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>44267.64171296296</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>44320.42899305555</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>44386</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44386</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44865.57608796296</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>44887.42784722222</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>44887.42950231482</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>44307.45770833334</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>44508</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>44175</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44225</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>44201</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>44201</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>44201</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>44285</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>44201</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44524.32766203704</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44613.65383101852</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44483.4240625</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44193</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44225</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44447</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44202</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44242</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>44487</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44552.45428240741</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>44536</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>44461.68690972222</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>44574.4577662037</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>44510</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>44127</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44734.36189814815</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>44456</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>44273</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>44321</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>44812.51043981482</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>44319.33803240741</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44859</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>44176.66133101852</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>44225</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44229</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>44574.45553240741</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>44165</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>44265.69087962963</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>44278</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>44859</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>44676.551875</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44859</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>44859</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44749</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>44574.43967592593</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>44602</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>44580</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>44602.57726851852</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>44217</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>44088.78303240741</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>44201</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>44201</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44859</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>44308</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>44259</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44795.48144675926</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>44757.40570601852</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44430.93283564815</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>44124</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>44228</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>44225</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>44228</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44225</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>44887.43138888889</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>44588.6396875</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>44088</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44505</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44456</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>44207</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>44434</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>44375</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>44845</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>44270.5584375</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44364</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>44375</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>44497</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44201</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>44552.45563657407</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44483.66988425926</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>44483.67144675926</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>44503</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>44375</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>44475</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44510</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>44119</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44376</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>44214</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>44602.51873842593</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44721.32116898148</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>44424.57810185185</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>44683.46200231482</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>44686</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>44803.35861111111</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>44887.42521990741</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>44711.38366898148</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>44343.88627314815</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44459</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>44610</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44089.35622685185</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>44522.60883101852</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>44531</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>44609</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>44607</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>44607</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>44253</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>44887.42283564815</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>44887.42663194444</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>44375</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>44490.74336805556</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>44424.57476851852</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>44470</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>44371</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         <v>44795.60174768518</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>44795.60293981482</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>44336.39239583333</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>44242</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>44102</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>44328.41473379629</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>44837.43361111111</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>44582</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>44676.56075231481</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>44729.65407407407</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>44859</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>44158</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>44788.47552083333</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>44705</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>44175</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>44207</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>44120</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>44602</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>44393</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>44592.48909722222</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>44757</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>44120</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>45385.49137731481</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>45041.59671296296</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>45041</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>44308</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>44285.87041666666</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>45338</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>45338</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>45338</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>44250</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>44127</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45709.38748842593</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>45709.39251157407</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>45091</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>45709.38243055555</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>45208.64244212963</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>45391.58608796296</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>44276</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>45190.39688657408</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>44354</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>44833</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>45338</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>45338</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>45770.62311342593</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>45335.63689814815</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14584,7 +14584,7 @@
         <v>45341.58440972222</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>44285.33586805555</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44601.75174768519</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44858.49122685185</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45775.49840277778</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>45697.97704861111</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>45165.77501157407</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>45245.37445601852</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>44524.66444444445</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>44503.58450231481</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45348</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>45348</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44475.66188657407</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>45001</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44400</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>45749.46740740741</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>45400</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>45709.42712962963</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>45506.59847222222</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45685.55012731482</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15739,7 +15739,7 @@
         <v>45288.46611111111</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45639.59918981481</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45335.63466435186</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>45642.46802083333</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         <v>45082.56950231481</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45428.55619212963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>45384.42409722223</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>44757.39927083333</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>44757.40454861111</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>44396</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>44496</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>45489.50666666667</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>44153</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45642.47061342592</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45391.59185185185</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>45600.47440972222</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>45273</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>45561.37106481481</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>45601</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>45516.37174768518</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>45568</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>45568</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45517.38890046296</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>45471</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44526</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44140</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44140</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45709.33226851852</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>45400</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45229.49331018519</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>45320</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>45716.34298611111</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45716.34217592593</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>45716.34775462963</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>45389</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45389</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>45279.37215277777</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>45454.73629629629</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45348.33475694444</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>45783.47896990741</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>44998</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45103</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>45140</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>45181</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>45440.6484375</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>45607.37846064815</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>45469.34783564815</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45428.5499537037</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>45428.55199074074</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45488.46717592593</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>44574</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>45502.49574074074</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>45386.35322916666</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>45153</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>45692</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>45530.36846064815</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45742</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>45476.50758101852</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45720.41747685185</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>44430.29293981481</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>45786</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>45140</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>45552.65006944445</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>44984</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>44284</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45229</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45279.61047453704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>44790</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45728.59358796296</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>45604.44618055555</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45389.74396990741</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>44175</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>44344.48678240741</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>44420.28219907408</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45154.57079861111</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>45162</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>45154.56967592592</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>44466</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>45736.32833333333</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44603</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>44602</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>44524</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>44524</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20580,7 +20580,7 @@
         <v>45146</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45783</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45506.60435185185</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45590.39090277778</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45428.53776620371</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>45118</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>45355.56142361111</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>44438</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>45370.64554398148</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>45544.33987268519</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>44153.45842592593</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45428.54791666667</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>45428.53717592593</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45428.54854166666</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>45428.54914351852</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>45428.55339120371</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>45428.58675925926</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>45622</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>44124</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>45544.36982638889</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>45204.42494212963</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44105</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>44524.46141203704</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>45597.34225694444</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>45610.35752314814</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45604.48289351852</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>44659.58702546296</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>45336.92125</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45579</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>45428.54546296296</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>45338.43309027778</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>45749.75060185185</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>44690</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>44610</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>45474.36921296296</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22652,7 +22652,7 @@
         <v>45089</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45191</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45720.40681712963</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>45534</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45642.47158564815</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>45800.6135300926</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>45540.56981481481</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23061,7 +23061,7 @@
         <v>45801.7406712963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>45597.38799768518</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23180,7 +23180,7 @@
         <v>45597.39101851852</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>45804</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>45804.49788194444</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44592.50912037037</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44844</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44858</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>45804.40983796296</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23584,7 +23584,7 @@
         <v>45801.72324074074</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>45801.7155324074</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45804</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>45801.73608796296</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>45372.49736111111</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>45764</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>45674.38413194445</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>45567.53571759259</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24050,7 +24050,7 @@
         <v>45440.63173611111</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>44140</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>45169.38462962963</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45049</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>45218</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>45729.67947916667</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24392,7 +24392,7 @@
         <v>45372.49458333333</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24449,7 +24449,7 @@
         <v>45805.59104166667</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>45764</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44599</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>44593</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>45196.47457175926</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>45404.56375</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>45476</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>44152</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>45366</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>44154</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25024,7 +25024,7 @@
         <v>45677.70096064815</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45547.6262037037</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25138,7 +25138,7 @@
         <v>45807.45759259259</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25195,7 +25195,7 @@
         <v>45223</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>44154</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>45098.44975694444</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>44566</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>45749.46461805556</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>45664.57111111111</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>45435.77655092593</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>45057</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>45117</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>45604.56101851852</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>45604.56190972222</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>45604.56958333333</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45807.45905092593</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>45807.46021990741</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>45552.6449537037</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45552</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>44154</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45211</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45811.59519675926</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>45688.58667824074</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>45747</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45107.61413194444</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>45747</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>45195</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>45113.36457175926</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>45013</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>45755.41075231481</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>45709.39714120371</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>45709.39515046297</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>45709.40043981482</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>45757</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>44942</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45692</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>45184.46447916667</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45777.45011574074</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45233</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>45211.81873842593</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45757.34662037037</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>45211</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45818</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>45085</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45146</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45649.6427662037</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45459.71376157407</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>44942.60704861111</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>45320.58873842593</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>45709.32859953704</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45709.40761574074</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>44592.72989583333</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>45819.32747685185</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>45688.58755787037</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>45688.63835648148</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>45819.46775462963</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>45153</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>45174</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         <v>45408.61435185185</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>45338.43358796297</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>45338</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28591,7 +28591,7 @@
         <v>45338</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>45230</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>45604.5687962963</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>44985</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28834,7 +28834,7 @@
         <v>45824.48737268519</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>45644.36364583333</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28948,7 +28948,7 @@
         <v>45688.43215277778</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29005,7 +29005,7 @@
         <v>45579</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>44250</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>45826.50130787037</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>44757</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45404</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>45826.37920138889</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>45826.50511574074</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>45825.40163194444</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>45825.58365740741</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>45825.46516203704</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>45826.49353009259</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45636.96761574074</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>45204</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>45702.36793981482</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>45769.41568287037</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>45722.40604166667</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>45831.5818287037</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>45831</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45389.73820601852</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45597.35365740741</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45832.47321759259</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>45831.37613425926</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45873</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>45831.36230324074</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>45155</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>45243</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>45831.37420138889</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>45763.68868055556</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>45763.69137731481</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>45831.51181712963</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30745,7 +30745,7 @@
         <v>44915.41944444444</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>45223.60331018519</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>44945.39559027777</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>45875</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>45063.27048611111</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>45597.3521412037</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45770</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>45336</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>45770</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45835.37094907407</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>44858</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31377,7 +31377,7 @@
         <v>44229</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>45278.39707175926</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>45009</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>44923</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>45629.38060185185</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>45838.67675925926</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>45838.6196875</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>45727.61247685185</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>44757.40103009259</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>44757.40538194445</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>45273.615</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>45835.48375</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>45230</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>45734</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>45351</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>45881.4566087963</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>45093</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45604.56769675926</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45604.48214120371</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>45264.6516087963</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>45295</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>44939</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>44939</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>45317</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32790,7 +32790,7 @@
         <v>44984</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32847,7 +32847,7 @@
         <v>44984</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32904,7 +32904,7 @@
         <v>44971.75834490741</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>45075.50622685185</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>44496.58679398148</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>44971.76626157408</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>45839</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>45840.479375</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45877</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45354.72975694444</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33360,7 +33360,7 @@
         <v>45881</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>45460.82011574074</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33474,7 +33474,7 @@
         <v>45324.40112268519</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45041</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>45838.37465277778</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>45279</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>45839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>45840.66209490741</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>45547.62553240741</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>44523.4103587963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33930,7 +33930,7 @@
         <v>45475</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33987,7 +33987,7 @@
         <v>45163.72633101852</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>45181</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>45357.39202546296</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>45615</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45840.49215277778</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>44603</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34329,7 +34329,7 @@
         <v>45604.26549768518</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>45597.38953703704</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>45118</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>45693</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>45693</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>45881.55119212963</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>45839.58087962963</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>44278</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>45146</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>45146</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>44208</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>45320.88226851852</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45692</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>45201.50586805555</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>44406</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>45028</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>45230</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>45692</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>45666</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>44924.77766203704</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>44369.46261574074</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>45637.63881944444</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45219.44987268518</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35665,7 +35665,7 @@
         <v>45764.67251157408</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>44410</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>45224</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>45841.73791666667</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>45205.35776620371</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>44757.40493055555</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36017,7 +36017,7 @@
         <v>45688</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>45688.64506944444</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44361.93059027778</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>45155</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45273.60899305555</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>45273</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>45622</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>45233</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>45755</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>45761.93627314815</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>45761</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>45745.75537037037</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>45749</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45028</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45244.86136574074</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>44097</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>44160</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>45709.40309027778</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>45308</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>45538.80545138889</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>45547.62391203704</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45547.62475694445</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>45841.74796296296</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>44375</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>44881.54231481482</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>44924.79619212963</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45012</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>45525.6055787037</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>45764</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45764.84103009259</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45716.33921296296</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45112.3402199074</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>45670.3792824074</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>44844.67142361111</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>45842.47915509259</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>45764</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>44392.68070601852</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>45706.36192129629</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38238,7 +38238,7 @@
         <v>45736.32997685186</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38300,7 +38300,7 @@
         <v>45736.33076388889</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>45085</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38419,7 +38419,7 @@
         <v>45583.40994212963</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>45770.625625</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         <v>45842.55467592592</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>44922.50314814815</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45755</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>44882</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>44971.76994212963</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38818,7 +38818,7 @@
         <v>45887.45643518519</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45887.46554398148</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45349</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45705.35732638889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45082</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39103,7 +39103,7 @@
         <v>44468.68219907407</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39160,7 +39160,7 @@
         <v>44446</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>45114.65185185185</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>44162</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39331,7 +39331,7 @@
         <v>45181</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>45407.5766087963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>45385</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44937</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>44937.46436342593</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45385.44706018519</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>44124</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>44917.58131944444</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>45547.62819444444</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45547.62703703704</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>45887.5765625</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>44838</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>45338</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>45338.43268518519</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>45889.36693287037</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>45093.34891203704</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>45596.54981481482</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45679.50844907408</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>44897.42872685185</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>45889.37565972222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>45716.35056712963</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40558,7 +40558,7 @@
         <v>45889.36107638889</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>44459.56224537037</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40672,7 +40672,7 @@
         <v>44951</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         <v>45590.38761574074</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>44946</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40843,7 +40843,7 @@
         <v>45369.42203703704</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>45561.3744212963</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40957,7 +40957,7 @@
         <v>44160</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41014,7 +41014,7 @@
         <v>45261</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>44552.46184027778</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41133,7 +41133,7 @@
         <v>45894.59266203704</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>44595.55912037037</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>44533.35804398148</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>45891.49868055555</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>45891.49476851852</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>45164</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>44638.34265046296</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>45854.62081018519</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>45230.37582175926</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>45898.39543981481</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>45897</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41765,7 +41765,7 @@
         <v>44089.35689814815</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>44887</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>44468.65578703704</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>45428.57578703704</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>45897.35350694445</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45897.34547453704</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>45398.79873842592</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45897</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45897.44971064815</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45204</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42340,7 +42340,7 @@
         <v>45901.57252314815</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>45709.40560185185</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45607.60341435186</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>45901.44929398148</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42573,7 +42573,7 @@
         <v>45595.77847222222</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>45901.55628472222</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>45901.31505787037</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>45546.60894675926</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42801,7 +42801,7 @@
         <v>45901.31172453704</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>45604.47792824074</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>45902.78745370371</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>45904.48038194444</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43029,7 +43029,7 @@
         <v>45226.45565972223</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43086,7 +43086,7 @@
         <v>45861.43393518519</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43143,7 +43143,7 @@
         <v>45455</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>45232.72258101852</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43262,7 +43262,7 @@
         <v>45861.42532407407</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>45842.48019675926</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>45568</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>45275.35230324074</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43495,7 +43495,7 @@
         <v>45902.56516203703</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>45792.81104166667</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>45245.7939699074</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>44711.38688657407</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>44994.45623842593</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43780,7 +43780,7 @@
         <v>45908.39239583333</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43837,7 +43837,7 @@
         <v>45865.67818287037</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>44902.79445601852</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>45428.55520833333</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44008,7 +44008,7 @@
         <v>45908.51197916667</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44065,7 +44065,7 @@
         <v>45674.38553240741</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>45865</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44184,7 +44184,7 @@
         <v>45174.34193287037</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>45597.34579861111</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44303,7 +44303,7 @@
         <v>45597.34881944444</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44365,7 +44365,7 @@
         <v>45600.45402777778</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44422,7 +44422,7 @@
         <v>44908</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45865.66577546296</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>44697</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45905.62797453703</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45737</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>45069.69295138889</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>45910.50434027778</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45020</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44893,7 +44893,7 @@
         <v>45910.6044212963</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44950,7 +44950,7 @@
         <v>44260</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>45668.63396990741</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45064,7 +45064,7 @@
         <v>45910.6277662037</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45121,7 +45121,7 @@
         <v>45910.63862268518</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45178,7 +45178,7 @@
         <v>45260.46252314815</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         <v>45909</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45292,7 +45292,7 @@
         <v>44865.54231481482</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         <v>45839</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45406,7 +45406,7 @@
         <v>45839</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45483,7 +45483,7 @@
         <v>45869.39628472222</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45540,7 +45540,7 @@
         <v>45156.54523148148</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45597,7 +45597,7 @@
         <v>45369.44256944444</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45654,7 +45654,7 @@
         <v>44375</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45711,7 +45711,7 @@
         <v>45434.56020833334</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45768,7 +45768,7 @@
         <v>45375</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>45427.93607638889</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45882,7 +45882,7 @@
         <v>45225</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45939,7 +45939,7 @@
         <v>45350</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45996,7 +45996,7 @@
         <v>44998.55319444444</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46073,7 +46073,7 @@
         <v>45428.55946759259</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>45428.5703587963</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46187,7 +46187,7 @@
         <v>45428.57371527778</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>45691.56284722222</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>45454.73359953704</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>45118.36900462963</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46415,7 +46415,7 @@
         <v>44593.63554398148</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46472,7 +46472,7 @@
         <v>45105.48627314815</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>45164</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46586,7 +46586,7 @@
         <v>45615</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>44165</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46700,7 +46700,7 @@
         <v>45105.47802083333</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46757,7 +46757,7 @@
         <v>45244.67376157407</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>45755.42104166667</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>45749</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46933,7 +46933,7 @@
         <v>45764</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46995,7 +46995,7 @@
         <v>45459.71949074074</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47052,7 +47052,7 @@
         <v>45005</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47109,7 +47109,7 @@
         <v>44098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47166,7 +47166,7 @@
         <v>45098</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47223,7 +47223,7 @@
         <v>45590</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47280,7 +47280,7 @@
         <v>45604.56427083333</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47342,7 +47342,7 @@
         <v>45604.56517361111</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47404,7 +47404,7 @@
         <v>45761.93880787037</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47466,7 +47466,7 @@
         <v>45604.56623842593</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47528,7 +47528,7 @@
         <v>45190.47119212963</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         <v>45708.35037037037</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47642,7 +47642,7 @@
         <v>45692.42515046296</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>44327</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>45229.53780092593</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>45091</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>45085</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>45749.74931712963</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>45716.34958333334</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48108,7 +48108,7 @@
         <v>44994.45271990741</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>45660</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>44610</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48279,7 +48279,7 @@
         <v>45149</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>44942.49850694444</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>44789.46129629629</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>45219.79758101852</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45085.53467592593</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>44154</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45427.9417824074</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45428.57160879629</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45338</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48797,7 +48797,7 @@
         <v>45338</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48859,7 +48859,7 @@
         <v>45716.3528125</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>45019</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45642</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>45714.37306712963</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45575.84530092592</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45057</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45154.65458333334</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45728</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45722.96171296296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45434.44790509259</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49434,7 +49434,7 @@
         <v>45709.42873842592</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>45229.58863425926</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>44734.3744212963</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>44734.37710648148</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -567,7 +567,7 @@
         <v>45174</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         <v>44112</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44175</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44266</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45313</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45475</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>45158</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>45840.46792824074</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45604.4624537037</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45195</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>44315</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>44455</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>44859</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45450.57783564815</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45604.53089120371</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44833</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>45517.34768518519</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>45404.55137731481</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45604.48800925926</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>44937</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45826.4996875</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45103</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45889</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>44295</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44375</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>44207</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>44827</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>44998</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45789.61961805556</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45791.44271990741</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>45335</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>44160</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44858</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>45688.59202546296</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>44676</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>45623</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45820.48319444444</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>44384</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>44663</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>44132</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>45825</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>44950</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45688.41431712963</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>44550</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>45897.51854166666</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>44207</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>44179.52865740741</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44243</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44270.56321759259</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>44228</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44155</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>44267.64171296296</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>44320.42899305555</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>44386</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>44386</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>44865.57608796296</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>44887.42784722222</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>44887.42950231482</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>44307.45770833334</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>44508</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>44175</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>44225</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>44201</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>44201</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>44201</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44285</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>44201</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>44613.65383101852</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>44483.4240625</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>44524.32766203704</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>44193</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>44225</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>44447</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>44242</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44202</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>44552.45428240741</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>44574.4577662037</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>44487</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>44461.68690972222</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>44536</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>44456</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>44127</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>44273</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>44321</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>44510</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>44734.36189814815</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>44812.51043981482</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>44319.33803240741</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         <v>44859</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>44176.66133101852</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>44225</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>44229</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>44574.45553240741</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>44165</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>44859</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44278</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>44265.69087962963</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44676.551875</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44859</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>44859</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44749</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>44574.43967592593</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>44602</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>44580</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>44602.57726851852</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44217</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>44201</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44201</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>44308</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>44859</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44430.93283564815</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44259</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>44795.48144675926</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>44757.40570601852</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>44124</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>44228</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>44225</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>44228</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>44225</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>44887.43138888889</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>44588.6396875</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>44505</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44456</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>44434</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>44375</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>44207</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>44845</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44375</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>44270.5584375</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44364</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44497</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>44201</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>44483.66988425926</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>44483.67144675926</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44552.45563657407</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>44503</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>44375</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>44475</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>44510</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>44376</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>44119</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>44214</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>44602.51873842593</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>44607</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>44607</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44803.35861111111</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>44887.42521990741</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>44343.88627314815</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>44711.38366898148</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>44887.42283564815</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44887.42663194444</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44490.74336805556</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>44721.32116898148</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>44610</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>44676.56075231481</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>44609</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>44522.60883101852</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>44424.57810185185</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44375</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>44371</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>44253</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>44795.60174768518</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>44795.60293981482</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11373,7 +11373,7 @@
         <v>44336.39239583333</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         <v>44242</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>44102</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>44250</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>44328.41473379629</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>44127</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>44837.43361111111</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>44582</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>44859</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>44683.46200231482</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>44158</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>44475.66188657407</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44686</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>44574</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>44459</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
         <v>44757</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>44175</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>44284</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>44120</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>44207</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>44175</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44344.48678240741</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44420.28219907408</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>44285.87041666666</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>44466</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>44603</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>44602</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>44524.46141203704</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>44690</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>44601.75174768519</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>44858.49122685185</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45275.35230324074</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>45098.44975694444</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>45770.625625</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>44524</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>45181</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>44610</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>44285.33586805555</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
         <v>44496.58679398148</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>45600.47440972222</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>45709.33226851852</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>45385</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>45708.35037037037</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>45709.40309027778</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>45601</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>45517.38890046296</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>45273</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45391.59185185185</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>44789.46129629629</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>45516.37174768518</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>44140</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>45020</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44526</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>44140</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44697</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44897.42872685185</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>44250</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>45607.60341435186</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45716.34217592593</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45697.97704861111</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>45716.34775462963</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>45716.34298611111</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>45783.47896990741</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>45398.79873842592</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>45604.48214120371</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>44154</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>44915.41944444444</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>44790</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45320</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>44531</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45454.73359953704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>45384.42409722223</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45642.47061342592</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45590</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>45389.73820601852</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>45775.49840277778</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>45057</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>45229.49331018519</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>45610.35752314814</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>45476.50758101852</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>45502.49574074074</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>45404</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>45165.77501157407</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>45761.93627314815</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>45761</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>45336</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45118.36900462963</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>45722.96171296296</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45755.41075231481</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>45568</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>45391.58608796296</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>44400</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45475</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>45639.59918981481</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>45642.46802083333</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>45525.6055787037</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         <v>45688.63835648148</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45709.38243055555</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>45338</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>45338.43268518519</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45590.39090277778</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>45664.57111111111</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>45622</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>44308</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>44424.57476851852</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>45488.46717592593</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>45428.54546296296</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>45428.54791666667</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>45428.55520833333</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45786</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>44470</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>45604.44618055555</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45552.65006944445</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>44523.4103587963</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>45279.61047453704</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>45742</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>44375</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>44327</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>45604.26549768518</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>45783</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>44430.29293981481</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45736.32833333333</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>45668.63396990741</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>44729.65407407407</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45069.69295138889</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>45440.6484375</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45279.37215277777</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>45320.58873842593</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>45348</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>45714.37306712963</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>45728.59358796296</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>44788.47552083333</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>45471</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>45181</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>45389.74396990741</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>45190.47119212963</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>45764</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45575.84530092592</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>44705</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>45544.36982638889</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44120</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44942.49850694444</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44602</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>44468.65578703704</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44468.68219907407</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>45408.61435185185</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45693</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45693</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>45709.42712962963</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>45098</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>44393</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>45019</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45140</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45769.41568287037</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>44592.48909722222</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>44369.46261574074</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45226.45565972223</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>44496</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45155</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>45229</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>44757</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>45745.75537037037</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>45506.59847222222</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>45720.40681712963</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45223.60331018519</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45350</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45348</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>45534</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45434.44790509259</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44552.46184027778</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45629.38060185185</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>44971.76626157408</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45801.73608796296</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>45801.72324074074</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45801.7406712963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45736.32997685186</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>45736.33076388889</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45801.7155324074</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>45800.6135300926</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45804</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>44757.40493055555</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>45805.59104166667</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45749.46461805556</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>45749.46740740741</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45804.40983796296</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>45804.49788194444</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22165,7 +22165,7 @@
         <v>45233</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>45804</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>45335.63466435186</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45338</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45338</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>45338.43358796297</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>45338</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>45338</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>45764</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45807.45759259259</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44524</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45764</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
         <v>45807.45905092593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>45807.46021990741</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>45049</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>45140</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45308</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>45691.56284722222</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>45245.37445601852</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>45153</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>45105.47802083333</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>45474.36921296296</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>44985</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45273.615</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23578,7 +23578,7 @@
         <v>45093.34891203704</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>45595.77847222222</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>45174</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23749,7 +23749,7 @@
         <v>45811.59519675926</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>44566</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>44278</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>44152</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>44459.56224537037</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>45547.6262037037</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>45547.62703703704</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45156.54523148148</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>45355.56142361111</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         <v>45709.39515046297</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>45709.40043981482</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>45278.39707175926</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>44446</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>45709.39714120371</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45348.33475694444</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45567.53571759259</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45692</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45400</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45149</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>45818</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45777.45011574074</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>45819.32747685185</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>45615</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>45819.46775462963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>45085</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>45041.59671296296</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>45041</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>44924.79619212963</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>45089</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>44392.68070601852</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>45674.38413194445</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45113.36457175926</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>45117</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45579</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>45351</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44922.50314814815</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>45229.58863425926</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>45642.47158564815</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45389</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>45389</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>44167</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>45400</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45469.34783564815</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>45670.3792824074</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>45706.36192129629</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>45440.63173611111</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         <v>45734</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>45338.43309027778</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         <v>45435.77655092593</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>45224</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>45211.81873842593</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>45622</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>44902.79445601852</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>45154.57079861111</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>44924.77766203704</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>45597.38953703704</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>45174.34193287037</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45162</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>45757.34662037037</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>45191</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>45547.62819444444</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         <v>45164</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27363,7 +27363,7 @@
         <v>45596.54981481482</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>44858</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>45727.61247685185</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45615</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45385.49137731481</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
         <v>45749.75060185185</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27705,7 +27705,7 @@
         <v>45375</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>44153.45842592593</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27819,7 +27819,7 @@
         <v>45597.3521412037</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>45597.35365740741</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>44984</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>45757</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>45824.48737268519</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44354</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         <v>45825.40163194444</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28233,7 +28233,7 @@
         <v>44984</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>45459.71376157407</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>45428.5499537037</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>45428.55199074074</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>45454.73629629629</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         <v>45369.42203703704</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>45082.56950231481</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>44858</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28689,7 +28689,7 @@
         <v>45404.56375</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>45709.38748842593</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>45709.42873842592</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>45085.53467592593</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28927,7 +28927,7 @@
         <v>44945.39559027777</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28984,7 +28984,7 @@
         <v>45604.56769675926</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29046,7 +29046,7 @@
         <v>45230</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>45385.44706018519</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>45825.58365740741</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>45476</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29284,7 +29284,7 @@
         <v>45636.96761574074</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>44734.3744212963</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>44734.37710648148</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29455,7 +29455,7 @@
         <v>45583.40994212963</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29512,7 +29512,7 @@
         <v>45336.92125</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>44942</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44942.60704861111</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>45644.36364583333</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         <v>44592.72989583333</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         <v>45677.70096064815</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29854,7 +29854,7 @@
         <v>45164</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>44208</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>45230.37582175926</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         <v>45546.60894675926</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>45082</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>45604.56190972222</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>45604.56427083333</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>45604.56517361111</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30335,7 +30335,7 @@
         <v>44838</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30392,7 +30392,7 @@
         <v>45107.61413194444</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>45204</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30506,7 +30506,7 @@
         <v>45692.42515046296</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30563,7 +30563,7 @@
         <v>45568</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>45568</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>45091</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>45118</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30806,7 +30806,7 @@
         <v>45163.72633101852</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>45005</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>45825.46516203704</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45692</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>45705.35732638889</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31096,7 +31096,7 @@
         <v>44994.45271990741</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>44951</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31210,7 +31210,7 @@
         <v>44396</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>45219.44987268518</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>45770</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>45547.62391203704</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>45547.62475694445</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>45763.68868055556</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>45763.69137731481</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>45688.58755787037</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>45370.64554398148</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>45434.56020833334</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31795,7 +31795,7 @@
         <v>45093</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>44917.58131944444</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45709.40761574074</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>45208.64244212963</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32028,7 +32028,7 @@
         <v>45428.53717592593</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>45428.54854166666</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32142,7 +32142,7 @@
         <v>45428.54914351852</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>45428.55339120371</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>45428.58675925926</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>45770</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>45223</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32427,7 +32427,7 @@
         <v>45716.3528125</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45372.49736111111</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>45604.47792824074</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45547.62553240741</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>44154</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>45201.50586805555</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>44984</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>45184.46447916667</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>45211</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>44638.34265046296</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>44865.54231481482</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>45826.49353009259</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>44923</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>45506.60435185185</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>44603</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>45103</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>44162</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>45826.37920138889</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45261</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>44503.58450231481</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>45826.50130787037</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33634,7 +33634,7 @@
         <v>45826.50511574074</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>45831.36230324074</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>45831.37613425926</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>45831.51181712963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>45831.37420138889</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>45831</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>45831.5818287037</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>45637.63881944444</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>45204</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34147,7 +34147,7 @@
         <v>44757.40103009259</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>44757.40538194445</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>45028</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>45338</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>44844.67142361111</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>44124</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>45552.6449537037</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>45552</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>44994.45623842593</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45112.3402199074</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>45232.72258101852</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>44229</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>45590.38761574074</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>45832.47321759259</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>45218</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>45028</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35084,7 +35084,7 @@
         <v>45459.71949074074</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35141,7 +35141,7 @@
         <v>45105.48627314815</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35198,7 +35198,7 @@
         <v>45835.37094907407</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35255,7 +35255,7 @@
         <v>45386.35322916666</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35317,7 +35317,7 @@
         <v>45688.43215277778</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>45688.58667824074</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>45835.48375</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>45338</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>45338</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>45366</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>45544.33987268519</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>44154</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>45155</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45219.79758101852</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35902,7 +35902,7 @@
         <v>45838.67675925926</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35964,7 +35964,7 @@
         <v>45428.55619212963</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>45761.93880787037</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>45839</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>45428.53776620371</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>44276</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36254,7 +36254,7 @@
         <v>45597.34225694444</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>45597.38799768518</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>45597.39101851852</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36440,7 +36440,7 @@
         <v>45838.37465277778</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36497,7 +36497,7 @@
         <v>45839.58087962963</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>45839</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>45838.6196875</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>45841.74796296296</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>45749</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>45230</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36849,7 +36849,7 @@
         <v>45540.56981481481</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>45709.32859953704</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>44711.38688657407</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37025,7 +37025,7 @@
         <v>45840.479375</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37082,7 +37082,7 @@
         <v>45749</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>45840.66209490741</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>45841.73791666667</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
         <v>45295</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37320,7 +37320,7 @@
         <v>45840.49215277778</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37377,7 +37377,7 @@
         <v>45338</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37439,7 +37439,7 @@
         <v>45349</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>45354.72975694444</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>45887.45643518519</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45243</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45887.46554398148</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>45666</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>44844</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>45842.47915509259</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>45842.55467592592</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>44406</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>45114.65185185185</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>45729.67947916667</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>44659.58702546296</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>45013</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>44908</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>44971.76994212963</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>44160</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44971.75834490741</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>45579</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>44154</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38594,7 +38594,7 @@
         <v>45211</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38651,7 +38651,7 @@
         <v>45205.35776620371</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38708,7 +38708,7 @@
         <v>44533.35804398148</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>45887.5765625</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45889.37565972222</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>45455</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45091</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>45372.49458333333</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>45889.36107638889</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>45196.47457175926</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
         <v>45889.36693287037</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>44140</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39288,7 +39288,7 @@
         <v>45755.42104166667</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>45755</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45891.49868055555</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>44833</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>45604.5687962963</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>44881.54231481482</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>45709.39251157407</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39702,7 +39702,7 @@
         <v>45244.86136574074</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>45728</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39816,7 +39816,7 @@
         <v>45229.53780092593</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39873,7 +39873,7 @@
         <v>45685.55012731482</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39930,7 +39930,7 @@
         <v>45063.27048611111</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39987,7 +39987,7 @@
         <v>45894.59266203704</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40044,7 +40044,7 @@
         <v>45245.7939699074</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>45764</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40163,7 +40163,7 @@
         <v>45225</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40220,7 +40220,7 @@
         <v>45679.50844907408</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45692</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>45891.49476851852</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>44160</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40448,7 +40448,7 @@
         <v>45854.62081018519</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40505,7 +40505,7 @@
         <v>45897.34547453704</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>45317</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40624,7 +40624,7 @@
         <v>45897</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40681,7 +40681,7 @@
         <v>45897.44971064815</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40738,7 +40738,7 @@
         <v>45041</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40795,7 +40795,7 @@
         <v>44260</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40852,7 +40852,7 @@
         <v>45320.88226851852</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         <v>45897.35350694445</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>45428.57160879629</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41023,7 +41023,7 @@
         <v>45146</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>45597.34579861111</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45597.34881944444</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>45897</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41261,7 +41261,7 @@
         <v>45357.39202546296</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>45260.46252314815</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>45901.57252314815</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>44592.50912037037</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41489,7 +41489,7 @@
         <v>44593</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41546,7 +41546,7 @@
         <v>45901.31172453704</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41603,7 +41603,7 @@
         <v>45716.33921296296</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41665,7 +41665,7 @@
         <v>45716.35056712963</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41727,7 +41727,7 @@
         <v>45901.31505787037</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41784,7 +41784,7 @@
         <v>45341.58440972222</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41846,7 +41846,7 @@
         <v>45898.39543981481</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>45901.44929398148</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41960,7 +41960,7 @@
         <v>45901.55628472222</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>45861.43393518519</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>45600.45402777778</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42131,7 +42131,7 @@
         <v>45233</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>45861.42532407407</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>45902.78745370371</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42302,7 +42302,7 @@
         <v>45230</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>45709.40560185185</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>45902.56516203703</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45118</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42540,7 +42540,7 @@
         <v>44105</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>45169.38462962963</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42654,7 +42654,7 @@
         <v>45720.41747685185</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42711,7 +42711,7 @@
         <v>45273.60899305555</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42768,7 +42768,7 @@
         <v>45273</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>44887</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42882,7 +42882,7 @@
         <v>45204</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>45085</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>44410</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>44882</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45407.5766087963</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43167,7 +43167,7 @@
         <v>45904.48038194444</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>45154.65458333334</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43281,7 +43281,7 @@
         <v>45905.62797453703</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
         <v>45075.50622685185</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>45530.36846064815</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>45842.48019675926</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43509,7 +43509,7 @@
         <v>45660</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>45688</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>45688.64506944444</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43690,7 +43690,7 @@
         <v>44939</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43747,7 +43747,7 @@
         <v>44939</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>45607.37846064815</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43861,7 +43861,7 @@
         <v>45865</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>45865.66577546296</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43975,7 +43975,7 @@
         <v>45908.51197916667</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>45865.67818287037</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>45737</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44146,7 +44146,7 @@
         <v>45909</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44203,7 +44203,7 @@
         <v>45908.39239583333</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44260,7 +44260,7 @@
         <v>45012</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45792.81104166667</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44374,7 +44374,7 @@
         <v>44375</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>45642</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44488,7 +44488,7 @@
         <v>45324.40112268519</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44545,7 +44545,7 @@
         <v>45910.6044212963</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44602,7 +44602,7 @@
         <v>45910.6277662037</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44659,7 +44659,7 @@
         <v>44438</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44716,7 +44716,7 @@
         <v>45692</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44773,7 +44773,7 @@
         <v>44946</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44830,7 +44830,7 @@
         <v>45204.42494212963</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44887,7 +44887,7 @@
         <v>45702.36793981482</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44944,7 +44944,7 @@
         <v>45755</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>44124</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45058,7 +45058,7 @@
         <v>45085</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45115,7 +45115,7 @@
         <v>45338</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45177,7 +45177,7 @@
         <v>44937</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>44937.46436342593</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45291,7 +45291,7 @@
         <v>45195</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45348,7 +45348,7 @@
         <v>44361.93059027778</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45405,7 +45405,7 @@
         <v>45428.57578703704</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45462,7 +45462,7 @@
         <v>45146</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45519,7 +45519,7 @@
         <v>45146</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45576,7 +45576,7 @@
         <v>45716.34958333334</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45638,7 +45638,7 @@
         <v>45604.48289351852</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45700,7 +45700,7 @@
         <v>45369.44256944444</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45757,7 +45757,7 @@
         <v>45869.39628472222</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45814,7 +45814,7 @@
         <v>45910.63862268518</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>45910.50434027778</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45928,7 +45928,7 @@
         <v>44599</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45985,7 +45985,7 @@
         <v>45460.82011574074</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46042,7 +46042,7 @@
         <v>44595.55912037037</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46099,7 +46099,7 @@
         <v>45561.37106481481</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>45839</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46213,7 +46213,7 @@
         <v>44757.39927083333</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>44757.40454861111</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46337,7 +46337,7 @@
         <v>45764</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46399,7 +46399,7 @@
         <v>45764.84103009259</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46461,7 +46461,7 @@
         <v>45001</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46518,7 +46518,7 @@
         <v>44593.63554398148</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46575,7 +46575,7 @@
         <v>45264.6516087963</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46632,7 +46632,7 @@
         <v>45181</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45561.3744212963</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>45722.40604166667</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45604.56101851852</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46870,7 +46870,7 @@
         <v>45604.56623842593</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45604.56958333333</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45770.62311342593</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>44153</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45288.46611111111</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>45674.38553240741</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47232,7 +47232,7 @@
         <v>45764.67251157408</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47289,7 +47289,7 @@
         <v>45279</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47346,7 +47346,7 @@
         <v>45153</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47403,7 +47403,7 @@
         <v>45244.67376157407</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47460,7 +47460,7 @@
         <v>45873</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47517,7 +47517,7 @@
         <v>45154.56967592592</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47574,7 +47574,7 @@
         <v>45915.54190972223</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47631,7 +47631,7 @@
         <v>45915.54486111111</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>45747</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45747</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45335.63689814815</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>44998.55319444444</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>45875</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>45190.39688657408</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>45427.93607638889</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>45428.55946759259</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>44165</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48231,7 +48231,7 @@
         <v>45749.74931712963</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48288,7 +48288,7 @@
         <v>45146</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48345,7 +48345,7 @@
         <v>44524.66444444445</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48402,7 +48402,7 @@
         <v>45057</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48459,7 +48459,7 @@
         <v>45538.80545138889</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
         <v>45427.9417824074</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48573,7 +48573,7 @@
         <v>45428.5703587963</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48630,7 +48630,7 @@
         <v>45428.57371527778</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48687,7 +48687,7 @@
         <v>45877</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48744,7 +48744,7 @@
         <v>45009</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48801,7 +48801,7 @@
         <v>44610</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>45649.6427662037</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48915,7 +48915,7 @@
         <v>44998</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>45489.50666666667</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49034,7 +49034,7 @@
         <v>45922.34789351852</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49091,7 +49091,7 @@
         <v>45923.58040509259</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49148,7 +49148,7 @@
         <v>45923.37464120371</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49205,7 +49205,7 @@
         <v>45923.39356481482</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49262,7 +49262,7 @@
         <v>45881.55119212963</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49319,7 +49319,7 @@
         <v>45881</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49376,7 +49376,7 @@
         <v>45923.70304398148</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49433,7 +49433,7 @@
         <v>45923.71457175926</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>45923.57438657407</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45839</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>45925.64894675926</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>45881.4566087963</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -567,7 +567,7 @@
         <v>45174</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         <v>44112</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44266</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45313</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45475</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44175</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>45158</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>45195</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>45604.4624537037</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45840.46792824074</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>44315</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>44455</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>44859</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45604.53089120371</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45889</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45604.48800925926</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>44833</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>45103</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45450.57783564815</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45826.4996875</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>45517.34768518519</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>45404.55137731481</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44937</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>44295</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44375</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>44207</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>44827</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>44950</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>44384</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>44858</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>44550</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>44676</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45623</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44160</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>45688.59202546296</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>45897.51854166666</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45688.41431712963</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45926.56731481481</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>44132</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>45335</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>45789.61961805556</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>45791.44271990741</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>45820.48319444444</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>45825</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>44998</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>44663</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>44207</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>44179.52865740741</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>44243</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>44270.56321759259</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>44228</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>44155</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>44267.64171296296</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>44320.42899305555</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>44386</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>44386</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44865.57608796296</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>44887.42784722222</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>44887.42950231482</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>44307.45770833334</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>44508</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>44175</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>44225</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44201</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44201</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>44201</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44285</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>44201</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44524.32766203704</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>44613.65383101852</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>44483.4240625</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>44193</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>44225</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44447</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>44242</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44487</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44574.4577662037</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>44552.45428240741</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>44536</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>44461.68690972222</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>44510</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>44456</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>44127</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>44734.36189814815</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>44273</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>44812.51043981482</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6947,7 